--- a/excel/historico_acertos_modelos.xlsx
+++ b/excel/historico_acertos_modelos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,11 +492,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>09 19 27 32 41 42</t>
+          <t>09, 19, 27, 32, 42, 58</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>06 15 23 36 37 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -541,11 +541,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -555,12 +555,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>09 19 32 34 41 45</t>
+          <t>09, 19, 32, 34, 41, 45</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>06 15 23 36 37 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -590,11 +590,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,22 +604,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>06 11 14 27 30 58</t>
+          <t>06, 11, 14, 27, 30, 58</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>06 15 23 36 37 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -639,11 +639,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -653,12 +653,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>04 08 11 13 33 60</t>
+          <t>04, 06, 08, 11, 27, 49</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>06 15 23 36 37 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -688,11 +688,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -702,12 +702,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>05 10 27 33 37 53</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>06 15 23 36 37 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -737,11 +737,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11 14 27 30 43 58</t>
+          <t>06, 11, 14, 27, 30, 58</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>06 15 23 36 37 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -786,11 +786,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>05 10 33 37 42 53</t>
+          <t>05, 10, 33, 37, 42, 53</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>06 15 23 36 37 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -835,11 +835,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>05 09 10 11 27 33</t>
+          <t>05, 06, 11, 27, 33, 53</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06 15 23 36 37 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -884,11 +884,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -898,22 +898,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>09 19 27 32 42 58</t>
+          <t>09, 19, 27, 32, 42, 58</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24 25 28 37 47 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -933,11 +933,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -947,22 +947,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>09 19 32 34 41 45</t>
+          <t>09, 19, 32, 34, 41, 45</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24 25 28 37 47 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -982,11 +982,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -996,22 +996,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>06 11 14 27 30 58</t>
+          <t>06, 11, 14, 27, 30, 58</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24 25 28 37 47 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1031,11 +1031,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>04 06 08 11 27 49</t>
+          <t>11, 13, 25, 33, 53, 56</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>24 25 28 37 47 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1080,11 +1080,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>05 10 27 33 37 53</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24 25 28 37 47 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1129,11 +1129,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1143,22 +1143,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>06 11 14 27 30 58</t>
+          <t>06, 11, 14, 27, 30, 58</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>24 25 28 37 47 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1178,11 +1178,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>05 10 33 37 42 53</t>
+          <t>05, 10, 33, 37, 42, 53</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24 25 28 37 47 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1227,11 +1227,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1241,22 +1241,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>05 06 09 11 27 58</t>
+          <t>05, 10, 11, 27, 33, 53</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>24 25 28 37 47 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1276,11 +1276,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>09 19 27 32 42 58</t>
+          <t>19, 27, 32, 41, 42, 45</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>05 09 11 17 18 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1325,11 +1325,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>09 19 32 34 41 45</t>
+          <t>19, 32, 34, 41, 45, 59</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>05 09 11 17 18 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1374,11 +1374,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>06 11 14 27 30 58</t>
+          <t>06, 11, 14, 17, 27, 58</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>05 09 11 17 18 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1423,11 +1423,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1437,22 +1437,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>11 13 25 33 53 56</t>
+          <t>05, 15, 25, 33, 36, 56</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>05 09 11 17 18 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>6</v>
       </c>
       <c r="I21" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1472,11 +1472,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>05 10 27 33 37 53</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>05 09 11 17 18 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1521,11 +1521,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1535,22 +1535,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>06 11 14 27 30 58</t>
+          <t>06, 11, 14, 17, 27, 38</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>05 09 11 17 18 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1570,11 +1570,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>05 10 33 37 42 53</t>
+          <t>05, 10, 33, 37, 42, 53</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>05 09 11 17 18 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1619,11 +1619,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1633,22 +1633,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>05 11 27 33 53 58</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>05 09 11 17 18 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1668,11 +1668,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>19 27 32 41 42 45</t>
+          <t>19, 27, 32, 42, 45, 46</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>05 35 36 41 43 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1717,11 +1717,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1731,22 +1731,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>19 32 34 41 45 59</t>
+          <t>19, 32, 34, 45, 46, 59</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>05 35 36 41 43 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1766,11 +1766,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1780,22 +1780,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>06 11 14 17 27 58</t>
+          <t>06, 11, 14, 27, 43, 58</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>05 35 36 41 43 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
         <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1815,11 +1815,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1829,22 +1829,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>05 15 25 33 36 56</t>
+          <t>23, 24, 41, 43, 53, 56</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>05 35 36 41 43 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1864,11 +1864,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1878,22 +1878,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>05 10 27 33 37 53</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>05 35 36 41 43 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
         <v>6</v>
       </c>
       <c r="I30" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1913,11 +1913,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1927,22 +1927,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>06 11 14 17 27 38</t>
+          <t>06, 11, 14, 17, 27, 43</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>05 35 36 41 43 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
         <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1962,11 +1962,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>05 10 33 37 42 53</t>
+          <t>05, 10, 33, 37, 42, 53</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>05 35 36 41 43 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2011,11 +2011,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2025,22 +2025,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>05 06 10 11 27 33</t>
+          <t>05, 10, 27, 37, 43, 53</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>05 35 36 41 43 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
         <v>6</v>
       </c>
       <c r="I33" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2060,11 +2060,11 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2074,22 +2074,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19 27 32 42 45 46</t>
+          <t>19, 32, 42, 45, 46, 58</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>04 10 20 25 27 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>6</v>
       </c>
       <c r="I34" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2109,11 +2109,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2123,12 +2123,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19 32 34 45 46 59</t>
+          <t>19, 32, 34, 45, 46, 59</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>04 10 20 25 27 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2158,11 +2158,11 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2172,22 +2172,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>06 11 14 27 43 58</t>
+          <t>06, 11, 14, 27, 43, 58</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>04 10 20 25 27 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2207,11 +2207,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2221,22 +2221,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>23 24 41 43 53 56</t>
+          <t>04, 10, 17, 23, 41, 56</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>04 10 20 25 27 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
         <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2256,11 +2256,11 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2270,12 +2270,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>05 10 27 33 37 53</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>04 10 20 25 27 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2305,11 +2305,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2319,22 +2319,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>06 11 14 17 27 43</t>
+          <t>06, 11, 14, 17, 27, 43</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>04 10 20 25 27 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2354,11 +2354,11 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2368,22 +2368,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>05 10 33 37 42 53</t>
+          <t>05, 10, 33, 37, 42, 53</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>04 10 20 25 27 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" t="n">
         <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2403,11 +2403,11 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>05 06 10 27 43 53</t>
+          <t>05, 10, 17, 27, 33, 53</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>04 10 20 25 27 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2452,11 +2452,11 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>19 32 42 45 46 58</t>
+          <t>19, 32, 42, 45, 46, 58</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>08 10 30 38 50 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2501,11 +2501,11 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>19 32 34 45 46 59</t>
+          <t>19, 32, 34, 45, 46, 59</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>08 10 30 38 50 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2550,11 +2550,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2564,22 +2564,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>06 11 14 27 43 58</t>
+          <t>06, 11, 27, 30, 43, 58</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>08 10 30 38 50 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
         <v>6</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2599,11 +2599,11 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2613,22 +2613,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>04 10 17 23 41 56</t>
+          <t>17, 23, 27, 36, 37, 41</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>08 10 30 38 50 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>6</v>
       </c>
       <c r="I45" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2648,11 +2648,11 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2662,22 +2662,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>05 10 27 33 37 53</t>
+          <t>05, 10, 27, 37, 38, 53</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>08 10 30 38 50 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>6</v>
       </c>
       <c r="I46" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2697,11 +2697,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>06 11 14 17 27 43</t>
+          <t>11, 14, 27, 30, 38, 43</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>08 10 30 38 50 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -2746,11 +2746,11 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2760,22 +2760,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>05 10 33 37 42 53</t>
+          <t>05, 10, 37, 38, 42, 53</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>08 10 30 38 50 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>6</v>
       </c>
       <c r="I48" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2795,11 +2795,11 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2809,22 +2809,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>05 06 10 11 14 27</t>
+          <t>05, 10, 27, 37, 38, 53</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>08 10 30 38 50 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>6</v>
       </c>
       <c r="I49" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2844,11 +2844,11 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>19 32 42 45 46 58</t>
+          <t>19, 32, 42, 45, 46, 58</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>04 06 09 13 28 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -2893,11 +2893,11 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19 32 34 45 46 59</t>
+          <t>19, 32, 34, 45, 46, 59</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>04 06 09 13 28 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2942,11 +2942,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2956,22 +2956,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>06 11 27 30 43 58</t>
+          <t>06, 11, 27, 30, 48, 58</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>04 06 09 13 28 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>6</v>
       </c>
       <c r="I52" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2991,11 +2991,11 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3005,22 +3005,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>17 23 27 36 37 41</t>
+          <t>04, 06, 11, 23, 35, 37</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>04 06 09 13 28 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
         <v>6</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3040,11 +3040,11 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>05 10 27 37 38 53</t>
+          <t>05, 10, 27, 37, 38, 53</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>04 06 09 13 28 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3089,11 +3089,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>11 14 27 30 38 43</t>
+          <t>06, 11, 14, 27, 30, 38</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>04 06 09 13 28 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3138,11 +3138,11 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>05 10 37 38 42 53</t>
+          <t>05, 10, 37, 38, 42, 53</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>04 06 09 13 28 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3187,11 +3187,11 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>05 10 11 27 37 38</t>
+          <t>05, 06, 11, 27, 37, 38</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>04 06 09 13 28 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3236,11 +3236,11 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>19 32 42 45 46 58</t>
+          <t>19, 32, 42, 45, 46, 58</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>01 04 17 33 41 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -3285,11 +3285,11 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>19 32 34 45 46 59</t>
+          <t>19, 32, 34, 45, 46, 59</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>01 04 17 33 41 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -3334,11 +3334,11 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>06 11 27 30 48 58</t>
+          <t>06, 11, 17, 27, 30, 58</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>01 04 17 33 41 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3383,11 +3383,11 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3397,22 +3397,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>04 06 11 23 35 37</t>
+          <t>05, 11, 23, 37, 41, 56</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>01 04 17 33 41 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>6</v>
       </c>
       <c r="I61" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3432,11 +3432,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3446,22 +3446,22 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>05 10 27 37 38 53</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>01 04 17 33 41 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="n">
         <v>6</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3481,11 +3481,11 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>06 11 14 27 30 38</t>
+          <t>06, 11, 17, 27, 30, 38</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>01 04 17 33 41 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -3530,11 +3530,11 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3544,22 +3544,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>05 10 37 38 42 53</t>
+          <t>05, 10, 33, 37, 42, 53</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>01 04 17 33 41 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
         <v>6</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3579,11 +3579,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3593,22 +3593,22 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>05 06 11 27 37 38</t>
+          <t>05, 10, 11, 27, 37, 53</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>01 04 17 33 41 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
         <v>6</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3628,11 +3628,11 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3642,22 +3642,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>19 32 42 45 46 58</t>
+          <t>19, 32, 42, 45, 46, 58</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>07 10 39 40 43 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
         <v>6</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3677,11 +3677,11 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3691,22 +3691,22 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>19 32 34 45 46 59</t>
+          <t>19, 32, 34, 45, 46, 59</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>07 10 39 40 43 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
         <v>6</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3726,11 +3726,11 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>06 11 17 27 30 58</t>
+          <t>06, 11, 17, 27, 30, 43</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>07 10 39 40 43 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -3775,11 +3775,11 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3789,22 +3789,22 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>05 11 23 37 41 56</t>
+          <t>05, 11, 41, 43, 53, 56</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>07 10 39 40 43 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" t="n">
         <v>6</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3824,11 +3824,11 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>05 10 27 33 37 53</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>07 10 39 40 43 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -3873,11 +3873,11 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3887,12 +3887,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>06 11 17 27 30 38</t>
+          <t>06, 10, 11, 17, 27, 43</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>07 10 39 40 43 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -3922,11 +3922,11 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>05 10 33 37 42 53</t>
+          <t>05, 10, 33, 37, 42, 53</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>07 10 39 40 43 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -3971,11 +3971,11 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>05 06 10 11 27 37</t>
+          <t>05, 10, 11, 27, 43, 53</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>07 10 39 40 43 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -4020,11 +4020,11 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>19 32 42 45 46 58</t>
+          <t>32, 42, 45, 46, 54, 58</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>05 19 22 44 47 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -4069,11 +4069,11 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4083,22 +4083,22 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>19 32 34 45 46 59</t>
+          <t>12, 32, 34, 45, 46, 59</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>05 19 22 44 47 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
         <v>6</v>
       </c>
       <c r="I75" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -4118,11 +4118,11 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4132,22 +4132,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>06 11 17 27 30 43</t>
+          <t>06, 11, 17, 27, 30, 43</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>05 19 22 44 47 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H76" t="n">
         <v>6</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -4167,11 +4167,11 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>05 11 41 43 53 56</t>
+          <t>05, 11, 27, 28, 41, 53</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>05 19 22 44 47 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -4216,11 +4216,11 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>05 10 27 33 37 53</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>05 19 22 44 47 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -4265,11 +4265,11 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>06 10 11 17 27 43</t>
+          <t>06, 10, 11, 17, 27, 43</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>05 19 22 44 47 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H79" t="n">
         <v>6</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -4314,11 +4314,11 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4328,22 +4328,22 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>05 10 33 37 42 53</t>
+          <t>05, 10, 33, 37, 42, 53</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>05 19 22 44 47 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
         <v>6</v>
       </c>
       <c r="I80" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -4363,11 +4363,11 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>05 10 11 27 43 53</t>
+          <t>05, 10, 11, 27, 33, 53</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>05 19 22 44 47 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -4412,11 +4412,11 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3794</v>
+        <v>3795</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4426,31 +4426,31 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 09 11 12 15 18 21 22 23 24 25</t>
+          <t>01, 02, 03, 04, 05, 09, 11, 12, 15, 16, 21, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 08 10 12 13 15 18 19 21 23 24</t>
+          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 13, 14, 18, 19, 22, 24</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H82" t="n">
         <v>15</v>
       </c>
       <c r="I82" t="n">
-        <v>73.3</v>
+        <v>53.3</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>11 acertos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -4461,11 +4461,11 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3794</v>
+        <v>3795</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4475,22 +4475,22 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>02 04 05 06 08 09 12 13 16 17 18 19 20 22 23</t>
+          <t>01, 02, 03, 05, 07, 09, 11, 14, 15, 16, 17, 20, 22, 24, 25</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 08 10 12 13 15 18 19 21 23 24</t>
+          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 13, 14, 18, 19, 22, 24</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H83" t="n">
         <v>15</v>
       </c>
       <c r="I83" t="n">
-        <v>60</v>
+        <v>46.7</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -4510,11 +4510,11 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3794</v>
+        <v>3795</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4524,31 +4524,31 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 09 11 12 13 14 15 21 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 14, 15, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 08 10 12 13 15 18 19 21 23 24</t>
+          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 13, 14, 18, 19, 22, 24</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H84" t="n">
         <v>15</v>
       </c>
       <c r="I84" t="n">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>11 acertos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -4559,11 +4559,11 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3794</v>
+        <v>3795</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4573,31 +4573,31 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>01 04 05 06 09 10 11 12 14 18 20 21 22 24 25</t>
+          <t>03, 05, 07, 08, 09, 11, 12, 13, 14, 18, 19, 20, 22, 24, 25</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 08 10 12 13 15 18 19 21 23 24</t>
+          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 13, 14, 18, 19, 22, 24</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H85" t="n">
         <v>15</v>
       </c>
       <c r="I85" t="n">
-        <v>60</v>
+        <v>73.3</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -4608,11 +4608,11 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3794</v>
+        <v>3795</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4622,31 +4622,31 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 09 10 11 12 13 14 15 20 24 25</t>
+          <t>01, 02, 03, 04, 05, 10, 11, 12, 13, 14, 15, 20, 22, 24, 25</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 08 10 12 13 15 18 19 21 23 24</t>
+          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 13, 14, 18, 19, 22, 24</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H86" t="n">
         <v>15</v>
       </c>
       <c r="I86" t="n">
-        <v>60</v>
+        <v>73.3</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -4657,11 +4657,11 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3794</v>
+        <v>3795</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4671,31 +4671,31 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 07 09 11 12 13 15 21 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 07, 09, 11, 12, 13, 15, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 08 10 12 13 15 18 19 21 23 24</t>
+          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 13, 14, 18, 19, 22, 24</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H87" t="n">
         <v>15</v>
       </c>
       <c r="I87" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>11 acertos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -4706,11 +4706,11 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3794</v>
+        <v>3795</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4720,31 +4720,31 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>01 03 04 07 09 10 11 12 13 14 19 20 22 24 25</t>
+          <t>01, 03, 04, 07, 09, 10, 11, 12, 13, 14, 19, 20, 22, 24, 25</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 08 10 12 13 15 18 19 21 23 24</t>
+          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 13, 14, 18, 19, 22, 24</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H88" t="n">
         <v>15</v>
       </c>
       <c r="I88" t="n">
-        <v>53.3</v>
+        <v>73.3</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -4755,11 +4755,11 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3794</v>
+        <v>3795</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 09 11 12 13 14 15 20 21 24 25</t>
+          <t>01, 03, 04, 05, 07, 09, 11, 12, 13, 14, 15, 20, 22, 24, 25</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 08 10 12 13 15 18 19 21 23 24</t>
+          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 13, 14, 18, 19, 22, 24</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -4804,11 +4804,11 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4818,22 +4818,22 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 09 11 12 15 16 21 22 23 24 25</t>
+          <t>01, 02, 03, 04, 05, 07, 09, 11, 15, 16, 17, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 08 10 11 12 13 14 18 19 22 24</t>
+          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H90" t="n">
         <v>15</v>
       </c>
       <c r="I90" t="n">
-        <v>53.3</v>
+        <v>66.7</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -4853,11 +4853,11 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4867,22 +4867,22 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>02 06 07 08 09 10 11 13 14 16 17 19 20 22 25</t>
+          <t>01, 02, 04, 05, 07, 09, 11, 15, 16, 17, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 08 10 11 12 13 14 18 19 22 24</t>
+          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H91" t="n">
         <v>15</v>
       </c>
       <c r="I91" t="n">
-        <v>53.3</v>
+        <v>66.7</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -4902,11 +4902,11 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4916,12 +4916,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 09 11 12 13 14 15 21 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 14, 15, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 08 10 11 12 13 14 18 19 22 24</t>
+          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -4951,11 +4951,11 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>03 05 07 08 09 11 12 13 14 18 19 20 22 24 25</t>
+          <t>01, 03, 04, 05, 07, 08, 09, 10, 11, 12, 13, 16, 18, 20, 24</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 08 10 11 12 13 14 18 19 22 24</t>
+          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>11 acertos</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5000,11 +5000,11 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 09 10 11 12 13 14 15 20 24 25</t>
+          <t>01, 02, 03, 04, 05, 10, 11, 12, 13, 14, 15, 20, 22, 24, 25</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 08 10 11 12 13 14 18 19 22 24</t>
+          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H94" t="n">
         <v>15</v>
       </c>
       <c r="I94" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -5049,11 +5049,11 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5063,22 +5063,22 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 07 09 11 12 13 15 21 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 14, 15, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 08 10 11 12 13 14 18 19 22 24</t>
+          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H95" t="n">
         <v>15</v>
       </c>
       <c r="I95" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -5098,11 +5098,11 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5112,31 +5112,31 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>01 03 04 07 09 10 11 12 13 14 19 20 22 24 25</t>
+          <t>01, 03, 04, 07, 09, 10, 11, 12, 13, 14, 19, 20, 22, 24, 25</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 08 10 11 12 13 14 18 19 22 24</t>
+          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H96" t="n">
         <v>15</v>
       </c>
       <c r="I96" t="n">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>11 acertos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -5147,11 +5147,11 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5161,31 +5161,31 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>01 03 04 05 07 09 11 12 13 14 15 20 22 24 25</t>
+          <t>01, 03, 04, 05, 07, 09, 10, 11, 12, 13, 14, 15, 20, 24, 25</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 08 10 11 12 13 14 18 19 22 24</t>
+          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H97" t="n">
         <v>15</v>
       </c>
       <c r="I97" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -5196,11 +5196,11 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5210,22 +5210,22 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 07 09 11 15 16 17 21 23 24 25</t>
+          <t>01, 02, 03, 04, 05, 06, 11, 12, 13, 14, 15, 17, 23, 24, 25</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>03 04 05 06 07 09 10 11 12 15 16 19 20 21 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H98" t="n">
         <v>15</v>
       </c>
       <c r="I98" t="n">
-        <v>66.7</v>
+        <v>46.7</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -5245,11 +5245,11 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>01 02 07 09 10 13 15 16 17 19 20 21 22 23 25</t>
+          <t>01, 02, 03, 05, 08, 11, 13, 14, 15, 17, 18, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>03 04 05 06 07 09 10 11 12 15 16 19 20 21 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -5294,11 +5294,11 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5308,22 +5308,22 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 09 11 12 13 14 15 21 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 14, 15, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>03 04 05 06 07 09 10 11 12 15 16 19 20 21 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H100" t="n">
         <v>15</v>
       </c>
       <c r="I100" t="n">
-        <v>66.7</v>
+        <v>46.7</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -5343,11 +5343,11 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5357,31 +5357,31 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>01 03 04 05 07 08 09 10 11 12 13 16 18 20 24</t>
+          <t>01, 03, 05, 06, 10, 11, 12, 13, 14, 18, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>03 04 05 06 07 09 10 11 12 15 16 19 20 21 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H101" t="n">
         <v>15</v>
       </c>
       <c r="I101" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>11 acertos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -5392,11 +5392,11 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 10 11 12 13 14 15 20 22 24 25</t>
+          <t>01, 02, 03, 04, 05, 10, 11, 12, 13, 14, 15, 20, 22, 24, 25</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>03 04 05 06 07 09 10 11 12 15 16 19 20 21 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H102" t="n">
         <v>15</v>
       </c>
       <c r="I102" t="n">
-        <v>60</v>
+        <v>46.7</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -5441,11 +5441,11 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5455,22 +5455,22 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 09 11 12 13 14 15 21 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 07, 09, 11, 12, 13, 15, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>03 04 05 06 07 09 10 11 12 15 16 19 20 21 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H103" t="n">
         <v>15</v>
       </c>
       <c r="I103" t="n">
-        <v>66.7</v>
+        <v>46.7</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -5490,11 +5490,11 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5504,22 +5504,22 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>01 03 04 07 09 10 11 12 13 14 19 20 22 24 25</t>
+          <t>01, 03, 04, 07, 09, 10, 11, 12, 13, 14, 19, 20, 22, 24, 25</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>03 04 05 06 07 09 10 11 12 15 16 19 20 21 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H104" t="n">
         <v>15</v>
       </c>
       <c r="I104" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -5539,11 +5539,11 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5553,31 +5553,31 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>01 03 04 05 07 09 10 11 12 13 14 15 20 24 25</t>
+          <t>01, 03, 04, 05, 06, 10, 11, 12, 13, 14, 15, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>03 04 05 06 07 09 10 11 12 15 16 19 20 21 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H105" t="n">
         <v>15</v>
       </c>
       <c r="I105" t="n">
-        <v>73.3</v>
+        <v>53.3</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>11 acertos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -5588,11 +5588,11 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5602,22 +5602,22 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 06 11 12 13 14 15 17 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 17, 21, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>01 02 03 06 07 08 09 10 13 14 16 18 19 20 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H106" t="n">
         <v>15</v>
       </c>
       <c r="I106" t="n">
-        <v>46.7</v>
+        <v>40</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -5637,11 +5637,11 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5651,31 +5651,31 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>01 02 07 08 10 13 14 16 17 18 19 21 22 23 25</t>
+          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 17, 21, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>01 02 03 06 07 08 09 10 13 14 16 18 19 20 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H107" t="n">
         <v>15</v>
       </c>
       <c r="I107" t="n">
-        <v>73.3</v>
+        <v>40</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>11 acertos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -5686,11 +5686,11 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5700,22 +5700,22 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 09 11 12 13 14 15 21 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 14, 15, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>01 02 03 06 07 08 09 10 13 14 16 18 19 20 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H108" t="n">
         <v>15</v>
       </c>
       <c r="I108" t="n">
-        <v>46.7</v>
+        <v>53.3</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -5735,11 +5735,11 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5749,22 +5749,22 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>01 03 05 06 10 11 12 13 14 18 20 21 23 24 25</t>
+          <t>03, 04, 05, 06, 10, 11, 12, 13, 15, 18, 20, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>01 02 03 06 07 08 09 10 13 14 16 18 19 20 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H109" t="n">
         <v>15</v>
       </c>
       <c r="I109" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -5784,11 +5784,11 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5798,22 +5798,22 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 09 10 11 12 13 14 15 20 24 25</t>
+          <t>01, 02, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 20, 24, 25</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>01 02 03 06 07 08 09 10 13 14 16 18 19 20 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H110" t="n">
         <v>15</v>
       </c>
       <c r="I110" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -5833,11 +5833,11 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5847,22 +5847,22 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 07 09 11 12 13 15 21 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 07, 09, 11, 12, 13, 15, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>01 02 03 06 07 08 09 10 13 14 16 18 19 20 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H111" t="n">
         <v>15</v>
       </c>
       <c r="I111" t="n">
-        <v>46.7</v>
+        <v>53.3</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -5882,11 +5882,11 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>01 03 04 07 09 10 11 12 13 14 19 20 22 24 25</t>
+          <t>01, 03, 04, 07, 09, 10, 11, 12, 13, 14, 19, 20, 22, 24, 25</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>01 02 03 06 07 08 09 10 13 14 16 18 19 20 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -5931,11 +5931,11 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5945,22 +5945,22 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 09 10 11 12 13 14 15 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>01 02 03 06 07 08 09 10 13 14 16 18 19 20 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H113" t="n">
         <v>15</v>
       </c>
       <c r="I113" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -5980,11 +5980,11 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5994,22 +5994,22 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 11 12 13 15 17 21 22 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 17, 21, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>01 02 04 05 06 07 08 09 10 11 14 18 19 20 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H114" t="n">
         <v>15</v>
       </c>
       <c r="I114" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -6029,11 +6029,11 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6043,22 +6043,22 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>02 04 05 07 10 11 12 15 16 17 20 21 22 24 25</t>
+          <t>01, 03, 05, 06, 11, 12, 13, 15, 16, 17, 21, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>01 02 04 05 06 07 08 09 10 11 14 18 19 20 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H115" t="n">
         <v>15</v>
       </c>
       <c r="I115" t="n">
-        <v>46.7</v>
+        <v>53.3</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -6078,11 +6078,11 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6092,22 +6092,22 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 09 11 12 13 14 15 21 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 14, 15, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>01 02 04 05 06 07 08 09 10 11 14 18 19 20 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H116" t="n">
         <v>15</v>
       </c>
       <c r="I116" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -6127,11 +6127,11 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6141,22 +6141,22 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>03 04 05 06 10 11 12 13 15 18 20 22 23 24 25</t>
+          <t>03, 05, 06, 09, 10, 11, 12, 13, 14, 15, 20, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>01 02 04 05 06 07 08 09 10 11 14 18 19 20 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H117" t="n">
         <v>15</v>
       </c>
       <c r="I117" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -6176,11 +6176,11 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6190,22 +6190,22 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 09 10 11 12 13 14 15 20 24 25</t>
+          <t>01, 02, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 20, 24, 25</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>01 02 04 05 06 07 08 09 10 11 14 18 19 20 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H118" t="n">
         <v>15</v>
       </c>
       <c r="I118" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -6225,11 +6225,11 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6239,22 +6239,22 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 07 09 11 12 13 15 21 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 07, 09, 11, 12, 13, 15, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>01 02 04 05 06 07 08 09 10 11 14 18 19 20 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H119" t="n">
         <v>15</v>
       </c>
       <c r="I119" t="n">
-        <v>53.3</v>
+        <v>66.7</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -6274,11 +6274,11 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6288,31 +6288,31 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>01 03 04 07 09 10 11 12 13 14 19 20 22 24 25</t>
+          <t>01, 03, 04, 07, 09, 10, 11, 12, 13, 14, 19, 20, 22, 24, 25</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>01 02 04 05 06 07 08 09 10 11 14 18 19 20 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H120" t="n">
         <v>15</v>
       </c>
       <c r="I120" t="n">
-        <v>60</v>
+        <v>73.3</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -6323,11 +6323,11 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6337,31 +6337,31 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 09 10 11 12 13 15 20 21 24 25</t>
+          <t>01, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>01 02 04 05 06 07 08 09 10 11 14 18 19 20 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H121" t="n">
         <v>15</v>
       </c>
       <c r="I121" t="n">
-        <v>53.3</v>
+        <v>73.3</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -6372,11 +6372,11 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6386,22 +6386,22 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 11 12 13 15 17 21 22 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 15, 17, 21, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>01 03 04 05 07 08 10 12 13 18 19 20 23 24 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H122" t="n">
         <v>15</v>
       </c>
       <c r="I122" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -6421,11 +6421,11 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6435,22 +6435,22 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>02 03 07 10 12 13 15 16 17 19 20 21 22 24 25</t>
+          <t>01, 02, 04, 05, 06, 09, 11, 14, 15, 16, 17, 21, 22, 23, 25</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>01 03 04 05 07 08 10 12 13 18 19 20 23 24 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H123" t="n">
         <v>15</v>
       </c>
       <c r="I123" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -6470,11 +6470,11 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6484,22 +6484,22 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 09 11 12 13 14 15 21 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>01 03 04 05 07 08 10 12 13 18 19 20 23 24 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H124" t="n">
         <v>15</v>
       </c>
       <c r="I124" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -6519,11 +6519,11 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>03 05 06 09 10 11 12 13 14 15 20 22 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 14, 15, 20, 22, 23, 25</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>01 03 04 05 07 08 10 12 13 18 19 20 23 24 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -6568,11 +6568,11 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6582,31 +6582,31 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 09 10 11 12 13 14 15 20 24 25</t>
+          <t>01, 02, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 20, 24, 25</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>01 03 04 05 07 08 10 12 13 18 19 20 23 24 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H126" t="n">
         <v>15</v>
       </c>
       <c r="I126" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -6617,11 +6617,11 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6631,12 +6631,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 07 09 11 12 13 15 21 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 07, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>01 03 04 05 07 08 10 12 13 18 19 20 23 24 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -6666,11 +6666,11 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6680,31 +6680,31 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>01 03 04 07 09 10 11 12 13 14 19 20 22 24 25</t>
+          <t>01, 03, 04, 07, 09, 10, 11, 12, 13, 14, 19, 20, 22, 24, 25</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>01 03 04 05 07 08 10 12 13 18 19 20 23 24 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H128" t="n">
         <v>15</v>
       </c>
       <c r="I128" t="n">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>11 acertos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -6715,11 +6715,11 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6729,22 +6729,22 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 09 10 11 12 13 14 15 20 24 25</t>
+          <t>01, 03, 04, 05, 06, 10, 11, 12, 13, 14, 15, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>01 03 04 05 07 08 10 12 13 18 19 20 23 24 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H129" t="n">
         <v>15</v>
       </c>
       <c r="I129" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -6764,11 +6764,11 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6778,22 +6778,22 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 09 11 12 15 17 21 22 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 16, 17, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 07 08 09 10 12 13 14 15 19 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H130" t="n">
         <v>15</v>
       </c>
       <c r="I130" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -6813,11 +6813,11 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6827,22 +6827,22 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>02 06 07 08 09 10 11 14 15 16 17 19 20 21 22</t>
+          <t>01, 05, 06, 11, 12, 13, 15, 16, 17, 18, 20, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 07 08 09 10 12 13 14 15 19 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H131" t="n">
         <v>15</v>
       </c>
       <c r="I131" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -6862,11 +6862,11 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6876,31 +6876,31 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 09 11 12 13 15 19 21 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 07 08 09 10 12 13 14 15 19 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H132" t="n">
         <v>15</v>
       </c>
       <c r="I132" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -6911,11 +6911,11 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6925,22 +6925,22 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 08 10 11 12 14 15 20 22 23 25</t>
+          <t>01, 02, 05, 06, 09, 10, 11, 12, 13, 15, 20, 21, 22, 24, 25</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 07 08 09 10 12 13 14 15 19 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H133" t="n">
         <v>15</v>
       </c>
       <c r="I133" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -6960,11 +6960,11 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6974,31 +6974,31 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 09 10 11 12 13 14 15 20 24 25</t>
+          <t>01, 02, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 20, 24, 25</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 07 08 09 10 12 13 14 15 19 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H134" t="n">
         <v>15</v>
       </c>
       <c r="I134" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>11 acertos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -7009,11 +7009,11 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7023,31 +7023,31 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 07 11 12 13 15 19 21 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 07, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 07 08 09 10 12 13 14 15 19 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H135" t="n">
         <v>15</v>
       </c>
       <c r="I135" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -7058,11 +7058,11 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>01 03 04 07 09 10 11 12 13 14 19 20 22 24 25</t>
+          <t>01, 03, 04, 07, 09, 10, 11, 12, 13, 14, 19, 20, 22, 24, 25</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 07 08 09 10 12 13 14 15 19 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -7107,11 +7107,11 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7121,31 +7121,31 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 09 10 11 12 13 14 15 19 24 25</t>
+          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 21, 24, 25</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 07 08 09 10 12 13 14 15 19 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H137" t="n">
         <v>15</v>
       </c>
       <c r="I137" t="n">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>11 acertos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -7156,11 +7156,11 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 11 12 13 15 16 17 22 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 11, 12, 13, 14, 15, 16, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>03 04 07 08 09 11 12 13 15 17 19 20 21 23 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -7205,11 +7205,11 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7219,22 +7219,22 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>06 07 08 09 10 11 14 16 17 18 20 22 23 24 25</t>
+          <t>01, 02, 04, 05, 06, 10, 11, 12, 14, 15, 16, 18, 22, 23, 25</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>03 04 07 08 09 11 12 13 15 17 19 20 21 23 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H139" t="n">
         <v>15</v>
       </c>
       <c r="I139" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -7254,11 +7254,11 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 09 11 12 13 15 19 21 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>03 04 07 08 09 11 12 13 15 17 19 20 21 23 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>11 acertos</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -7303,11 +7303,11 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7317,22 +7317,22 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>01 02 05 06 09 10 11 12 13 15 20 21 22 24 25</t>
+          <t>01, 03, 06, 10, 12, 13, 14, 15, 16, 17, 18, 19, 20, 22, 24</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>03 04 07 08 09 11 12 13 15 17 19 20 21 23 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H141" t="n">
         <v>15</v>
       </c>
       <c r="I141" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -7352,11 +7352,11 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7366,31 +7366,31 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 09 10 11 12 13 14 15 20 24 25</t>
+          <t>01, 02, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 20, 24, 25</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>03 04 07 08 09 11 12 13 15 17 19 20 21 23 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H142" t="n">
         <v>15</v>
       </c>
       <c r="I142" t="n">
-        <v>60</v>
+        <v>73.3</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -7401,11 +7401,11 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7415,31 +7415,31 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 07 11 12 13 15 19 21 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 07, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>03 04 07 08 09 11 12 13 15 17 19 20 21 23 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H143" t="n">
         <v>15</v>
       </c>
       <c r="I143" t="n">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>11 acertos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -7450,11 +7450,11 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7464,22 +7464,22 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>01 03 04 07 09 10 11 12 13 14 19 20 22 24 25</t>
+          <t>01, 03, 04, 07, 09, 10, 11, 12, 13, 14, 19, 20, 22, 24, 25</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>03 04 07 08 09 11 12 13 15 17 19 20 21 23 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H144" t="n">
         <v>15</v>
       </c>
       <c r="I144" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -7499,11 +7499,11 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7513,31 +7513,31 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 09 10 11 12 13 15 20 22 24 25</t>
+          <t>01, 03, 04, 05, 06, 10, 11, 12, 13, 14, 15, 19, 20, 24, 25</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>03 04 07 08 09 11 12 13 15 17 19 20 21 23 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H145" t="n">
         <v>15</v>
       </c>
       <c r="I145" t="n">
-        <v>60</v>
+        <v>73.3</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -7548,11 +7548,11 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7562,22 +7562,22 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 11 12 13 14 15 16 22 23 24 25</t>
+          <t>01, 03, 04, 05, 07, 08, 11, 12, 13, 15, 16, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>02 03 05 06 09 10 11 12 14 15 19 20 21 23 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H146" t="n">
         <v>15</v>
       </c>
       <c r="I146" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -7597,11 +7597,11 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7611,22 +7611,22 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>01 02 05 06 07 08 10 14 16 18 19 20 21 22 25</t>
+          <t>01, 03, 04, 05, 07, 08, 11, 13, 15, 16, 17, 18, 22, 23, 25</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>02 03 05 06 09 10 11 12 14 15 19 20 21 23 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H147" t="n">
         <v>15</v>
       </c>
       <c r="I147" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -7646,11 +7646,11 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7660,31 +7660,31 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 09 11 12 13 15 19 21 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>02 03 05 06 09 10 11 12 14 15 19 20 21 23 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H148" t="n">
         <v>15</v>
       </c>
       <c r="I148" t="n">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>11 acertos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -7695,11 +7695,11 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>01 03 06 10 12 13 14 15 16 17 18 19 20 22 24</t>
+          <t>01, 04, 05, 07, 09, 10, 11, 12, 13, 15, 16, 18, 20, 22, 24</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>02 03 05 06 09 10 11 12 14 15 19 20 21 23 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -7744,11 +7744,11 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7758,31 +7758,31 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 09 10 11 12 13 14 15 20 24 25</t>
+          <t>01, 02, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 20, 24, 25</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>02 03 05 06 09 10 11 12 14 15 19 20 21 23 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H150" t="n">
         <v>15</v>
       </c>
       <c r="I150" t="n">
-        <v>73.3</v>
+        <v>46.7</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>11 acertos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -7793,11 +7793,11 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 07 11 12 13 15 19 21 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>02 03 05 06 09 10 11 12 14 15 19 20 21 23 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -7842,11 +7842,11 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>01 03 04 07 09 10 11 12 13 14 19 20 22 24 25</t>
+          <t>01, 03, 04, 07, 09, 10, 11, 12, 13, 14, 19, 20, 22, 24, 25</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>02 03 05 06 09 10 11 12 14 15 19 20 21 23 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -7891,11 +7891,11 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7905,31 +7905,31 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 10 11 12 13 14 15 19 20 24 25</t>
+          <t>01, 03, 04, 05, 07, 09, 10, 11, 12, 13, 15, 20, 22, 24, 25</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>02 03 05 06 09 10 11 12 14 15 19 20 21 23 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H153" t="n">
         <v>15</v>
       </c>
       <c r="I153" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>11 acertos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -7940,11 +7940,11 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7954,22 +7954,22 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>01 03 04 05 07 08 11 12 13 15 16 22 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 14, 15, 18, 19, 23, 24, 25</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>03 06 07 08 09 11 12 13 15 16 19 20 21 22 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H154" t="n">
         <v>15</v>
       </c>
       <c r="I154" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -7989,11 +7989,11 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -8003,22 +8003,22 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>01 03 04 07 08 11 13 15 16 17 18 22 23 24 25</t>
+          <t>01, 02, 03, 04, 05, 06, 10, 11, 14, 15, 17, 18, 19, 24, 25</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>03 06 07 08 09 11 12 13 15 16 19 20 21 22 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H155" t="n">
         <v>15</v>
       </c>
       <c r="I155" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -8038,11 +8038,11 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -8052,22 +8052,22 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 09 11 12 13 15 19 21 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>03 06 07 08 09 11 12 13 15 16 19 20 21 22 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H156" t="n">
         <v>15</v>
       </c>
       <c r="I156" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -8087,11 +8087,11 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>01 04 05 07 09 10 11 12 13 15 16 18 20 22 24</t>
+          <t>01, 03, 04, 06, 09, 10, 11, 12, 14, 15, 18, 19, 20, 24, 25</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>03 06 07 08 09 11 12 13 15 16 19 20 21 22 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -8136,11 +8136,11 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>01 02 03 04 05 09 10 11 12 13 14 15 20 24 25</t>
+          <t>01, 02, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 20, 24, 25</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>03 06 07 08 09 11 12 13 15 16 19 20 21 22 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -8185,11 +8185,11 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -8199,22 +8199,22 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>01 03 04 05 06 09 11 12 13 15 19 21 23 24 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>03 06 07 08 09 11 12 13 15 16 19 20 21 22 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G159" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H159" t="n">
         <v>15</v>
       </c>
       <c r="I159" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -8234,11 +8234,11 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>01 03 04 07 09 10 11 12 13 14 19 20 22 24 25</t>
+          <t>01, 03, 04, 07, 09, 10, 11, 12, 13, 14, 19, 20, 22, 24, 25</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>03 06 07 08 09 11 12 13 15 16 19 20 21 22 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H160" t="n">
         <v>15</v>
       </c>
       <c r="I160" t="n">
-        <v>60</v>
+        <v>46.7</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -8283,11 +8283,11 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8297,22 +8297,22 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>01 03 04 05 07 09 10 11 12 13 15 22 23 24 25</t>
+          <t>01, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 19, 20, 24, 25</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>03 06 07 08 09 11 12 13 15 16 19 20 21 22 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H161" t="n">
         <v>15</v>
       </c>
       <c r="I161" t="n">
-        <v>60</v>
+        <v>46.7</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -8332,11 +8332,11 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>7132</v>
+        <v>7133</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -8346,12 +8346,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>26 31 50 55 56</t>
+          <t>26, 29, 50, 55, 56</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>23 40 57 60 74</t>
+          <t>19, 31, 46, 49, 60</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -8381,11 +8381,11 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>7132</v>
+        <v>7133</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8395,22 +8395,22 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>31 45 50 55 56</t>
+          <t>31, 45, 50, 55, 56</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>23 40 57 60 74</t>
+          <t>19, 31, 46, 49, 60</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H163" t="n">
         <v>5</v>
       </c>
       <c r="I163" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -8430,11 +8430,11 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>7132</v>
+        <v>7133</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -8444,22 +8444,22 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>14 26 42 57 70</t>
+          <t>14, 26, 42, 57, 70</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>23 40 57 60 74</t>
+          <t>19, 31, 46, 49, 60</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H164" t="n">
         <v>5</v>
       </c>
       <c r="I164" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -8479,11 +8479,11 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>7132</v>
+        <v>7133</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8493,22 +8493,22 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>08 26 40 42 72</t>
+          <t>41, 42, 57, 61, 76</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>23 40 57 60 74</t>
+          <t>19, 31, 46, 49, 60</t>
         </is>
       </c>
       <c r="G165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H165" t="n">
         <v>5</v>
       </c>
       <c r="I165" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -8528,11 +8528,11 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>7132</v>
+        <v>7133</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8542,22 +8542,22 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>04 26 44 49 52</t>
+          <t>04, 26, 44, 49, 52</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>23 40 57 60 74</t>
+          <t>19, 31, 46, 49, 60</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H166" t="n">
         <v>5</v>
       </c>
       <c r="I166" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -8577,11 +8577,11 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>7132</v>
+        <v>7133</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8591,22 +8591,22 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>14 26 29 42 57</t>
+          <t>14, 26, 29, 42, 57</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>23 40 57 60 74</t>
+          <t>19, 31, 46, 49, 60</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
         <v>5</v>
       </c>
       <c r="I167" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -8626,11 +8626,11 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>7132</v>
+        <v>7133</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8640,22 +8640,22 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>04 16 31 52 56</t>
+          <t>04, 16, 31, 52, 56</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>23 40 57 60 74</t>
+          <t>19, 31, 46, 49, 60</t>
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H168" t="n">
         <v>5</v>
       </c>
       <c r="I168" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -8675,11 +8675,11 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>7132</v>
+        <v>7133</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -8689,12 +8689,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>04 26 31 42 56</t>
+          <t>04, 26, 42, 52, 57</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>23 40 57 60 74</t>
+          <t>19, 31, 46, 49, 60</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -8724,11 +8724,11 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>7133</v>
+        <v>7134</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>26 29 50 55 56</t>
+          <t>26, 29, 50, 55, 56</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>19 31 46 49 60</t>
+          <t>14, 15, 43, 54, 72</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -8773,11 +8773,11 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>7133</v>
+        <v>7134</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8787,22 +8787,22 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>31 45 50 55 56</t>
+          <t>06, 45, 50, 55, 56</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>19 31 46 49 60</t>
+          <t>14, 15, 43, 54, 72</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H171" t="n">
         <v>5</v>
       </c>
       <c r="I171" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -8822,11 +8822,11 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>7133</v>
+        <v>7134</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8836,22 +8836,22 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>14 26 42 57 70</t>
+          <t>14, 19, 26, 42, 57</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>19 31 46 49 60</t>
+          <t>14, 15, 43, 54, 72</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H172" t="n">
         <v>5</v>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -8871,11 +8871,11 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>7133</v>
+        <v>7134</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>41 42 57 61 76</t>
+          <t>04, 10, 23, 26, 37</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>19 31 46 49 60</t>
+          <t>14, 15, 43, 54, 72</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -8920,11 +8920,11 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>7133</v>
+        <v>7134</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8934,22 +8934,22 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>04 26 44 49 52</t>
+          <t>04, 26, 44, 49, 52</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>19 31 46 49 60</t>
+          <t>14, 15, 43, 54, 72</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H174" t="n">
         <v>5</v>
       </c>
       <c r="I174" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -8969,11 +8969,11 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>7133</v>
+        <v>7134</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8983,22 +8983,22 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>14 26 29 42 57</t>
+          <t>14, 26, 29, 42, 57</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>19 31 46 49 60</t>
+          <t>14, 15, 43, 54, 72</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H175" t="n">
         <v>5</v>
       </c>
       <c r="I175" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -9018,11 +9018,11 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>7133</v>
+        <v>7134</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -9032,22 +9032,22 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>04 16 31 52 56</t>
+          <t>04, 16, 31, 52, 56</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>19 31 46 49 60</t>
+          <t>14, 15, 43, 54, 72</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H176" t="n">
         <v>5</v>
       </c>
       <c r="I176" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -9067,11 +9067,11 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>7133</v>
+        <v>7134</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>04 26 42 56 57</t>
+          <t>04, 26, 29, 49, 52</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>19 31 46 49 60</t>
+          <t>14, 15, 43, 54, 72</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -9116,11 +9116,11 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -9130,12 +9130,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>26 29 50 55 56</t>
+          <t>26, 29, 50, 55, 56</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>14 15 43 54 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -9165,11 +9165,11 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -9179,22 +9179,22 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>06 45 50 55 56</t>
+          <t>06, 45, 50, 55, 56</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>14 15 43 54 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H179" t="n">
         <v>5</v>
       </c>
       <c r="I179" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -9214,11 +9214,11 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -9228,22 +9228,22 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>14 19 26 42 57</t>
+          <t>14, 26, 42, 54, 57</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>14 15 43 54 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H180" t="n">
         <v>5</v>
       </c>
       <c r="I180" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -9263,11 +9263,11 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>04 10 23 26 37</t>
+          <t>04, 10, 15, 37, 42</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>14 15 43 54 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -9312,11 +9312,11 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>04 26 44 49 52</t>
+          <t>04, 26, 44, 49, 52</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>14 15 43 54 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -9361,11 +9361,11 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -9375,22 +9375,22 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>14 26 29 42 57</t>
+          <t>14, 26, 29, 42, 57</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>14 15 43 54 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H183" t="n">
         <v>5</v>
       </c>
       <c r="I183" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -9410,11 +9410,11 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>04 16 31 52 56</t>
+          <t>04, 16, 31, 52, 56</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>14 15 43 54 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -9459,11 +9459,11 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -9473,22 +9473,22 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>04 14 26 29 56</t>
+          <t>04, 26, 29, 42, 52</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>14 15 43 54 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H185" t="n">
         <v>5</v>
       </c>
       <c r="I185" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -9508,11 +9508,11 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>26 29 50 55 56</t>
+          <t>26, 29, 50, 55, 56</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>01 06 18 43 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -9557,11 +9557,11 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9571,22 +9571,22 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>06 45 50 55 56</t>
+          <t>45, 50, 52, 55, 56</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>01 06 18 43 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H187" t="n">
         <v>5</v>
       </c>
       <c r="I187" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -9606,11 +9606,11 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9620,22 +9620,22 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>14 26 42 54 57</t>
+          <t>14, 26, 42, 54, 57</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>01 06 18 43 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H188" t="n">
         <v>5</v>
       </c>
       <c r="I188" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -9655,11 +9655,11 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>04 10 15 37 42</t>
+          <t>04, 06, 31, 37, 42</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>01 06 18 43 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -9704,11 +9704,11 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9718,12 +9718,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>04 26 44 49 52</t>
+          <t>04, 26, 44, 49, 52</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>01 06 18 43 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -9753,11 +9753,11 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9767,22 +9767,22 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>14 26 29 42 57</t>
+          <t>14, 26, 29, 42, 57</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>01 06 18 43 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H191" t="n">
         <v>5</v>
       </c>
       <c r="I191" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -9802,11 +9802,11 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>04 16 31 52 56</t>
+          <t>04, 16, 31, 52, 56</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>01 06 18 43 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -9851,11 +9851,11 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>04 14 26 42 56</t>
+          <t>04, 26, 29, 42, 52</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>01 06 18 43 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -9900,11 +9900,11 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -9914,22 +9914,22 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>26 29 50 55 56</t>
+          <t>14, 26, 50, 55, 56</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>13 14 30 53 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H194" t="n">
         <v>5</v>
       </c>
       <c r="I194" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -9949,11 +9949,11 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -9963,22 +9963,22 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>45 50 52 55 56</t>
+          <t>45, 50, 52, 55, 56</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>13 14 30 53 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H195" t="n">
         <v>5</v>
       </c>
       <c r="I195" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -9998,11 +9998,11 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>14 26 42 54 57</t>
+          <t>14, 26, 42, 54, 57</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>13 14 30 53 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H196" t="n">
         <v>5</v>
       </c>
       <c r="I196" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -10047,11 +10047,11 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -10061,12 +10061,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>04 06 31 37 42</t>
+          <t>04, 18, 30, 49, 53</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>13 14 30 53 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -10096,11 +10096,11 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>04 26 44 49 52</t>
+          <t>04, 26, 44, 49, 52</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>13 14 30 53 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -10145,11 +10145,11 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -10159,22 +10159,22 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>14 26 29 42 57</t>
+          <t>14, 26, 29, 42, 57</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>13 14 30 53 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H199" t="n">
         <v>5</v>
       </c>
       <c r="I199" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -10194,11 +10194,11 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>04 16 31 52 56</t>
+          <t>04, 16, 31, 52, 56</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>13 14 30 53 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -10243,11 +10243,11 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>04 26 42 52 56</t>
+          <t>04, 14, 26, 49, 52</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>13 14 30 53 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -10292,11 +10292,11 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>14 26 50 55 56</t>
+          <t>14, 26, 29, 55, 56</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>02 07 50 61 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -10341,11 +10341,11 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>45 50 52 55 56</t>
+          <t>26, 45, 52, 55, 56</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>02 07 50 61 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -10390,11 +10390,11 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -10404,22 +10404,22 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>14 26 42 54 57</t>
+          <t>02, 14, 26, 42, 57</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>02 07 50 61 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H204" t="n">
         <v>5</v>
       </c>
       <c r="I204" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -10439,11 +10439,11 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>04 18 30 49 53</t>
+          <t>04, 13, 18, 49, 53</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>02 07 50 61 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -10488,11 +10488,11 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -10502,22 +10502,22 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>04 26 44 49 52</t>
+          <t>04, 26, 44, 49, 52</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>02 07 50 61 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H206" t="n">
         <v>5</v>
       </c>
       <c r="I206" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -10537,11 +10537,11 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -10551,22 +10551,22 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>14 26 29 42 57</t>
+          <t>14, 26, 29, 42, 57</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>02 07 50 61 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H207" t="n">
         <v>5</v>
       </c>
       <c r="I207" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -10586,11 +10586,11 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -10600,31 +10600,31 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>04 16 31 52 56</t>
+          <t>04, 16, 31, 52, 56</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>02 07 50 61 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H208" t="n">
         <v>5</v>
       </c>
       <c r="I208" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Duque (2 acertos)</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -10635,11 +10635,11 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -10649,31 +10649,31 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>04 14 26 52 56</t>
+          <t>04, 14, 26, 49, 52</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>02 07 50 61 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H209" t="n">
         <v>5</v>
       </c>
       <c r="I209" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Duque (2 acertos)</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -10684,11 +10684,11 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -10698,22 +10698,22 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>14 26 29 55 56</t>
+          <t>14, 26, 29, 55, 56</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>14 16 27 34 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H210" t="n">
         <v>5</v>
       </c>
       <c r="I210" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -10733,11 +10733,11 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -10747,12 +10747,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>26 45 52 55 56</t>
+          <t>17, 26, 45, 55, 56</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>14 16 27 34 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -10782,11 +10782,11 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -10796,22 +10796,22 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>02 14 26 42 57</t>
+          <t>02, 14, 26, 42, 57</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>14 16 27 34 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H212" t="n">
         <v>5</v>
       </c>
       <c r="I212" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
@@ -10831,11 +10831,11 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -10845,12 +10845,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>04 13 18 49 53</t>
+          <t>04, 13, 31, 42, 49</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>14 16 27 34 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -10880,11 +10880,11 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -10894,22 +10894,22 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>04 26 44 49 52</t>
+          <t>04, 26, 44, 49, 52</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>14 16 27 34 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H214" t="n">
         <v>5</v>
       </c>
       <c r="I214" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
@@ -10929,11 +10929,11 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -10943,22 +10943,22 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>14 26 29 42 57</t>
+          <t>14, 26, 29, 42, 57</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>14 16 27 34 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H215" t="n">
         <v>5</v>
       </c>
       <c r="I215" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -10978,11 +10978,11 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -10992,31 +10992,31 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>04 16 31 52 56</t>
+          <t>04, 16, 31, 52, 56</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>14 16 27 34 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H216" t="n">
         <v>5</v>
       </c>
       <c r="I216" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Duque (2 acertos)</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -11027,11 +11027,11 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -11041,31 +11041,31 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>04 14 26 52 56</t>
+          <t>04, 26, 42, 49, 52</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>14 16 27 34 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G217" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H217" t="n">
         <v>5</v>
       </c>
       <c r="I217" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Duque (2 acertos)</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -11076,11 +11076,11 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>14 26 29 55 56</t>
+          <t>14, 26, 29, 55, 56</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>11 17 40 62 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -11125,11 +11125,11 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>17 26 45 55 56</t>
+          <t>26, 45, 55, 56, 65</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>11 17 40 62 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -11174,11 +11174,11 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -11188,22 +11188,22 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>02 14 26 42 57</t>
+          <t>02, 14, 26, 42, 57</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>11 17 40 62 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H220" t="n">
         <v>5</v>
       </c>
       <c r="I220" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -11223,11 +11223,11 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>04 13 31 42 49</t>
+          <t>04, 49, 50, 52, 61</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>11 17 40 62 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -11272,11 +11272,11 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -11286,12 +11286,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>04 26 44 49 52</t>
+          <t>04, 26, 44, 49, 52</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>11 17 40 62 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -11321,11 +11321,11 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -11335,22 +11335,22 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>14 26 29 42 57</t>
+          <t>14, 26, 29, 42, 57</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>11 17 40 62 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H223" t="n">
         <v>5</v>
       </c>
       <c r="I223" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -11370,11 +11370,11 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>04 16 31 52 56</t>
+          <t>04, 16, 31, 52, 56</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>11 17 40 62 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -11419,11 +11419,11 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>04 14 26 42 56</t>
+          <t>04, 14, 26, 49, 52</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>11 17 40 62 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -11468,11 +11468,11 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -11482,22 +11482,22 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>14 26 29 55 56</t>
+          <t>14, 26, 29, 55, 56</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>05 28 45 57 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H226" t="n">
         <v>5</v>
       </c>
       <c r="I226" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
@@ -11517,11 +11517,11 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>26 45 55 56 65</t>
+          <t>26, 55, 56, 65, 75</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>05 28 45 57 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -11566,11 +11566,11 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -11580,22 +11580,22 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>02 14 26 42 57</t>
+          <t>02, 14, 26, 42, 57</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>05 28 45 57 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H228" t="n">
         <v>5</v>
       </c>
       <c r="I228" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
@@ -11615,11 +11615,11 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -11629,12 +11629,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>04 49 50 52 61</t>
+          <t>05, 13, 28, 52, 57</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>05 28 45 57 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -11664,11 +11664,11 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -11678,12 +11678,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>04 26 44 49 52</t>
+          <t>04, 26, 44, 49, 52</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>05 28 45 57 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -11713,11 +11713,11 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -11727,22 +11727,22 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>14 26 29 42 57</t>
+          <t>14, 26, 29, 42, 57</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>05 28 45 57 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H231" t="n">
         <v>5</v>
       </c>
       <c r="I231" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -11762,11 +11762,11 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11776,22 +11776,22 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>04 16 31 52 56</t>
+          <t>04, 16, 31, 52, 56</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>05 28 45 57 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H232" t="n">
         <v>5</v>
       </c>
       <c r="I232" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -11811,11 +11811,11 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11825,12 +11825,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>04 14 26 52 56</t>
+          <t>04, 14, 26, 52, 57</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>05 28 45 57 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -11860,11 +11860,11 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11874,22 +11874,22 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>14 26 29 55 56</t>
+          <t>14, 25, 26, 29, 55</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>01 18 19 33 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H234" t="n">
         <v>5</v>
       </c>
       <c r="I234" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -11909,11 +11909,11 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11923,22 +11923,22 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>26 55 56 65 75</t>
+          <t>26, 29, 55, 65, 75</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>01 18 19 33 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H235" t="n">
         <v>5</v>
       </c>
       <c r="I235" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -11958,11 +11958,11 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11972,12 +11972,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>02 14 26 42 57</t>
+          <t>14, 19, 42, 56, 57</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>01 18 19 33 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -12007,11 +12007,11 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -12021,12 +12021,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>05 13 28 52 57</t>
+          <t>04, 37, 45, 49, 52</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>01 18 19 33 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -12056,11 +12056,11 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -12070,12 +12070,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>04 26 44 49 52</t>
+          <t>04, 26, 44, 49, 52</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>01 18 19 33 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -12105,11 +12105,11 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -12119,12 +12119,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>14 26 29 42 57</t>
+          <t>14, 26, 42, 56, 57</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>01 18 19 33 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -12154,11 +12154,11 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -12168,22 +12168,22 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>04 16 31 52 56</t>
+          <t>04, 16, 31, 52, 56</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>01 18 19 33 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H240" t="n">
         <v>5</v>
       </c>
       <c r="I240" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
@@ -12203,11 +12203,11 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -12217,22 +12217,22 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>14 26 52 56 57</t>
+          <t>04, 26, 49, 52, 56</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>01 18 19 33 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H241" t="n">
         <v>5</v>
       </c>
       <c r="I241" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>

--- a/excel/historico_acertos_modelos.xlsx
+++ b/excel/historico_acertos_modelos.xlsx
@@ -4412,11 +4412,11 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4426,22 +4426,22 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 09, 11, 12, 15, 16, 21, 22, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 09, 11, 15, 16, 17, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 13, 14, 18, 19, 22, 24</t>
+          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H82" t="n">
         <v>15</v>
       </c>
       <c r="I82" t="n">
-        <v>53.3</v>
+        <v>66.7</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -4461,11 +4461,11 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4475,22 +4475,22 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>01, 02, 03, 05, 07, 09, 11, 14, 15, 16, 17, 20, 22, 24, 25</t>
+          <t>01, 02, 04, 05, 07, 09, 11, 15, 16, 17, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 13, 14, 18, 19, 22, 24</t>
+          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H83" t="n">
         <v>15</v>
       </c>
       <c r="I83" t="n">
-        <v>46.7</v>
+        <v>66.7</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -4510,11 +4510,11 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 13, 14, 18, 19, 22, 24</t>
+          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -4559,11 +4559,11 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>03, 05, 07, 08, 09, 11, 12, 13, 14, 18, 19, 20, 22, 24, 25</t>
+          <t>01, 03, 04, 05, 07, 08, 09, 10, 11, 12, 13, 16, 18, 20, 24</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 13, 14, 18, 19, 22, 24</t>
+          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -4608,11 +4608,11 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4627,26 +4627,26 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 13, 14, 18, 19, 22, 24</t>
+          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H86" t="n">
         <v>15</v>
       </c>
       <c r="I86" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -4657,11 +4657,11 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4671,22 +4671,22 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 07, 09, 11, 12, 13, 15, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 14, 15, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 13, 14, 18, 19, 22, 24</t>
+          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H87" t="n">
         <v>15</v>
       </c>
       <c r="I87" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -4706,11 +4706,11 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4725,26 +4725,26 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 13, 14, 18, 19, 22, 24</t>
+          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H88" t="n">
         <v>15</v>
       </c>
       <c r="I88" t="n">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -4755,11 +4755,11 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4769,31 +4769,31 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 09, 11, 12, 13, 14, 15, 20, 22, 24, 25</t>
+          <t>01, 03, 04, 05, 07, 09, 10, 11, 12, 13, 14, 15, 20, 24, 25</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 13, 14, 18, 19, 22, 24</t>
+          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H89" t="n">
         <v>15</v>
       </c>
       <c r="I89" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -4804,11 +4804,11 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4818,22 +4818,22 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 09, 11, 15, 16, 17, 21, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 06, 11, 12, 13, 14, 15, 17, 23, 24, 25</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H90" t="n">
         <v>15</v>
       </c>
       <c r="I90" t="n">
-        <v>66.7</v>
+        <v>46.7</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -4853,11 +4853,11 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4867,22 +4867,22 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 07, 09, 11, 15, 16, 17, 20, 21, 23, 24, 25</t>
+          <t>01, 02, 03, 05, 08, 11, 13, 14, 15, 17, 18, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H91" t="n">
         <v>15</v>
       </c>
       <c r="I91" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -4902,11 +4902,11 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4921,17 +4921,17 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H92" t="n">
         <v>15</v>
       </c>
       <c r="I92" t="n">
-        <v>66.7</v>
+        <v>46.7</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -4951,11 +4951,11 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4965,31 +4965,31 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 09, 10, 11, 12, 13, 16, 18, 20, 24</t>
+          <t>01, 03, 05, 06, 10, 11, 12, 13, 14, 18, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H93" t="n">
         <v>15</v>
       </c>
       <c r="I93" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -5000,11 +5000,11 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H94" t="n">
         <v>15</v>
       </c>
       <c r="I94" t="n">
-        <v>60</v>
+        <v>46.7</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -5049,11 +5049,11 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5063,22 +5063,22 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 14, 15, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 07, 09, 11, 12, 13, 15, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H95" t="n">
         <v>15</v>
       </c>
       <c r="I95" t="n">
-        <v>66.7</v>
+        <v>46.7</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -5098,11 +5098,11 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5117,17 +5117,17 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H96" t="n">
         <v>15</v>
       </c>
       <c r="I96" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -5147,11 +5147,11 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5161,31 +5161,31 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 09, 10, 11, 12, 13, 14, 15, 20, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 10, 11, 12, 13, 14, 15, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H97" t="n">
         <v>15</v>
       </c>
       <c r="I97" t="n">
-        <v>73.3</v>
+        <v>53.3</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -5196,11 +5196,11 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5210,22 +5210,22 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 06, 11, 12, 13, 14, 15, 17, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 17, 21, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H98" t="n">
         <v>15</v>
       </c>
       <c r="I98" t="n">
-        <v>46.7</v>
+        <v>40</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -5245,11 +5245,11 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5259,22 +5259,22 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>01, 02, 03, 05, 08, 11, 13, 14, 15, 17, 18, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 17, 21, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H99" t="n">
         <v>15</v>
       </c>
       <c r="I99" t="n">
-        <v>53.3</v>
+        <v>40</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -5294,11 +5294,11 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5313,17 +5313,17 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H100" t="n">
         <v>15</v>
       </c>
       <c r="I100" t="n">
-        <v>46.7</v>
+        <v>53.3</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -5343,11 +5343,11 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5357,22 +5357,22 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>01, 03, 05, 06, 10, 11, 12, 13, 14, 18, 20, 21, 23, 24, 25</t>
+          <t>03, 04, 05, 06, 10, 11, 12, 13, 15, 18, 20, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H101" t="n">
         <v>15</v>
       </c>
       <c r="I101" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -5392,11 +5392,11 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 10, 11, 12, 13, 14, 15, 20, 22, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 20, 24, 25</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H102" t="n">
         <v>15</v>
       </c>
       <c r="I102" t="n">
-        <v>46.7</v>
+        <v>60</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -5441,11 +5441,11 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5460,17 +5460,17 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H103" t="n">
         <v>15</v>
       </c>
       <c r="I103" t="n">
-        <v>46.7</v>
+        <v>53.3</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -5490,11 +5490,11 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -5539,11 +5539,11 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5553,22 +5553,22 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 10, 11, 12, 13, 14, 15, 20, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H105" t="n">
         <v>15</v>
       </c>
       <c r="I105" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -5588,11 +5588,11 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5607,17 +5607,17 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H106" t="n">
         <v>15</v>
       </c>
       <c r="I106" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -5637,11 +5637,11 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5651,22 +5651,22 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 17, 21, 22, 23, 24, 25</t>
+          <t>01, 03, 05, 06, 11, 12, 13, 15, 16, 17, 21, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H107" t="n">
         <v>15</v>
       </c>
       <c r="I107" t="n">
-        <v>40</v>
+        <v>53.3</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -5686,11 +5686,11 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5705,17 +5705,17 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H108" t="n">
         <v>15</v>
       </c>
       <c r="I108" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -5735,11 +5735,11 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5749,22 +5749,22 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 10, 11, 12, 13, 15, 18, 20, 22, 23, 24, 25</t>
+          <t>03, 05, 06, 09, 10, 11, 12, 13, 14, 15, 20, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H109" t="n">
         <v>15</v>
       </c>
       <c r="I109" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -5784,11 +5784,11 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5803,17 +5803,17 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H110" t="n">
         <v>15</v>
       </c>
       <c r="I110" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -5833,11 +5833,11 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5852,17 +5852,17 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H111" t="n">
         <v>15</v>
       </c>
       <c r="I111" t="n">
-        <v>53.3</v>
+        <v>66.7</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -5882,11 +5882,11 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5901,26 +5901,26 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H112" t="n">
         <v>15</v>
       </c>
       <c r="I112" t="n">
-        <v>60</v>
+        <v>73.3</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -5931,11 +5931,11 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5945,31 +5945,31 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H113" t="n">
         <v>15</v>
       </c>
       <c r="I113" t="n">
-        <v>60</v>
+        <v>73.3</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -5980,11 +5980,11 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5994,22 +5994,22 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 17, 21, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 15, 17, 21, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H114" t="n">
         <v>15</v>
       </c>
       <c r="I114" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -6029,11 +6029,11 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>01, 03, 05, 06, 11, 12, 13, 15, 16, 17, 21, 22, 23, 24, 25</t>
+          <t>01, 02, 04, 05, 06, 09, 11, 14, 15, 16, 17, 21, 22, 23, 25</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -6078,11 +6078,11 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6092,22 +6092,22 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 14, 15, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H116" t="n">
         <v>15</v>
       </c>
       <c r="I116" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -6127,11 +6127,11 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6141,12 +6141,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>03, 05, 06, 09, 10, 11, 12, 13, 14, 15, 20, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 14, 15, 20, 22, 23, 25</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -6176,11 +6176,11 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6195,26 +6195,26 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H118" t="n">
         <v>15</v>
       </c>
       <c r="I118" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -6225,11 +6225,11 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 07, 09, 11, 12, 13, 15, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 07, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -6274,11 +6274,11 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6293,26 +6293,26 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H120" t="n">
         <v>15</v>
       </c>
       <c r="I120" t="n">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -6323,11 +6323,11 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6337,31 +6337,31 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 20, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 10, 11, 12, 13, 14, 15, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H121" t="n">
         <v>15</v>
       </c>
       <c r="I121" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -6372,11 +6372,11 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6386,22 +6386,22 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 11, 12, 15, 17, 21, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 16, 17, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H122" t="n">
         <v>15</v>
       </c>
       <c r="I122" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -6421,11 +6421,11 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 09, 11, 14, 15, 16, 17, 21, 22, 23, 25</t>
+          <t>01, 05, 06, 11, 12, 13, 15, 16, 17, 18, 20, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -6470,11 +6470,11 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6489,26 +6489,26 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H124" t="n">
         <v>15</v>
       </c>
       <c r="I124" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -6519,11 +6519,11 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6533,22 +6533,22 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 14, 15, 20, 22, 23, 25</t>
+          <t>01, 02, 05, 06, 09, 10, 11, 12, 13, 15, 20, 21, 22, 24, 25</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H125" t="n">
         <v>15</v>
       </c>
       <c r="I125" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -6568,11 +6568,11 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6587,26 +6587,26 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H126" t="n">
         <v>15</v>
       </c>
       <c r="I126" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -6617,11 +6617,11 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6636,26 +6636,26 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H127" t="n">
         <v>15</v>
       </c>
       <c r="I127" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -6666,11 +6666,11 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -6715,11 +6715,11 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6729,22 +6729,22 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 10, 11, 12, 13, 14, 15, 20, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 21, 24, 25</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H129" t="n">
         <v>15</v>
       </c>
       <c r="I129" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -6764,11 +6764,11 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 16, 17, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 11, 12, 13, 14, 15, 16, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -6813,11 +6813,11 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6827,22 +6827,22 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>01, 05, 06, 11, 12, 13, 15, 16, 17, 18, 20, 22, 23, 24, 25</t>
+          <t>01, 02, 04, 05, 06, 10, 11, 12, 14, 15, 16, 18, 22, 23, 25</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H131" t="n">
         <v>15</v>
       </c>
       <c r="I131" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -6862,11 +6862,11 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -6911,11 +6911,11 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6925,22 +6925,22 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>01, 02, 05, 06, 09, 10, 11, 12, 13, 15, 20, 21, 22, 24, 25</t>
+          <t>01, 03, 06, 10, 12, 13, 14, 15, 16, 17, 18, 19, 20, 22, 24</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H133" t="n">
         <v>15</v>
       </c>
       <c r="I133" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -6960,11 +6960,11 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6979,26 +6979,26 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H134" t="n">
         <v>15</v>
       </c>
       <c r="I134" t="n">
-        <v>60</v>
+        <v>73.3</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -7009,11 +7009,11 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7028,26 +7028,26 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H135" t="n">
         <v>15</v>
       </c>
       <c r="I135" t="n">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -7058,11 +7058,11 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7077,17 +7077,17 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H136" t="n">
         <v>15</v>
       </c>
       <c r="I136" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -7107,11 +7107,11 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7121,31 +7121,31 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 21, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 10, 11, 12, 13, 14, 15, 19, 20, 24, 25</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H137" t="n">
         <v>15</v>
       </c>
       <c r="I137" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -7156,11 +7156,11 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7170,22 +7170,22 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 11, 12, 13, 14, 15, 16, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 07, 08, 11, 12, 13, 15, 16, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H138" t="n">
         <v>15</v>
       </c>
       <c r="I138" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -7205,11 +7205,11 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 10, 11, 12, 14, 15, 16, 18, 22, 23, 25</t>
+          <t>01, 03, 04, 05, 07, 08, 11, 13, 15, 16, 17, 18, 22, 23, 25</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -7254,11 +7254,11 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7273,26 +7273,26 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H140" t="n">
         <v>15</v>
       </c>
       <c r="I140" t="n">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -7303,11 +7303,11 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7317,12 +7317,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>01, 03, 06, 10, 12, 13, 14, 15, 16, 17, 18, 19, 20, 22, 24</t>
+          <t>01, 04, 05, 07, 09, 10, 11, 12, 13, 15, 16, 18, 20, 22, 24</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -7352,11 +7352,11 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7371,26 +7371,26 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H142" t="n">
         <v>15</v>
       </c>
       <c r="I142" t="n">
-        <v>73.3</v>
+        <v>46.7</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -7401,11 +7401,11 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 07, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -7450,11 +7450,11 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -7499,11 +7499,11 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7513,31 +7513,31 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 10, 11, 12, 13, 14, 15, 19, 20, 24, 25</t>
+          <t>01, 03, 04, 05, 07, 09, 10, 11, 12, 13, 15, 20, 22, 24, 25</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H145" t="n">
         <v>15</v>
       </c>
       <c r="I145" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -7548,11 +7548,11 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7562,22 +7562,22 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 11, 12, 13, 15, 16, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 14, 15, 18, 19, 23, 24, 25</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H146" t="n">
         <v>15</v>
       </c>
       <c r="I146" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -7597,11 +7597,11 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7611,22 +7611,22 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 11, 13, 15, 16, 17, 18, 22, 23, 25</t>
+          <t>01, 02, 03, 04, 05, 06, 10, 11, 14, 15, 17, 18, 19, 24, 25</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H147" t="n">
         <v>15</v>
       </c>
       <c r="I147" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -7646,11 +7646,11 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H148" t="n">
         <v>15</v>
       </c>
       <c r="I148" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -7695,11 +7695,11 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>01, 04, 05, 07, 09, 10, 11, 12, 13, 15, 16, 18, 20, 22, 24</t>
+          <t>01, 03, 04, 06, 09, 10, 11, 12, 14, 15, 18, 19, 20, 24, 25</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -7744,11 +7744,11 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -7793,11 +7793,11 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7812,17 +7812,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H151" t="n">
         <v>15</v>
       </c>
       <c r="I151" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -7842,11 +7842,11 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7861,17 +7861,17 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G152" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H152" t="n">
         <v>15</v>
       </c>
       <c r="I152" t="n">
-        <v>60</v>
+        <v>46.7</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -7891,11 +7891,11 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7905,22 +7905,22 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 09, 10, 11, 12, 13, 15, 20, 22, 24, 25</t>
+          <t>01, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 19, 20, 24, 25</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H153" t="n">
         <v>15</v>
       </c>
       <c r="I153" t="n">
-        <v>60</v>
+        <v>46.7</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -7940,11 +7940,11 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7954,22 +7954,22 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 11, 12, 14, 15, 18, 19, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H154" t="n">
         <v>15</v>
       </c>
       <c r="I154" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -7989,11 +7989,11 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 06, 10, 11, 14, 15, 17, 18, 19, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 22, 23, 25</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -8038,11 +8038,11 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -8052,22 +8052,22 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 08, 09, 11, 12, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H156" t="n">
         <v>15</v>
       </c>
       <c r="I156" t="n">
-        <v>53.3</v>
+        <v>66.7</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -8087,11 +8087,11 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -8101,22 +8101,22 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>01, 03, 04, 06, 09, 10, 11, 12, 14, 15, 18, 19, 20, 24, 25</t>
+          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 13, 17, 18, 20, 21, 25</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G157" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H157" t="n">
         <v>15</v>
       </c>
       <c r="I157" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -8136,11 +8136,11 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -8155,17 +8155,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H158" t="n">
         <v>15</v>
       </c>
       <c r="I158" t="n">
-        <v>46.7</v>
+        <v>60</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -8185,11 +8185,11 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -8199,31 +8199,31 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 07, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G159" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H159" t="n">
         <v>15</v>
       </c>
       <c r="I159" t="n">
-        <v>53.3</v>
+        <v>73.3</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -8234,11 +8234,11 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -8253,17 +8253,17 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H160" t="n">
         <v>15</v>
       </c>
       <c r="I160" t="n">
-        <v>46.7</v>
+        <v>66.7</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -8283,11 +8283,11 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8297,22 +8297,22 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 19, 20, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 07, 09, 10, 11, 12, 13, 15, 20, 24, 25</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H161" t="n">
         <v>15</v>
       </c>
       <c r="I161" t="n">
-        <v>46.7</v>
+        <v>66.7</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -8332,11 +8332,11 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>7133</v>
+        <v>7134</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>19, 31, 46, 49, 60</t>
+          <t>14, 15, 43, 54, 72</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -8381,11 +8381,11 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>7133</v>
+        <v>7134</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8395,22 +8395,22 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>31, 45, 50, 55, 56</t>
+          <t>06, 45, 50, 55, 56</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>19, 31, 46, 49, 60</t>
+          <t>14, 15, 43, 54, 72</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
         <v>5</v>
       </c>
       <c r="I163" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -8430,11 +8430,11 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>7133</v>
+        <v>7134</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -8444,22 +8444,22 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>14, 26, 42, 57, 70</t>
+          <t>14, 19, 26, 42, 57</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>19, 31, 46, 49, 60</t>
+          <t>14, 15, 43, 54, 72</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H164" t="n">
         <v>5</v>
       </c>
       <c r="I164" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -8479,11 +8479,11 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>7133</v>
+        <v>7134</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>41, 42, 57, 61, 76</t>
+          <t>04, 10, 23, 26, 37</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>19, 31, 46, 49, 60</t>
+          <t>14, 15, 43, 54, 72</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -8528,11 +8528,11 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>7133</v>
+        <v>7134</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8547,17 +8547,17 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>19, 31, 46, 49, 60</t>
+          <t>14, 15, 43, 54, 72</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H166" t="n">
         <v>5</v>
       </c>
       <c r="I166" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -8577,11 +8577,11 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>7133</v>
+        <v>7134</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8596,17 +8596,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>19, 31, 46, 49, 60</t>
+          <t>14, 15, 43, 54, 72</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H167" t="n">
         <v>5</v>
       </c>
       <c r="I167" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -8626,11 +8626,11 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>7133</v>
+        <v>7134</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8645,17 +8645,17 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>19, 31, 46, 49, 60</t>
+          <t>14, 15, 43, 54, 72</t>
         </is>
       </c>
       <c r="G168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H168" t="n">
         <v>5</v>
       </c>
       <c r="I168" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -8675,11 +8675,11 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>7133</v>
+        <v>7134</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -8689,12 +8689,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>04, 26, 42, 52, 57</t>
+          <t>04, 26, 29, 49, 52</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>19, 31, 46, 49, 60</t>
+          <t>14, 15, 43, 54, 72</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -8724,11 +8724,11 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>14, 15, 43, 54, 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -8773,11 +8773,11 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8792,17 +8792,17 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>14, 15, 43, 54, 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H171" t="n">
         <v>5</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -8822,11 +8822,11 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8836,22 +8836,22 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>14, 19, 26, 42, 57</t>
+          <t>14, 26, 42, 54, 57</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>14, 15, 43, 54, 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H172" t="n">
         <v>5</v>
       </c>
       <c r="I172" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -8871,11 +8871,11 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>04, 10, 23, 26, 37</t>
+          <t>04, 10, 15, 37, 42</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>14, 15, 43, 54, 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -8920,11 +8920,11 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>14, 15, 43, 54, 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -8969,11 +8969,11 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8988,17 +8988,17 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>14, 15, 43, 54, 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H175" t="n">
         <v>5</v>
       </c>
       <c r="I175" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -9018,11 +9018,11 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>14, 15, 43, 54, 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -9067,11 +9067,11 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>04, 26, 29, 49, 52</t>
+          <t>04, 26, 29, 42, 52</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>14, 15, 43, 54, 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -9116,11 +9116,11 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -9165,11 +9165,11 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -9179,22 +9179,22 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>06, 45, 50, 55, 56</t>
+          <t>45, 50, 52, 55, 56</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H179" t="n">
         <v>5</v>
       </c>
       <c r="I179" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -9214,11 +9214,11 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -9233,17 +9233,17 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H180" t="n">
         <v>5</v>
       </c>
       <c r="I180" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -9263,11 +9263,11 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>04, 10, 15, 37, 42</t>
+          <t>04, 06, 31, 37, 42</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -9312,11 +9312,11 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -9361,11 +9361,11 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -9380,17 +9380,17 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H183" t="n">
         <v>5</v>
       </c>
       <c r="I183" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -9410,11 +9410,11 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -9459,11 +9459,11 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -9508,11 +9508,11 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -9522,22 +9522,22 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>26, 29, 50, 55, 56</t>
+          <t>14, 26, 50, 55, 56</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H186" t="n">
         <v>5</v>
       </c>
       <c r="I186" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -9557,11 +9557,11 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9576,17 +9576,17 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H187" t="n">
         <v>5</v>
       </c>
       <c r="I187" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -9606,11 +9606,11 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9625,17 +9625,17 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H188" t="n">
         <v>5</v>
       </c>
       <c r="I188" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -9655,11 +9655,11 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>04, 06, 31, 37, 42</t>
+          <t>04, 18, 30, 49, 53</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -9704,11 +9704,11 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9723,7 +9723,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -9753,11 +9753,11 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9772,17 +9772,17 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H191" t="n">
         <v>5</v>
       </c>
       <c r="I191" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -9802,11 +9802,11 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -9851,11 +9851,11 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>04, 26, 29, 42, 52</t>
+          <t>04, 14, 26, 49, 52</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -9900,11 +9900,11 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>14, 26, 50, 55, 56</t>
+          <t>14, 26, 29, 55, 56</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -9949,11 +9949,11 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>45, 50, 52, 55, 56</t>
+          <t>26, 45, 52, 55, 56</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -9998,11 +9998,11 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>14, 26, 42, 54, 57</t>
+          <t>02, 14, 26, 42, 57</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H196" t="n">
         <v>5</v>
       </c>
       <c r="I196" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -10047,11 +10047,11 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -10061,12 +10061,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>04, 18, 30, 49, 53</t>
+          <t>04, 13, 18, 49, 53</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -10096,11 +10096,11 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -10115,17 +10115,17 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H198" t="n">
         <v>5</v>
       </c>
       <c r="I198" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -10145,11 +10145,11 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -10164,17 +10164,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H199" t="n">
         <v>5</v>
       </c>
       <c r="I199" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -10194,11 +10194,11 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -10213,26 +10213,26 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H200" t="n">
         <v>5</v>
       </c>
       <c r="I200" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Duque (2 acertos)</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -10243,11 +10243,11 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -10262,26 +10262,26 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H201" t="n">
         <v>5</v>
       </c>
       <c r="I201" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Duque (2 acertos)</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -10292,11 +10292,11 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -10311,17 +10311,17 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H202" t="n">
         <v>5</v>
       </c>
       <c r="I202" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -10341,11 +10341,11 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>26, 45, 52, 55, 56</t>
+          <t>17, 26, 45, 55, 56</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -10390,11 +10390,11 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -10409,17 +10409,17 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H204" t="n">
         <v>5</v>
       </c>
       <c r="I204" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -10439,11 +10439,11 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>04, 13, 18, 49, 53</t>
+          <t>04, 13, 31, 42, 49</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -10488,11 +10488,11 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -10507,17 +10507,17 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H206" t="n">
         <v>5</v>
       </c>
       <c r="I206" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -10537,11 +10537,11 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -10556,17 +10556,17 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H207" t="n">
         <v>5</v>
       </c>
       <c r="I207" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -10586,11 +10586,11 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -10605,26 +10605,26 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H208" t="n">
         <v>5</v>
       </c>
       <c r="I208" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Duque (2 acertos)</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -10635,11 +10635,11 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -10649,31 +10649,31 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>04, 14, 26, 49, 52</t>
+          <t>04, 26, 42, 49, 52</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H209" t="n">
         <v>5</v>
       </c>
       <c r="I209" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Duque (2 acertos)</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -10684,11 +10684,11 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -10733,11 +10733,11 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -10747,12 +10747,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>17, 26, 45, 55, 56</t>
+          <t>26, 45, 55, 56, 65</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -10782,11 +10782,11 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -10801,17 +10801,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H212" t="n">
         <v>5</v>
       </c>
       <c r="I212" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
@@ -10831,11 +10831,11 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -10845,12 +10845,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>04, 13, 31, 42, 49</t>
+          <t>04, 49, 50, 52, 61</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -10880,11 +10880,11 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -10929,11 +10929,11 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -10948,17 +10948,17 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H215" t="n">
         <v>5</v>
       </c>
       <c r="I215" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -10978,11 +10978,11 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -11027,11 +11027,11 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>04, 26, 42, 49, 52</t>
+          <t>04, 14, 26, 49, 52</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -11076,11 +11076,11 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -11095,17 +11095,17 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H218" t="n">
         <v>5</v>
       </c>
       <c r="I218" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -11125,11 +11125,11 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>26, 45, 55, 56, 65</t>
+          <t>26, 55, 56, 65, 75</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -11174,11 +11174,11 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -11193,17 +11193,17 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H220" t="n">
         <v>5</v>
       </c>
       <c r="I220" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -11223,11 +11223,11 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>04, 49, 50, 52, 61</t>
+          <t>05, 13, 28, 52, 57</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -11272,11 +11272,11 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -11321,11 +11321,11 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -11340,17 +11340,17 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H223" t="n">
         <v>5</v>
       </c>
       <c r="I223" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -11370,11 +11370,11 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -11389,17 +11389,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H224" t="n">
         <v>5</v>
       </c>
       <c r="I224" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -11419,11 +11419,11 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>04, 14, 26, 49, 52</t>
+          <t>04, 14, 26, 52, 57</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -11468,11 +11468,11 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -11482,22 +11482,22 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>14, 26, 29, 55, 56</t>
+          <t>14, 25, 26, 29, 55</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H226" t="n">
         <v>5</v>
       </c>
       <c r="I226" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
@@ -11517,11 +11517,11 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -11531,22 +11531,22 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>26, 55, 56, 65, 75</t>
+          <t>26, 29, 55, 65, 75</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H227" t="n">
         <v>5</v>
       </c>
       <c r="I227" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -11566,11 +11566,11 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>02, 14, 26, 42, 57</t>
+          <t>14, 19, 42, 56, 57</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -11615,11 +11615,11 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -11629,12 +11629,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>05, 13, 28, 52, 57</t>
+          <t>04, 37, 45, 49, 52</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -11664,11 +11664,11 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -11713,11 +11713,11 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>14, 26, 29, 42, 57</t>
+          <t>14, 26, 42, 56, 57</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -11762,11 +11762,11 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11781,17 +11781,17 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H232" t="n">
         <v>5</v>
       </c>
       <c r="I232" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -11811,11 +11811,11 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11825,12 +11825,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>04, 14, 26, 52, 57</t>
+          <t>04, 26, 49, 52, 56</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -11860,11 +11860,11 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -11909,11 +11909,11 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -11958,11 +11958,11 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11972,12 +11972,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>14, 19, 42, 56, 57</t>
+          <t>14, 19, 34, 42, 57</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -12007,11 +12007,11 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -12021,12 +12021,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>04, 37, 45, 49, 52</t>
+          <t>04, 18, 49, 56, 58</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -12056,11 +12056,11 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -12105,11 +12105,11 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -12154,11 +12154,11 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -12173,17 +12173,17 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H240" t="n">
         <v>5</v>
       </c>
       <c r="I240" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
@@ -12203,11 +12203,11 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G241" t="n">

--- a/excel/historico_acertos_modelos.xlsx
+++ b/excel/historico_acertos_modelos.xlsx
@@ -4412,11 +4412,11 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4426,22 +4426,22 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 09, 11, 15, 16, 17, 21, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 06, 11, 12, 13, 14, 15, 17, 23, 24, 25</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H82" t="n">
         <v>15</v>
       </c>
       <c r="I82" t="n">
-        <v>66.7</v>
+        <v>46.7</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -4461,11 +4461,11 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4475,22 +4475,22 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 07, 09, 11, 15, 16, 17, 20, 21, 23, 24, 25</t>
+          <t>01, 02, 03, 05, 08, 11, 13, 14, 15, 17, 18, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H83" t="n">
         <v>15</v>
       </c>
       <c r="I83" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -4510,11 +4510,11 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4529,17 +4529,17 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H84" t="n">
         <v>15</v>
       </c>
       <c r="I84" t="n">
-        <v>66.7</v>
+        <v>46.7</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -4559,11 +4559,11 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4573,31 +4573,31 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 09, 10, 11, 12, 13, 16, 18, 20, 24</t>
+          <t>01, 03, 05, 06, 10, 11, 12, 13, 14, 18, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H85" t="n">
         <v>15</v>
       </c>
       <c r="I85" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -4608,11 +4608,11 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4627,17 +4627,17 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H86" t="n">
         <v>15</v>
       </c>
       <c r="I86" t="n">
-        <v>60</v>
+        <v>46.7</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -4657,11 +4657,11 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4671,22 +4671,22 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 14, 15, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 07, 09, 11, 12, 13, 15, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H87" t="n">
         <v>15</v>
       </c>
       <c r="I87" t="n">
-        <v>66.7</v>
+        <v>46.7</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -4706,11 +4706,11 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4725,17 +4725,17 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H88" t="n">
         <v>15</v>
       </c>
       <c r="I88" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -4755,11 +4755,11 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4769,31 +4769,31 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 09, 10, 11, 12, 13, 14, 15, 20, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 10, 11, 12, 13, 14, 15, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 15, 16, 19, 20, 21, 24</t>
+          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H89" t="n">
         <v>15</v>
       </c>
       <c r="I89" t="n">
-        <v>73.3</v>
+        <v>53.3</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -4804,11 +4804,11 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4818,22 +4818,22 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 06, 11, 12, 13, 14, 15, 17, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 17, 21, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H90" t="n">
         <v>15</v>
       </c>
       <c r="I90" t="n">
-        <v>46.7</v>
+        <v>40</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -4853,11 +4853,11 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4867,22 +4867,22 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>01, 02, 03, 05, 08, 11, 13, 14, 15, 17, 18, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 17, 21, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H91" t="n">
         <v>15</v>
       </c>
       <c r="I91" t="n">
-        <v>53.3</v>
+        <v>40</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -4902,11 +4902,11 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4921,17 +4921,17 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H92" t="n">
         <v>15</v>
       </c>
       <c r="I92" t="n">
-        <v>46.7</v>
+        <v>53.3</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -4951,11 +4951,11 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4965,22 +4965,22 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>01, 03, 05, 06, 10, 11, 12, 13, 14, 18, 20, 21, 23, 24, 25</t>
+          <t>03, 04, 05, 06, 10, 11, 12, 13, 15, 18, 20, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H93" t="n">
         <v>15</v>
       </c>
       <c r="I93" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -5000,11 +5000,11 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 10, 11, 12, 13, 14, 15, 20, 22, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 20, 24, 25</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H94" t="n">
         <v>15</v>
       </c>
       <c r="I94" t="n">
-        <v>46.7</v>
+        <v>60</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -5049,11 +5049,11 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5068,17 +5068,17 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H95" t="n">
         <v>15</v>
       </c>
       <c r="I95" t="n">
-        <v>46.7</v>
+        <v>53.3</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -5098,11 +5098,11 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -5147,11 +5147,11 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5161,22 +5161,22 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 10, 11, 12, 13, 14, 15, 20, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H97" t="n">
         <v>15</v>
       </c>
       <c r="I97" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -5196,11 +5196,11 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5215,17 +5215,17 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H98" t="n">
         <v>15</v>
       </c>
       <c r="I98" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -5245,11 +5245,11 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5259,22 +5259,22 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 17, 21, 22, 23, 24, 25</t>
+          <t>01, 03, 05, 06, 11, 12, 13, 15, 16, 17, 21, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H99" t="n">
         <v>15</v>
       </c>
       <c r="I99" t="n">
-        <v>40</v>
+        <v>53.3</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -5294,11 +5294,11 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5313,17 +5313,17 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H100" t="n">
         <v>15</v>
       </c>
       <c r="I100" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -5343,11 +5343,11 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5357,22 +5357,22 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 10, 11, 12, 13, 15, 18, 20, 22, 23, 24, 25</t>
+          <t>03, 05, 06, 09, 10, 11, 12, 13, 14, 15, 20, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H101" t="n">
         <v>15</v>
       </c>
       <c r="I101" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -5392,11 +5392,11 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5411,17 +5411,17 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H102" t="n">
         <v>15</v>
       </c>
       <c r="I102" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -5441,11 +5441,11 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5460,17 +5460,17 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H103" t="n">
         <v>15</v>
       </c>
       <c r="I103" t="n">
-        <v>53.3</v>
+        <v>66.7</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -5490,11 +5490,11 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5509,26 +5509,26 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H104" t="n">
         <v>15</v>
       </c>
       <c r="I104" t="n">
-        <v>60</v>
+        <v>73.3</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -5539,11 +5539,11 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5553,31 +5553,31 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H105" t="n">
         <v>15</v>
       </c>
       <c r="I105" t="n">
-        <v>60</v>
+        <v>73.3</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -5588,11 +5588,11 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5602,22 +5602,22 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 17, 21, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 15, 17, 21, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H106" t="n">
         <v>15</v>
       </c>
       <c r="I106" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -5637,11 +5637,11 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>01, 03, 05, 06, 11, 12, 13, 15, 16, 17, 21, 22, 23, 24, 25</t>
+          <t>01, 02, 04, 05, 06, 09, 11, 14, 15, 16, 17, 21, 22, 23, 25</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -5686,11 +5686,11 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5700,22 +5700,22 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 14, 15, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H108" t="n">
         <v>15</v>
       </c>
       <c r="I108" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -5735,11 +5735,11 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>03, 05, 06, 09, 10, 11, 12, 13, 14, 15, 20, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 14, 15, 20, 22, 23, 25</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -5784,11 +5784,11 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5803,26 +5803,26 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H110" t="n">
         <v>15</v>
       </c>
       <c r="I110" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -5833,11 +5833,11 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 07, 09, 11, 12, 13, 15, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 07, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -5882,11 +5882,11 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5901,26 +5901,26 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H112" t="n">
         <v>15</v>
       </c>
       <c r="I112" t="n">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -5931,11 +5931,11 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5945,31 +5945,31 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 20, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 10, 11, 12, 13, 14, 15, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H113" t="n">
         <v>15</v>
       </c>
       <c r="I113" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -5980,11 +5980,11 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5994,22 +5994,22 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 11, 12, 15, 17, 21, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 16, 17, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H114" t="n">
         <v>15</v>
       </c>
       <c r="I114" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -6029,11 +6029,11 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 09, 11, 14, 15, 16, 17, 21, 22, 23, 25</t>
+          <t>01, 05, 06, 11, 12, 13, 15, 16, 17, 18, 20, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -6078,11 +6078,11 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6097,26 +6097,26 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H116" t="n">
         <v>15</v>
       </c>
       <c r="I116" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -6127,11 +6127,11 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6141,22 +6141,22 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 14, 15, 20, 22, 23, 25</t>
+          <t>01, 02, 05, 06, 09, 10, 11, 12, 13, 15, 20, 21, 22, 24, 25</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H117" t="n">
         <v>15</v>
       </c>
       <c r="I117" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -6176,11 +6176,11 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6195,26 +6195,26 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H118" t="n">
         <v>15</v>
       </c>
       <c r="I118" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -6225,11 +6225,11 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6244,26 +6244,26 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H119" t="n">
         <v>15</v>
       </c>
       <c r="I119" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -6274,11 +6274,11 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -6323,11 +6323,11 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6337,22 +6337,22 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 10, 11, 12, 13, 14, 15, 20, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 21, 24, 25</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H121" t="n">
         <v>15</v>
       </c>
       <c r="I121" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -6372,11 +6372,11 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 16, 17, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 11, 12, 13, 14, 15, 16, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -6421,11 +6421,11 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6435,22 +6435,22 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>01, 05, 06, 11, 12, 13, 15, 16, 17, 18, 20, 22, 23, 24, 25</t>
+          <t>01, 02, 04, 05, 06, 10, 11, 12, 14, 15, 16, 18, 22, 23, 25</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H123" t="n">
         <v>15</v>
       </c>
       <c r="I123" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -6470,11 +6470,11 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -6519,11 +6519,11 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6533,22 +6533,22 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>01, 02, 05, 06, 09, 10, 11, 12, 13, 15, 20, 21, 22, 24, 25</t>
+          <t>01, 03, 06, 10, 12, 13, 14, 15, 16, 17, 18, 19, 20, 22, 24</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H125" t="n">
         <v>15</v>
       </c>
       <c r="I125" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -6568,11 +6568,11 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6587,26 +6587,26 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H126" t="n">
         <v>15</v>
       </c>
       <c r="I126" t="n">
-        <v>60</v>
+        <v>73.3</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -6617,11 +6617,11 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6636,26 +6636,26 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H127" t="n">
         <v>15</v>
       </c>
       <c r="I127" t="n">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -6666,11 +6666,11 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6685,17 +6685,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H128" t="n">
         <v>15</v>
       </c>
       <c r="I128" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -6715,11 +6715,11 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6729,31 +6729,31 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 21, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 10, 11, 12, 13, 14, 15, 19, 20, 24, 25</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H129" t="n">
         <v>15</v>
       </c>
       <c r="I129" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -6764,11 +6764,11 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6778,22 +6778,22 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 11, 12, 13, 14, 15, 16, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 07, 08, 11, 12, 13, 15, 16, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H130" t="n">
         <v>15</v>
       </c>
       <c r="I130" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -6813,11 +6813,11 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6827,12 +6827,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 10, 11, 12, 14, 15, 16, 18, 22, 23, 25</t>
+          <t>01, 03, 04, 05, 07, 08, 11, 13, 15, 16, 17, 18, 22, 23, 25</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -6862,11 +6862,11 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6881,26 +6881,26 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H132" t="n">
         <v>15</v>
       </c>
       <c r="I132" t="n">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -6911,11 +6911,11 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>01, 03, 06, 10, 12, 13, 14, 15, 16, 17, 18, 19, 20, 22, 24</t>
+          <t>01, 04, 05, 07, 09, 10, 11, 12, 13, 15, 16, 18, 20, 22, 24</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -6960,11 +6960,11 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6979,26 +6979,26 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H134" t="n">
         <v>15</v>
       </c>
       <c r="I134" t="n">
-        <v>73.3</v>
+        <v>46.7</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -7009,11 +7009,11 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 07, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -7058,11 +7058,11 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -7107,11 +7107,11 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7121,31 +7121,31 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 10, 11, 12, 13, 14, 15, 19, 20, 24, 25</t>
+          <t>01, 03, 04, 05, 07, 09, 10, 11, 12, 13, 15, 20, 22, 24, 25</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H137" t="n">
         <v>15</v>
       </c>
       <c r="I137" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -7156,11 +7156,11 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7170,22 +7170,22 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 11, 12, 13, 15, 16, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 14, 15, 18, 19, 23, 24, 25</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H138" t="n">
         <v>15</v>
       </c>
       <c r="I138" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -7205,11 +7205,11 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7219,22 +7219,22 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 11, 13, 15, 16, 17, 18, 22, 23, 25</t>
+          <t>01, 02, 03, 04, 05, 06, 10, 11, 14, 15, 17, 18, 19, 24, 25</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H139" t="n">
         <v>15</v>
       </c>
       <c r="I139" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -7254,11 +7254,11 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7273,17 +7273,17 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H140" t="n">
         <v>15</v>
       </c>
       <c r="I140" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -7303,11 +7303,11 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7317,12 +7317,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>01, 04, 05, 07, 09, 10, 11, 12, 13, 15, 16, 18, 20, 22, 24</t>
+          <t>01, 03, 04, 06, 09, 10, 11, 12, 14, 15, 18, 19, 20, 24, 25</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -7352,11 +7352,11 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -7401,11 +7401,11 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7420,17 +7420,17 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H143" t="n">
         <v>15</v>
       </c>
       <c r="I143" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -7450,11 +7450,11 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7469,17 +7469,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H144" t="n">
         <v>15</v>
       </c>
       <c r="I144" t="n">
-        <v>60</v>
+        <v>46.7</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -7499,11 +7499,11 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7513,22 +7513,22 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 09, 10, 11, 12, 13, 15, 20, 22, 24, 25</t>
+          <t>01, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 19, 20, 24, 25</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H145" t="n">
         <v>15</v>
       </c>
       <c r="I145" t="n">
-        <v>60</v>
+        <v>46.7</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -7548,11 +7548,11 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7562,22 +7562,22 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 11, 12, 14, 15, 18, 19, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H146" t="n">
         <v>15</v>
       </c>
       <c r="I146" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -7597,11 +7597,11 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 06, 10, 11, 14, 15, 17, 18, 19, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 22, 23, 25</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -7646,11 +7646,11 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7660,22 +7660,22 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 08, 09, 11, 12, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H148" t="n">
         <v>15</v>
       </c>
       <c r="I148" t="n">
-        <v>53.3</v>
+        <v>66.7</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -7695,11 +7695,11 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7709,22 +7709,22 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>01, 03, 04, 06, 09, 10, 11, 12, 14, 15, 18, 19, 20, 24, 25</t>
+          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 13, 17, 18, 20, 21, 25</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H149" t="n">
         <v>15</v>
       </c>
       <c r="I149" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -7744,11 +7744,11 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7763,17 +7763,17 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H150" t="n">
         <v>15</v>
       </c>
       <c r="I150" t="n">
-        <v>46.7</v>
+        <v>60</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -7793,11 +7793,11 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7807,31 +7807,31 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 07, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H151" t="n">
         <v>15</v>
       </c>
       <c r="I151" t="n">
-        <v>53.3</v>
+        <v>73.3</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -7842,11 +7842,11 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7861,17 +7861,17 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G152" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H152" t="n">
         <v>15</v>
       </c>
       <c r="I152" t="n">
-        <v>46.7</v>
+        <v>66.7</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -7891,11 +7891,11 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7905,22 +7905,22 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 19, 20, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 07, 09, 10, 11, 12, 13, 15, 20, 24, 25</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H153" t="n">
         <v>15</v>
       </c>
       <c r="I153" t="n">
-        <v>46.7</v>
+        <v>66.7</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -7940,11 +7940,11 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>3805</v>
+        <v>3806</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7954,31 +7954,31 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 15, 19, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
+          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H154" t="n">
         <v>15</v>
       </c>
       <c r="I154" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -7989,11 +7989,11 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>3805</v>
+        <v>3806</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -8003,22 +8003,22 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 22, 23, 25</t>
+          <t>01, 02, 03, 04, 05, 09, 11, 12, 15, 16, 17, 18, 20, 21, 24</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
+          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H155" t="n">
         <v>15</v>
       </c>
       <c r="I155" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -8038,11 +8038,11 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>3805</v>
+        <v>3806</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -8052,31 +8052,31 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 08, 09, 11, 12, 15, 19, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 08, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
+          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H156" t="n">
         <v>15</v>
       </c>
       <c r="I156" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -8087,11 +8087,11 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>3805</v>
+        <v>3806</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 13, 17, 18, 20, 21, 25</t>
+          <t>01, 04, 05, 06, 09, 10, 11, 12, 14, 15, 17, 18, 20, 24, 25</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
+          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -8136,11 +8136,11 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>3805</v>
+        <v>3806</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -8155,17 +8155,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
+          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H158" t="n">
         <v>15</v>
       </c>
       <c r="I158" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -8185,11 +8185,11 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>3805</v>
+        <v>3806</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
+          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -8234,11 +8234,11 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>3805</v>
+        <v>3806</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -8253,17 +8253,17 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
+          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H160" t="n">
         <v>15</v>
       </c>
       <c r="I160" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -8283,11 +8283,11 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>3805</v>
+        <v>3806</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8297,22 +8297,22 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 07, 09, 10, 11, 12, 13, 15, 20, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 14, 15, 20, 24, 25</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
+          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H161" t="n">
         <v>15</v>
       </c>
       <c r="I161" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -8332,11 +8332,11 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>14, 15, 43, 54, 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -8381,11 +8381,11 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8400,17 +8400,17 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>14, 15, 43, 54, 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H163" t="n">
         <v>5</v>
       </c>
       <c r="I163" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -8430,11 +8430,11 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -8444,22 +8444,22 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>14, 19, 26, 42, 57</t>
+          <t>14, 26, 42, 54, 57</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>14, 15, 43, 54, 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H164" t="n">
         <v>5</v>
       </c>
       <c r="I164" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -8479,11 +8479,11 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>04, 10, 23, 26, 37</t>
+          <t>04, 10, 15, 37, 42</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>14, 15, 43, 54, 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -8528,11 +8528,11 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8547,7 +8547,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>14, 15, 43, 54, 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -8577,11 +8577,11 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8596,17 +8596,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>14, 15, 43, 54, 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
         <v>5</v>
       </c>
       <c r="I167" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -8626,11 +8626,11 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>14, 15, 43, 54, 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -8675,11 +8675,11 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>7134</v>
+        <v>7135</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -8689,12 +8689,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>04, 26, 29, 49, 52</t>
+          <t>04, 26, 29, 42, 52</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>14, 15, 43, 54, 72</t>
+          <t>01, 06, 18, 43, 80</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -8724,11 +8724,11 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -8773,11 +8773,11 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8787,22 +8787,22 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>06, 45, 50, 55, 56</t>
+          <t>45, 50, 52, 55, 56</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H171" t="n">
         <v>5</v>
       </c>
       <c r="I171" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -8822,11 +8822,11 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H172" t="n">
         <v>5</v>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -8871,11 +8871,11 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>04, 10, 15, 37, 42</t>
+          <t>04, 06, 31, 37, 42</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -8920,11 +8920,11 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -8969,11 +8969,11 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8988,17 +8988,17 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H175" t="n">
         <v>5</v>
       </c>
       <c r="I175" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -9018,11 +9018,11 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -9067,11 +9067,11 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -9116,11 +9116,11 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -9130,22 +9130,22 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>26, 29, 50, 55, 56</t>
+          <t>14, 26, 50, 55, 56</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H178" t="n">
         <v>5</v>
       </c>
       <c r="I178" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -9165,11 +9165,11 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -9184,17 +9184,17 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H179" t="n">
         <v>5</v>
       </c>
       <c r="I179" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -9214,11 +9214,11 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -9233,17 +9233,17 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H180" t="n">
         <v>5</v>
       </c>
       <c r="I180" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -9263,11 +9263,11 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>04, 06, 31, 37, 42</t>
+          <t>04, 18, 30, 49, 53</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -9312,11 +9312,11 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -9361,11 +9361,11 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -9380,17 +9380,17 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H183" t="n">
         <v>5</v>
       </c>
       <c r="I183" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -9410,11 +9410,11 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -9459,11 +9459,11 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -9473,12 +9473,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>04, 26, 29, 42, 52</t>
+          <t>04, 14, 26, 49, 52</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -9508,11 +9508,11 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>14, 26, 50, 55, 56</t>
+          <t>14, 26, 29, 55, 56</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -9557,11 +9557,11 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>45, 50, 52, 55, 56</t>
+          <t>26, 45, 52, 55, 56</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -9606,11 +9606,11 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9620,22 +9620,22 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>14, 26, 42, 54, 57</t>
+          <t>02, 14, 26, 42, 57</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H188" t="n">
         <v>5</v>
       </c>
       <c r="I188" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -9655,11 +9655,11 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>04, 18, 30, 49, 53</t>
+          <t>04, 13, 18, 49, 53</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -9704,11 +9704,11 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9723,17 +9723,17 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H190" t="n">
         <v>5</v>
       </c>
       <c r="I190" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -9753,11 +9753,11 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9772,17 +9772,17 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H191" t="n">
         <v>5</v>
       </c>
       <c r="I191" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -9802,11 +9802,11 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -9821,26 +9821,26 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G192" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H192" t="n">
         <v>5</v>
       </c>
       <c r="I192" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Duque (2 acertos)</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -9851,11 +9851,11 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -9870,26 +9870,26 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H193" t="n">
         <v>5</v>
       </c>
       <c r="I193" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Duque (2 acertos)</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -9900,11 +9900,11 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -9919,17 +9919,17 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H194" t="n">
         <v>5</v>
       </c>
       <c r="I194" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -9949,11 +9949,11 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>26, 45, 52, 55, 56</t>
+          <t>17, 26, 45, 55, 56</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -9998,11 +9998,11 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -10017,17 +10017,17 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H196" t="n">
         <v>5</v>
       </c>
       <c r="I196" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -10047,11 +10047,11 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -10061,12 +10061,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>04, 13, 18, 49, 53</t>
+          <t>04, 13, 31, 42, 49</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -10096,11 +10096,11 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -10115,17 +10115,17 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H198" t="n">
         <v>5</v>
       </c>
       <c r="I198" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -10145,11 +10145,11 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -10164,17 +10164,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H199" t="n">
         <v>5</v>
       </c>
       <c r="I199" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -10194,11 +10194,11 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -10213,26 +10213,26 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G200" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H200" t="n">
         <v>5</v>
       </c>
       <c r="I200" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Duque (2 acertos)</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -10243,11 +10243,11 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -10257,31 +10257,31 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>04, 14, 26, 49, 52</t>
+          <t>04, 26, 42, 49, 52</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G201" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H201" t="n">
         <v>5</v>
       </c>
       <c r="I201" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Duque (2 acertos)</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -10292,11 +10292,11 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -10341,11 +10341,11 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>17, 26, 45, 55, 56</t>
+          <t>26, 45, 55, 56, 65</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -10390,11 +10390,11 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -10409,17 +10409,17 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H204" t="n">
         <v>5</v>
       </c>
       <c r="I204" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -10439,11 +10439,11 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>04, 13, 31, 42, 49</t>
+          <t>04, 49, 50, 52, 61</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -10488,11 +10488,11 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -10507,7 +10507,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -10537,11 +10537,11 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -10556,17 +10556,17 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H207" t="n">
         <v>5</v>
       </c>
       <c r="I207" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -10586,11 +10586,11 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -10635,11 +10635,11 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -10649,12 +10649,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>04, 26, 42, 49, 52</t>
+          <t>04, 14, 26, 49, 52</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -10684,11 +10684,11 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -10703,17 +10703,17 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H210" t="n">
         <v>5</v>
       </c>
       <c r="I210" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -10733,11 +10733,11 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -10747,12 +10747,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>26, 45, 55, 56, 65</t>
+          <t>26, 55, 56, 65, 75</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -10782,11 +10782,11 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -10801,17 +10801,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H212" t="n">
         <v>5</v>
       </c>
       <c r="I212" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
@@ -10831,11 +10831,11 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -10845,12 +10845,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>04, 49, 50, 52, 61</t>
+          <t>05, 13, 28, 52, 57</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -10880,11 +10880,11 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -10929,11 +10929,11 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -10948,17 +10948,17 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H215" t="n">
         <v>5</v>
       </c>
       <c r="I215" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -10978,11 +10978,11 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -10997,17 +10997,17 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H216" t="n">
         <v>5</v>
       </c>
       <c r="I216" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -11027,11 +11027,11 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>04, 14, 26, 49, 52</t>
+          <t>04, 14, 26, 52, 57</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -11076,11 +11076,11 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -11090,22 +11090,22 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>14, 26, 29, 55, 56</t>
+          <t>14, 25, 26, 29, 55</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H218" t="n">
         <v>5</v>
       </c>
       <c r="I218" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -11125,11 +11125,11 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -11139,22 +11139,22 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>26, 55, 56, 65, 75</t>
+          <t>26, 29, 55, 65, 75</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H219" t="n">
         <v>5</v>
       </c>
       <c r="I219" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
@@ -11174,11 +11174,11 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -11188,12 +11188,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>02, 14, 26, 42, 57</t>
+          <t>14, 19, 42, 56, 57</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -11223,11 +11223,11 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>05, 13, 28, 52, 57</t>
+          <t>04, 37, 45, 49, 52</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -11272,11 +11272,11 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -11321,11 +11321,11 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -11335,12 +11335,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>14, 26, 29, 42, 57</t>
+          <t>14, 26, 42, 56, 57</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -11370,11 +11370,11 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -11389,17 +11389,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H224" t="n">
         <v>5</v>
       </c>
       <c r="I224" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -11419,11 +11419,11 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>04, 14, 26, 52, 57</t>
+          <t>04, 26, 49, 52, 56</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -11468,11 +11468,11 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -11517,11 +11517,11 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -11566,11 +11566,11 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>14, 19, 42, 56, 57</t>
+          <t>14, 19, 34, 42, 57</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -11615,11 +11615,11 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -11629,12 +11629,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>04, 37, 45, 49, 52</t>
+          <t>04, 18, 49, 56, 58</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -11664,11 +11664,11 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -11713,11 +11713,11 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -11762,11 +11762,11 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11781,17 +11781,17 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H232" t="n">
         <v>5</v>
       </c>
       <c r="I232" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -11811,11 +11811,11 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -11860,11 +11860,11 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>7143</v>
+        <v>7144</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>10, 27, 31, 66, 80</t>
+          <t>12, 32, 43, 70, 75</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -11909,11 +11909,11 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>7143</v>
+        <v>7144</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11928,17 +11928,17 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>10, 27, 31, 66, 80</t>
+          <t>12, 32, 43, 70, 75</t>
         </is>
       </c>
       <c r="G235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H235" t="n">
         <v>5</v>
       </c>
       <c r="I235" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -11958,11 +11958,11 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>7143</v>
+        <v>7144</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11972,12 +11972,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>14, 19, 34, 42, 57</t>
+          <t>14, 19, 34, 57, 66</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>10, 27, 31, 66, 80</t>
+          <t>12, 32, 43, 70, 75</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -12007,11 +12007,11 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>7143</v>
+        <v>7144</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -12021,12 +12021,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>04, 18, 49, 56, 58</t>
+          <t>04, 18, 49, 52, 56</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>10, 27, 31, 66, 80</t>
+          <t>12, 32, 43, 70, 75</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -12056,11 +12056,11 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>7143</v>
+        <v>7144</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>10, 27, 31, 66, 80</t>
+          <t>12, 32, 43, 70, 75</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -12105,11 +12105,11 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>7143</v>
+        <v>7144</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>10, 27, 31, 66, 80</t>
+          <t>12, 32, 43, 70, 75</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -12154,11 +12154,11 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>7143</v>
+        <v>7144</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -12173,17 +12173,17 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>10, 27, 31, 66, 80</t>
+          <t>12, 32, 43, 70, 75</t>
         </is>
       </c>
       <c r="G240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H240" t="n">
         <v>5</v>
       </c>
       <c r="I240" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
@@ -12203,11 +12203,11 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>7143</v>
+        <v>7144</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>10, 27, 31, 66, 80</t>
+          <t>12, 32, 43, 70, 75</t>
         </is>
       </c>
       <c r="G241" t="n">

--- a/excel/historico_acertos_modelos.xlsx
+++ b/excel/historico_acertos_modelos.xlsx
@@ -492,11 +492,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -511,17 +511,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -541,11 +541,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -560,17 +560,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -590,11 +590,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -609,17 +609,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -639,11 +639,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -653,22 +653,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>04, 06, 08, 11, 27, 49</t>
+          <t>11, 13, 25, 33, 53, 56</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -688,11 +688,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -737,11 +737,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -786,11 +786,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -835,11 +835,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -849,22 +849,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>05, 06, 11, 27, 33, 53</t>
+          <t>05, 10, 11, 27, 33, 53</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -884,11 +884,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>09, 19, 27, 32, 42, 58</t>
+          <t>19, 27, 32, 41, 42, 45</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -933,11 +933,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>09, 19, 32, 34, 41, 45</t>
+          <t>19, 32, 34, 41, 45, 59</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -982,11 +982,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -996,22 +996,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>06, 11, 14, 27, 30, 58</t>
+          <t>06, 11, 14, 17, 27, 58</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1031,11 +1031,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11, 13, 25, 33, 53, 56</t>
+          <t>05, 15, 25, 33, 36, 56</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1080,11 +1080,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1129,11 +1129,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1143,22 +1143,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>06, 11, 14, 27, 30, 58</t>
+          <t>06, 11, 14, 17, 27, 38</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1178,11 +1178,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1227,11 +1227,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1241,22 +1241,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>05, 10, 11, 27, 33, 53</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1276,11 +1276,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>19, 27, 32, 41, 42, 45</t>
+          <t>19, 27, 32, 42, 45, 46</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1325,11 +1325,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1339,22 +1339,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19, 32, 34, 41, 45, 59</t>
+          <t>19, 32, 34, 45, 46, 59</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1374,11 +1374,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>06, 11, 14, 17, 27, 58</t>
+          <t>06, 11, 14, 27, 43, 58</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
         <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1423,11 +1423,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1437,22 +1437,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>05, 15, 25, 33, 36, 56</t>
+          <t>23, 24, 41, 43, 53, 56</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>6</v>
       </c>
       <c r="I21" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1472,11 +1472,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1491,17 +1491,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
         <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1521,11 +1521,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1535,22 +1535,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>06, 11, 14, 17, 27, 38</t>
+          <t>06, 11, 14, 17, 27, 43</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1570,11 +1570,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1619,11 +1619,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1633,22 +1633,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>05, 10, 27, 33, 37, 53</t>
+          <t>05, 10, 27, 37, 43, 53</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
         <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1668,11 +1668,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1682,22 +1682,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>19, 27, 32, 42, 45, 46</t>
+          <t>19, 32, 42, 45, 46, 58</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1717,11 +1717,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1766,11 +1766,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1785,17 +1785,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1815,11 +1815,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1829,22 +1829,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>23, 24, 41, 43, 53, 56</t>
+          <t>04, 10, 17, 23, 41, 56</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
         <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1864,11 +1864,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1913,11 +1913,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1962,11 +1962,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1981,17 +1981,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
         <v>6</v>
       </c>
       <c r="I32" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2011,11 +2011,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>05, 10, 27, 37, 43, 53</t>
+          <t>05, 10, 17, 27, 33, 53</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2060,11 +2060,11 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2109,11 +2109,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2158,11 +2158,11 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2172,22 +2172,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>06, 11, 14, 27, 43, 58</t>
+          <t>06, 11, 27, 30, 43, 58</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2207,11 +2207,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2221,22 +2221,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>04, 10, 17, 23, 41, 56</t>
+          <t>17, 23, 27, 36, 37, 41</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2256,11 +2256,11 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2270,22 +2270,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>05, 10, 27, 33, 37, 53</t>
+          <t>05, 10, 27, 37, 38, 53</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>6</v>
       </c>
       <c r="I38" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2305,11 +2305,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2319,12 +2319,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>06, 11, 14, 17, 27, 43</t>
+          <t>11, 14, 27, 30, 38, 43</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2354,11 +2354,11 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2368,22 +2368,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>05, 10, 33, 37, 42, 53</t>
+          <t>05, 10, 37, 38, 42, 53</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2403,11 +2403,11 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2417,22 +2417,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>05, 10, 17, 27, 33, 53</t>
+          <t>05, 10, 27, 37, 38, 53</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>6</v>
       </c>
       <c r="I41" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2452,11 +2452,11 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2501,11 +2501,11 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2550,11 +2550,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2564,22 +2564,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>06, 11, 27, 30, 43, 58</t>
+          <t>06, 11, 27, 30, 48, 58</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>6</v>
       </c>
       <c r="I44" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2599,11 +2599,11 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2613,22 +2613,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>17, 23, 27, 36, 37, 41</t>
+          <t>04, 06, 11, 23, 35, 37</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
         <v>6</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2648,11 +2648,11 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2697,11 +2697,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>11, 14, 27, 30, 38, 43</t>
+          <t>06, 11, 14, 27, 30, 38</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -2746,11 +2746,11 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2795,11 +2795,11 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>05, 10, 27, 37, 38, 53</t>
+          <t>05, 06, 11, 27, 37, 38</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2844,11 +2844,11 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -2893,11 +2893,11 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2942,11 +2942,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>06, 11, 27, 30, 48, 58</t>
+          <t>06, 11, 17, 27, 30, 58</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -2991,11 +2991,11 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3005,22 +3005,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>04, 06, 11, 23, 35, 37</t>
+          <t>05, 11, 23, 37, 41, 56</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>6</v>
       </c>
       <c r="I53" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3040,11 +3040,11 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3054,22 +3054,22 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>05, 10, 27, 37, 38, 53</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
         <v>6</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3089,11 +3089,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>06, 11, 14, 27, 30, 38</t>
+          <t>06, 11, 17, 27, 30, 38</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3138,11 +3138,11 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3152,22 +3152,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>05, 10, 37, 38, 42, 53</t>
+          <t>05, 10, 33, 37, 42, 53</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
         <v>6</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3187,11 +3187,11 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3201,22 +3201,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>05, 06, 11, 27, 37, 38</t>
+          <t>05, 10, 11, 27, 37, 53</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
         <v>6</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3236,11 +3236,11 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3255,17 +3255,17 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
         <v>6</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3285,11 +3285,11 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3304,17 +3304,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
         <v>6</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3334,11 +3334,11 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>06, 11, 17, 27, 30, 58</t>
+          <t>06, 11, 17, 27, 30, 43</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3383,11 +3383,11 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3397,22 +3397,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>05, 11, 23, 37, 41, 56</t>
+          <t>05, 11, 41, 43, 53, 56</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
         <v>6</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3432,11 +3432,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -3481,11 +3481,11 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>06, 11, 17, 27, 30, 38</t>
+          <t>06, 10, 11, 17, 27, 43</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -3530,11 +3530,11 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -3579,11 +3579,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>05, 10, 11, 27, 37, 53</t>
+          <t>05, 10, 11, 27, 43, 53</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -3628,11 +3628,11 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>19, 32, 42, 45, 46, 58</t>
+          <t>32, 42, 45, 46, 54, 58</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -3677,11 +3677,11 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3691,22 +3691,22 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>19, 32, 34, 45, 46, 59</t>
+          <t>12, 32, 34, 45, 46, 59</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>6</v>
       </c>
       <c r="I67" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3726,11 +3726,11 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3745,17 +3745,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H68" t="n">
         <v>6</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3775,11 +3775,11 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>05, 11, 41, 43, 53, 56</t>
+          <t>05, 11, 27, 28, 41, 53</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -3824,11 +3824,11 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -3873,11 +3873,11 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3892,17 +3892,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H71" t="n">
         <v>6</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3922,11 +3922,11 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3941,17 +3941,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
         <v>6</v>
       </c>
       <c r="I72" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3971,11 +3971,11 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>05, 10, 11, 27, 43, 53</t>
+          <t>05, 10, 11, 27, 33, 53</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -4020,11 +4020,11 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>32, 42, 45, 46, 54, 58</t>
+          <t>11, 32, 42, 45, 46, 58</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -4069,11 +4069,11 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H75" t="n">
         <v>6</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -4118,11 +4118,11 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4137,17 +4137,17 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
         <v>6</v>
       </c>
       <c r="I76" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -4167,11 +4167,11 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>05, 11, 27, 28, 41, 53</t>
+          <t>11, 28, 38, 41, 44, 53</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -4216,11 +4216,11 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4235,17 +4235,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
         <v>6</v>
       </c>
       <c r="I78" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -4265,11 +4265,11 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
         <v>6</v>
       </c>
       <c r="I79" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -4314,11 +4314,11 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>05, 10, 33, 37, 42, 53</t>
+          <t>05, 10, 33, 37, 43, 53</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -4363,11 +4363,11 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
         <v>6</v>
       </c>
       <c r="I81" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -4412,11 +4412,11 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4426,22 +4426,22 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 06, 11, 12, 13, 14, 15, 17, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 17, 21, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H82" t="n">
         <v>15</v>
       </c>
       <c r="I82" t="n">
-        <v>46.7</v>
+        <v>40</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -4461,11 +4461,11 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4475,22 +4475,22 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>01, 02, 03, 05, 08, 11, 13, 14, 15, 17, 18, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 17, 21, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H83" t="n">
         <v>15</v>
       </c>
       <c r="I83" t="n">
-        <v>53.3</v>
+        <v>40</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -4510,11 +4510,11 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4529,17 +4529,17 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H84" t="n">
         <v>15</v>
       </c>
       <c r="I84" t="n">
-        <v>46.7</v>
+        <v>53.3</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -4559,11 +4559,11 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4573,22 +4573,22 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>01, 03, 05, 06, 10, 11, 12, 13, 14, 18, 20, 21, 23, 24, 25</t>
+          <t>03, 04, 05, 06, 10, 11, 12, 13, 15, 18, 20, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H85" t="n">
         <v>15</v>
       </c>
       <c r="I85" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -4608,11 +4608,11 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4622,22 +4622,22 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 10, 11, 12, 13, 14, 15, 20, 22, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 20, 24, 25</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H86" t="n">
         <v>15</v>
       </c>
       <c r="I86" t="n">
-        <v>46.7</v>
+        <v>60</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -4657,11 +4657,11 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4676,17 +4676,17 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H87" t="n">
         <v>15</v>
       </c>
       <c r="I87" t="n">
-        <v>46.7</v>
+        <v>53.3</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -4706,11 +4706,11 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -4755,11 +4755,11 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4769,22 +4769,22 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 10, 11, 12, 13, 14, 15, 20, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>01, 02, 03, 06, 07, 08, 09, 10, 13, 14, 16, 18, 19, 20, 23</t>
+          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H89" t="n">
         <v>15</v>
       </c>
       <c r="I89" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -4804,11 +4804,11 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4823,17 +4823,17 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H90" t="n">
         <v>15</v>
       </c>
       <c r="I90" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -4853,11 +4853,11 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4867,22 +4867,22 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 17, 21, 22, 23, 24, 25</t>
+          <t>01, 03, 05, 06, 11, 12, 13, 15, 16, 17, 21, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H91" t="n">
         <v>15</v>
       </c>
       <c r="I91" t="n">
-        <v>40</v>
+        <v>53.3</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -4902,11 +4902,11 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4921,17 +4921,17 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H92" t="n">
         <v>15</v>
       </c>
       <c r="I92" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -4951,11 +4951,11 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4965,22 +4965,22 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 10, 11, 12, 13, 15, 18, 20, 22, 23, 24, 25</t>
+          <t>03, 05, 06, 09, 10, 11, 12, 13, 14, 15, 20, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H93" t="n">
         <v>15</v>
       </c>
       <c r="I93" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -5000,11 +5000,11 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H94" t="n">
         <v>15</v>
       </c>
       <c r="I94" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -5049,11 +5049,11 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5068,17 +5068,17 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H95" t="n">
         <v>15</v>
       </c>
       <c r="I95" t="n">
-        <v>53.3</v>
+        <v>66.7</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -5098,11 +5098,11 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5117,26 +5117,26 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H96" t="n">
         <v>15</v>
       </c>
       <c r="I96" t="n">
-        <v>60</v>
+        <v>73.3</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -5147,11 +5147,11 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5161,31 +5161,31 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 07, 08, 09, 10, 11, 14, 18, 19, 20, 23</t>
+          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H97" t="n">
         <v>15</v>
       </c>
       <c r="I97" t="n">
-        <v>60</v>
+        <v>73.3</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -5196,11 +5196,11 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5210,22 +5210,22 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 17, 21, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 15, 17, 21, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H98" t="n">
         <v>15</v>
       </c>
       <c r="I98" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -5245,11 +5245,11 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>01, 03, 05, 06, 11, 12, 13, 15, 16, 17, 21, 22, 23, 24, 25</t>
+          <t>01, 02, 04, 05, 06, 09, 11, 14, 15, 16, 17, 21, 22, 23, 25</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -5294,11 +5294,11 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5308,22 +5308,22 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 14, 15, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H100" t="n">
         <v>15</v>
       </c>
       <c r="I100" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -5343,11 +5343,11 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>03, 05, 06, 09, 10, 11, 12, 13, 14, 15, 20, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 14, 15, 20, 22, 23, 25</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -5392,11 +5392,11 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5411,26 +5411,26 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H102" t="n">
         <v>15</v>
       </c>
       <c r="I102" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -5441,11 +5441,11 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5455,12 +5455,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 07, 09, 11, 12, 13, 15, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 07, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -5490,11 +5490,11 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5509,26 +5509,26 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H104" t="n">
         <v>15</v>
       </c>
       <c r="I104" t="n">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -5539,11 +5539,11 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5553,31 +5553,31 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 20, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 10, 11, 12, 13, 14, 15, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 10, 12, 13, 18, 19, 20, 23, 24, 25</t>
+          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H105" t="n">
         <v>15</v>
       </c>
       <c r="I105" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -5588,11 +5588,11 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5602,22 +5602,22 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 11, 12, 15, 17, 21, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 16, 17, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H106" t="n">
         <v>15</v>
       </c>
       <c r="I106" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -5637,11 +5637,11 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 09, 11, 14, 15, 16, 17, 21, 22, 23, 25</t>
+          <t>01, 05, 06, 11, 12, 13, 15, 16, 17, 18, 20, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -5686,11 +5686,11 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5705,26 +5705,26 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H108" t="n">
         <v>15</v>
       </c>
       <c r="I108" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -5735,11 +5735,11 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5749,22 +5749,22 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 08, 10, 11, 12, 14, 15, 20, 22, 23, 25</t>
+          <t>01, 02, 05, 06, 09, 10, 11, 12, 13, 15, 20, 21, 22, 24, 25</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H109" t="n">
         <v>15</v>
       </c>
       <c r="I109" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -5784,11 +5784,11 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5803,26 +5803,26 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H110" t="n">
         <v>15</v>
       </c>
       <c r="I110" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -5833,11 +5833,11 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5852,26 +5852,26 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H111" t="n">
         <v>15</v>
       </c>
       <c r="I111" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -5882,11 +5882,11 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -5931,11 +5931,11 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5945,22 +5945,22 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 10, 11, 12, 13, 14, 15, 20, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 21, 24, 25</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 07, 08, 09, 10, 12, 13, 14, 15, 19, 21</t>
+          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H113" t="n">
         <v>15</v>
       </c>
       <c r="I113" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -5980,11 +5980,11 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5994,12 +5994,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 11, 12, 13, 15, 16, 17, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 11, 12, 13, 14, 15, 16, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -6029,11 +6029,11 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6043,22 +6043,22 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>01, 05, 06, 11, 12, 13, 15, 16, 17, 18, 20, 22, 23, 24, 25</t>
+          <t>01, 02, 04, 05, 06, 10, 11, 12, 14, 15, 16, 18, 22, 23, 25</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H115" t="n">
         <v>15</v>
       </c>
       <c r="I115" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -6078,11 +6078,11 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -6127,11 +6127,11 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6141,22 +6141,22 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>01, 02, 05, 06, 09, 10, 11, 12, 13, 15, 20, 21, 22, 24, 25</t>
+          <t>01, 03, 06, 10, 12, 13, 14, 15, 16, 17, 18, 19, 20, 22, 24</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H117" t="n">
         <v>15</v>
       </c>
       <c r="I117" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -6176,11 +6176,11 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6195,26 +6195,26 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H118" t="n">
         <v>15</v>
       </c>
       <c r="I118" t="n">
-        <v>60</v>
+        <v>73.3</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -6225,11 +6225,11 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6244,26 +6244,26 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H119" t="n">
         <v>15</v>
       </c>
       <c r="I119" t="n">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -6274,11 +6274,11 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H120" t="n">
         <v>15</v>
       </c>
       <c r="I120" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -6323,11 +6323,11 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6337,31 +6337,31 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 21, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 10, 11, 12, 13, 14, 15, 19, 20, 24, 25</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>03, 04, 07, 08, 09, 11, 12, 13, 15, 17, 19, 20, 21, 23, 24</t>
+          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H121" t="n">
         <v>15</v>
       </c>
       <c r="I121" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -6372,11 +6372,11 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6386,22 +6386,22 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 11, 12, 13, 14, 15, 16, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 07, 08, 11, 12, 13, 15, 16, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H122" t="n">
         <v>15</v>
       </c>
       <c r="I122" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -6421,11 +6421,11 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05, 06, 10, 11, 12, 14, 15, 16, 18, 22, 23, 25</t>
+          <t>01, 03, 04, 05, 07, 08, 11, 13, 15, 16, 17, 18, 22, 23, 25</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -6470,11 +6470,11 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6489,26 +6489,26 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H124" t="n">
         <v>15</v>
       </c>
       <c r="I124" t="n">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -6519,11 +6519,11 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>01, 03, 06, 10, 12, 13, 14, 15, 16, 17, 18, 19, 20, 22, 24</t>
+          <t>01, 04, 05, 07, 09, 10, 11, 12, 13, 15, 16, 18, 20, 22, 24</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -6568,11 +6568,11 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6587,26 +6587,26 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H126" t="n">
         <v>15</v>
       </c>
       <c r="I126" t="n">
-        <v>73.3</v>
+        <v>46.7</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -6617,11 +6617,11 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6631,12 +6631,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 07, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -6666,11 +6666,11 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -6715,11 +6715,11 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6729,31 +6729,31 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 10, 11, 12, 13, 14, 15, 19, 20, 24, 25</t>
+          <t>01, 03, 04, 05, 07, 09, 10, 11, 12, 13, 15, 20, 22, 24, 25</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>02, 03, 05, 06, 09, 10, 11, 12, 14, 15, 19, 20, 21, 23, 24</t>
+          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H129" t="n">
         <v>15</v>
       </c>
       <c r="I129" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -6764,11 +6764,11 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6778,22 +6778,22 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 11, 12, 13, 15, 16, 22, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 14, 15, 18, 19, 23, 24, 25</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H130" t="n">
         <v>15</v>
       </c>
       <c r="I130" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -6813,11 +6813,11 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6827,22 +6827,22 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 08, 11, 13, 15, 16, 17, 18, 22, 23, 25</t>
+          <t>01, 02, 03, 04, 05, 06, 10, 11, 14, 15, 17, 18, 19, 24, 25</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H131" t="n">
         <v>15</v>
       </c>
       <c r="I131" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -6862,11 +6862,11 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6881,17 +6881,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H132" t="n">
         <v>15</v>
       </c>
       <c r="I132" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -6911,11 +6911,11 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>01, 04, 05, 07, 09, 10, 11, 12, 13, 15, 16, 18, 20, 22, 24</t>
+          <t>01, 03, 04, 06, 09, 10, 11, 12, 14, 15, 18, 19, 20, 24, 25</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -6960,11 +6960,11 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -7009,11 +7009,11 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7028,17 +7028,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H135" t="n">
         <v>15</v>
       </c>
       <c r="I135" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -7058,11 +7058,11 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7077,17 +7077,17 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H136" t="n">
         <v>15</v>
       </c>
       <c r="I136" t="n">
-        <v>60</v>
+        <v>46.7</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -7107,11 +7107,11 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7121,22 +7121,22 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 07, 09, 10, 11, 12, 13, 15, 20, 22, 24, 25</t>
+          <t>01, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 19, 20, 24, 25</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>03, 06, 07, 08, 09, 11, 12, 13, 15, 16, 19, 20, 21, 22, 23</t>
+          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H137" t="n">
         <v>15</v>
       </c>
       <c r="I137" t="n">
-        <v>60</v>
+        <v>46.7</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -7156,11 +7156,11 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7170,22 +7170,22 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 11, 12, 14, 15, 18, 19, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 23, 24, 25</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H138" t="n">
         <v>15</v>
       </c>
       <c r="I138" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -7205,11 +7205,11 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 06, 10, 11, 14, 15, 17, 18, 19, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 22, 23, 25</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -7254,11 +7254,11 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7268,22 +7268,22 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 08, 09, 11, 12, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H140" t="n">
         <v>15</v>
       </c>
       <c r="I140" t="n">
-        <v>53.3</v>
+        <v>66.7</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -7303,11 +7303,11 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7317,22 +7317,22 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>01, 03, 04, 06, 09, 10, 11, 12, 14, 15, 18, 19, 20, 24, 25</t>
+          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 13, 17, 18, 20, 21, 25</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H141" t="n">
         <v>15</v>
       </c>
       <c r="I141" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -7352,11 +7352,11 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7371,17 +7371,17 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H142" t="n">
         <v>15</v>
       </c>
       <c r="I142" t="n">
-        <v>46.7</v>
+        <v>60</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -7401,11 +7401,11 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7415,31 +7415,31 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 07, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H143" t="n">
         <v>15</v>
       </c>
       <c r="I143" t="n">
-        <v>53.3</v>
+        <v>73.3</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -7450,11 +7450,11 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7469,17 +7469,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H144" t="n">
         <v>15</v>
       </c>
       <c r="I144" t="n">
-        <v>46.7</v>
+        <v>66.7</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -7499,11 +7499,11 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7513,22 +7513,22 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 09, 10, 11, 12, 13, 14, 15, 19, 20, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 07, 09, 10, 11, 12, 13, 15, 20, 24, 25</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>01, 02, 06, 07, 08, 12, 14, 15, 16, 17, 18, 19, 21, 24, 25</t>
+          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H145" t="n">
         <v>15</v>
       </c>
       <c r="I145" t="n">
-        <v>46.7</v>
+        <v>66.7</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -7548,11 +7548,11 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>3805</v>
+        <v>3806</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7562,31 +7562,31 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 11, 12, 15, 19, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
+          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H146" t="n">
         <v>15</v>
       </c>
       <c r="I146" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -7597,11 +7597,11 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>3805</v>
+        <v>3806</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7611,22 +7611,22 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 15, 20, 22, 23, 25</t>
+          <t>01, 02, 03, 04, 05, 09, 11, 12, 15, 16, 17, 18, 20, 21, 24</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
+          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H147" t="n">
         <v>15</v>
       </c>
       <c r="I147" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -7646,11 +7646,11 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>3805</v>
+        <v>3806</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7660,31 +7660,31 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 08, 09, 11, 12, 15, 19, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 08, 11, 12, 13, 15, 19, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
+          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H148" t="n">
         <v>15</v>
       </c>
       <c r="I148" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>11 Pontos</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -7695,11 +7695,11 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>3805</v>
+        <v>3806</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>03, 04, 05, 06, 07, 09, 10, 11, 12, 13, 17, 18, 20, 21, 25</t>
+          <t>01, 04, 05, 06, 09, 10, 11, 12, 14, 15, 17, 18, 20, 24, 25</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
+          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -7744,11 +7744,11 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>3805</v>
+        <v>3806</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7763,17 +7763,17 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
+          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H150" t="n">
         <v>15</v>
       </c>
       <c r="I150" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -7793,11 +7793,11 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>3805</v>
+        <v>3806</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
+          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -7842,11 +7842,11 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>3805</v>
+        <v>3806</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7861,17 +7861,17 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
+          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="G152" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H152" t="n">
         <v>15</v>
       </c>
       <c r="I152" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -7891,11 +7891,11 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>3805</v>
+        <v>3806</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7905,22 +7905,22 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 07, 09, 10, 11, 12, 13, 15, 20, 24, 25</t>
+          <t>01, 03, 04, 05, 06, 09, 10, 11, 12, 13, 14, 15, 20, 24, 25</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>03, 05, 06, 07, 08, 10, 11, 13, 14, 15, 19, 22, 23, 24, 25</t>
+          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H153" t="n">
         <v>15</v>
       </c>
       <c r="I153" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -7940,11 +7940,11 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>3806</v>
+        <v>3807</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7954,31 +7954,31 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>01, 03, 04, 05, 06, 09, 11, 12, 15, 19, 20, 21, 23, 24, 25</t>
+          <t>01, 02, 03, 05, 06, 11, 12, 14, 15, 17, 18, 19, 23, 24, 25</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 07, 10, 11, 13, 16, 17, 19, 20, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H154" t="n">
         <v>15</v>
       </c>
       <c r="I154" t="n">
-        <v>73.3</v>
+        <v>53.3</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -7989,11 +7989,11 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>3806</v>
+        <v>3807</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>01, 02, 03, 04, 05, 09, 11, 12, 15, 16, 17, 18, 20, 21, 24</t>
+          <t>01, 02, 03, 05, 06, 10, 11, 12, 14, 15, 17, 18, 22, 24, 25</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 07, 10, 11, 13, 16, 17, 19, 20, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -8038,11 +8038,11 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>3806</v>
+        <v>3807</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -8057,26 +8057,26 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 07, 10, 11, 13, 16, 17, 19, 20, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H156" t="n">
         <v>15</v>
       </c>
       <c r="I156" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -8087,11 +8087,11 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>3806</v>
+        <v>3807</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>01, 04, 05, 06, 09, 10, 11, 12, 14, 15, 17, 18, 20, 24, 25</t>
+          <t>01, 03, 05, 06, 09, 10, 11, 12, 13, 14, 18, 20, 21, 24, 25</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 07, 10, 11, 13, 16, 17, 19, 20, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -8136,11 +8136,11 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>3806</v>
+        <v>3807</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -8155,17 +8155,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 07, 10, 11, 13, 16, 17, 19, 20, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H158" t="n">
         <v>15</v>
       </c>
       <c r="I158" t="n">
-        <v>53.3</v>
+        <v>60</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -8185,11 +8185,11 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>3806</v>
+        <v>3807</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -8204,26 +8204,26 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 07, 10, 11, 13, 16, 17, 19, 20, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G159" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H159" t="n">
         <v>15</v>
       </c>
       <c r="I159" t="n">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>11 Pontos</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -8234,11 +8234,11 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>3806</v>
+        <v>3807</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -8253,26 +8253,26 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 07, 10, 11, 13, 16, 17, 19, 20, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H160" t="n">
         <v>15</v>
       </c>
       <c r="I160" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>12 Pontos</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -8283,11 +8283,11 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>3806</v>
+        <v>3807</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>04, 05, 06, 07, 08, 09, 11, 13, 16, 19, 20, 21, 23, 24, 25</t>
+          <t>01, 03, 04, 07, 10, 11, 13, 16, 17, 19, 20, 22, 23, 24, 25</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -8332,11 +8332,11 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -8381,11 +8381,11 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8395,22 +8395,22 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>06, 45, 50, 55, 56</t>
+          <t>45, 50, 52, 55, 56</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
         <v>5</v>
       </c>
       <c r="I163" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -8430,11 +8430,11 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -8449,17 +8449,17 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H164" t="n">
         <v>5</v>
       </c>
       <c r="I164" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -8479,11 +8479,11 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>04, 10, 15, 37, 42</t>
+          <t>04, 06, 31, 37, 42</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -8528,11 +8528,11 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8547,7 +8547,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -8577,11 +8577,11 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8596,17 +8596,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H167" t="n">
         <v>5</v>
       </c>
       <c r="I167" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -8626,11 +8626,11 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -8675,11 +8675,11 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>01, 06, 18, 43, 80</t>
+          <t>13, 14, 30, 53, 60</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -8724,11 +8724,11 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8738,22 +8738,22 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>26, 29, 50, 55, 56</t>
+          <t>14, 26, 50, 55, 56</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H170" t="n">
         <v>5</v>
       </c>
       <c r="I170" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -8773,11 +8773,11 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8792,17 +8792,17 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H171" t="n">
         <v>5</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -8822,11 +8822,11 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H172" t="n">
         <v>5</v>
       </c>
       <c r="I172" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -8871,11 +8871,11 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>04, 06, 31, 37, 42</t>
+          <t>04, 18, 30, 49, 53</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -8920,11 +8920,11 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -8969,11 +8969,11 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8988,17 +8988,17 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H175" t="n">
         <v>5</v>
       </c>
       <c r="I175" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -9018,11 +9018,11 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -9067,11 +9067,11 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>7136</v>
+        <v>7137</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>04, 26, 29, 42, 52</t>
+          <t>04, 14, 26, 49, 52</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>13, 14, 30, 53, 60</t>
+          <t>02, 07, 50, 61, 79</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -9116,11 +9116,11 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -9130,12 +9130,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>14, 26, 50, 55, 56</t>
+          <t>14, 26, 29, 55, 56</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -9165,11 +9165,11 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>45, 50, 52, 55, 56</t>
+          <t>26, 45, 52, 55, 56</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -9214,11 +9214,11 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -9228,22 +9228,22 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>14, 26, 42, 54, 57</t>
+          <t>02, 14, 26, 42, 57</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H180" t="n">
         <v>5</v>
       </c>
       <c r="I180" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -9263,11 +9263,11 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>04, 18, 30, 49, 53</t>
+          <t>04, 13, 18, 49, 53</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -9312,11 +9312,11 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -9331,17 +9331,17 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H182" t="n">
         <v>5</v>
       </c>
       <c r="I182" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
@@ -9361,11 +9361,11 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -9380,17 +9380,17 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H183" t="n">
         <v>5</v>
       </c>
       <c r="I183" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -9410,11 +9410,11 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -9429,26 +9429,26 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H184" t="n">
         <v>5</v>
       </c>
       <c r="I184" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Duque (2 acertos)</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -9459,11 +9459,11 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>7137</v>
+        <v>7138</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -9478,26 +9478,26 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>02, 07, 50, 61, 79</t>
+          <t>14, 16, 27, 34, 52</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H185" t="n">
         <v>5</v>
       </c>
       <c r="I185" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Duque (2 acertos)</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -9508,11 +9508,11 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -9527,17 +9527,17 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H186" t="n">
         <v>5</v>
       </c>
       <c r="I186" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -9557,11 +9557,11 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>26, 45, 52, 55, 56</t>
+          <t>17, 26, 45, 55, 56</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -9606,11 +9606,11 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9625,17 +9625,17 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H188" t="n">
         <v>5</v>
       </c>
       <c r="I188" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -9655,11 +9655,11 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>04, 13, 18, 49, 53</t>
+          <t>04, 13, 31, 42, 49</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -9704,11 +9704,11 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9723,17 +9723,17 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H190" t="n">
         <v>5</v>
       </c>
       <c r="I190" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -9753,11 +9753,11 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9772,17 +9772,17 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H191" t="n">
         <v>5</v>
       </c>
       <c r="I191" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -9802,11 +9802,11 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -9821,26 +9821,26 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H192" t="n">
         <v>5</v>
       </c>
       <c r="I192" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Duque (2 acertos)</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -9851,11 +9851,11 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>7138</v>
+        <v>7139</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -9865,31 +9865,31 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>04, 14, 26, 49, 52</t>
+          <t>04, 26, 42, 49, 52</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>14, 16, 27, 34, 52</t>
+          <t>11, 17, 40, 62, 68</t>
         </is>
       </c>
       <c r="G193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H193" t="n">
         <v>5</v>
       </c>
       <c r="I193" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Duque (2 acertos)</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -9900,11 +9900,11 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -9949,11 +9949,11 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>17, 26, 45, 55, 56</t>
+          <t>26, 45, 55, 56, 65</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -9998,11 +9998,11 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -10017,17 +10017,17 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H196" t="n">
         <v>5</v>
       </c>
       <c r="I196" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -10047,11 +10047,11 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -10061,12 +10061,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>04, 13, 31, 42, 49</t>
+          <t>04, 49, 50, 52, 61</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -10096,11 +10096,11 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -10145,11 +10145,11 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -10164,17 +10164,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H199" t="n">
         <v>5</v>
       </c>
       <c r="I199" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -10194,11 +10194,11 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -10243,11 +10243,11 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>7139</v>
+        <v>7140</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>04, 26, 42, 49, 52</t>
+          <t>04, 14, 26, 49, 52</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>11, 17, 40, 62, 68</t>
+          <t>05, 28, 45, 57, 59</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -10292,11 +10292,11 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -10311,17 +10311,17 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H202" t="n">
         <v>5</v>
       </c>
       <c r="I202" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -10341,11 +10341,11 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>26, 45, 55, 56, 65</t>
+          <t>26, 55, 56, 65, 75</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -10390,11 +10390,11 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -10409,17 +10409,17 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H204" t="n">
         <v>5</v>
       </c>
       <c r="I204" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -10439,11 +10439,11 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>04, 49, 50, 52, 61</t>
+          <t>05, 13, 28, 52, 57</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -10488,11 +10488,11 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -10507,7 +10507,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -10537,11 +10537,11 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -10556,17 +10556,17 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H207" t="n">
         <v>5</v>
       </c>
       <c r="I207" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -10586,11 +10586,11 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -10605,17 +10605,17 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H208" t="n">
         <v>5</v>
       </c>
       <c r="I208" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -10635,11 +10635,11 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>7140</v>
+        <v>7141</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -10649,12 +10649,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>04, 14, 26, 49, 52</t>
+          <t>04, 14, 26, 52, 57</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>05, 28, 45, 57, 59</t>
+          <t>01, 18, 19, 33, 56</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -10684,11 +10684,11 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -10698,22 +10698,22 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>14, 26, 29, 55, 56</t>
+          <t>14, 25, 26, 29, 55</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H210" t="n">
         <v>5</v>
       </c>
       <c r="I210" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -10733,11 +10733,11 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -10747,22 +10747,22 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>26, 55, 56, 65, 75</t>
+          <t>26, 29, 55, 65, 75</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H211" t="n">
         <v>5</v>
       </c>
       <c r="I211" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -10782,11 +10782,11 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>02, 14, 26, 42, 57</t>
+          <t>14, 19, 42, 56, 57</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -10831,11 +10831,11 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -10845,12 +10845,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>05, 13, 28, 52, 57</t>
+          <t>04, 37, 45, 49, 52</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -10880,11 +10880,11 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -10929,11 +10929,11 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>14, 26, 29, 42, 57</t>
+          <t>14, 26, 42, 56, 57</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -10978,11 +10978,11 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -10997,17 +10997,17 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H216" t="n">
         <v>5</v>
       </c>
       <c r="I216" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -11027,11 +11027,11 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>7141</v>
+        <v>7142</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>04, 14, 26, 52, 57</t>
+          <t>04, 26, 49, 52, 56</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>01, 18, 19, 33, 56</t>
+          <t>05, 33, 34, 48, 58</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -11076,11 +11076,11 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -11125,11 +11125,11 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -11174,11 +11174,11 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -11188,12 +11188,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>14, 19, 42, 56, 57</t>
+          <t>14, 19, 34, 42, 57</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -11223,11 +11223,11 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>04, 37, 45, 49, 52</t>
+          <t>04, 18, 49, 56, 58</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -11272,11 +11272,11 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -11321,11 +11321,11 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -11370,11 +11370,11 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -11389,17 +11389,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H224" t="n">
         <v>5</v>
       </c>
       <c r="I224" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -11419,11 +11419,11 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>7142</v>
+        <v>7143</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>05, 33, 34, 48, 58</t>
+          <t>10, 27, 31, 66, 80</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -11468,11 +11468,11 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>7143</v>
+        <v>7144</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>10, 27, 31, 66, 80</t>
+          <t>12, 32, 43, 70, 75</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -11517,11 +11517,11 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>7143</v>
+        <v>7144</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -11536,17 +11536,17 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>10, 27, 31, 66, 80</t>
+          <t>12, 32, 43, 70, 75</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H227" t="n">
         <v>5</v>
       </c>
       <c r="I227" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -11566,11 +11566,11 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>7143</v>
+        <v>7144</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>14, 19, 34, 42, 57</t>
+          <t>14, 19, 34, 57, 66</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>10, 27, 31, 66, 80</t>
+          <t>12, 32, 43, 70, 75</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -11615,11 +11615,11 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>7143</v>
+        <v>7144</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -11629,12 +11629,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>04, 18, 49, 56, 58</t>
+          <t>04, 18, 49, 52, 56</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>10, 27, 31, 66, 80</t>
+          <t>12, 32, 43, 70, 75</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -11664,11 +11664,11 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>7143</v>
+        <v>7144</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>10, 27, 31, 66, 80</t>
+          <t>12, 32, 43, 70, 75</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -11713,11 +11713,11 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>7143</v>
+        <v>7144</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>10, 27, 31, 66, 80</t>
+          <t>12, 32, 43, 70, 75</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -11762,11 +11762,11 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>7143</v>
+        <v>7144</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11781,17 +11781,17 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>10, 27, 31, 66, 80</t>
+          <t>12, 32, 43, 70, 75</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H232" t="n">
         <v>5</v>
       </c>
       <c r="I232" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -11811,11 +11811,11 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>7143</v>
+        <v>7144</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>10, 27, 31, 66, 80</t>
+          <t>12, 32, 43, 70, 75</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -11860,11 +11860,11 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>7144</v>
+        <v>7145</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>12, 32, 43, 70, 75</t>
+          <t>01, 06, 52, 62, 69</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -11909,11 +11909,11 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>7144</v>
+        <v>7145</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11923,22 +11923,22 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>26, 29, 55, 65, 75</t>
+          <t>25, 26, 29, 55, 65</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>12, 32, 43, 70, 75</t>
+          <t>01, 06, 52, 62, 69</t>
         </is>
       </c>
       <c r="G235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H235" t="n">
         <v>5</v>
       </c>
       <c r="I235" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -11958,11 +11958,11 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>7144</v>
+        <v>7145</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11972,12 +11972,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>14, 19, 34, 57, 66</t>
+          <t>14, 19, 34, 57, 70</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>12, 32, 43, 70, 75</t>
+          <t>01, 06, 52, 62, 69</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -12007,11 +12007,11 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>7144</v>
+        <v>7145</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -12021,22 +12021,22 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>04, 18, 49, 52, 56</t>
+          <t>04, 40, 49, 52, 56</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>12, 32, 43, 70, 75</t>
+          <t>01, 06, 52, 62, 69</t>
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H237" t="n">
         <v>5</v>
       </c>
       <c r="I237" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
@@ -12056,11 +12056,11 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>7144</v>
+        <v>7145</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -12075,17 +12075,17 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>12, 32, 43, 70, 75</t>
+          <t>01, 06, 52, 62, 69</t>
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H238" t="n">
         <v>5</v>
       </c>
       <c r="I238" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -12105,11 +12105,11 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>7144</v>
+        <v>7145</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>12, 32, 43, 70, 75</t>
+          <t>01, 06, 52, 62, 69</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -12154,11 +12154,11 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>7144</v>
+        <v>7145</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -12173,17 +12173,17 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>12, 32, 43, 70, 75</t>
+          <t>01, 06, 52, 62, 69</t>
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H240" t="n">
         <v>5</v>
       </c>
       <c r="I240" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
@@ -12203,11 +12203,11 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>7144</v>
+        <v>7145</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -12222,17 +12222,17 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>12, 32, 43, 70, 75</t>
+          <t>01, 06, 52, 62, 69</t>
         </is>
       </c>
       <c r="G241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H241" t="n">
         <v>5</v>
       </c>
       <c r="I241" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>

--- a/excel/historico_acertos_modelos.xlsx
+++ b/excel/historico_acertos_modelos.xlsx
@@ -492,11 +492,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -506,22 +506,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>09, 19, 27, 32, 41, 58</t>
+          <t>09, 19, 27, 32, 41, 45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>08, 17, 24, 43, 47, 58</t>
+          <t>01, 11, 36, 43, 48, 49</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -541,11 +541,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>08, 17, 24, 43, 47, 58</t>
+          <t>01, 11, 36, 43, 48, 49</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -590,11 +590,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,12 +604,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>06, 11, 27, 30, 42, 58</t>
+          <t>06, 11, 17, 27, 30, 58</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>08, 17, 24, 43, 47, 58</t>
+          <t>01, 11, 36, 43, 48, 49</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -639,11 +639,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -653,22 +653,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10, 15, 25, 51, 53, 60</t>
+          <t>10, 25, 27, 38, 43, 53</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>08, 17, 24, 43, 47, 58</t>
+          <t>01, 11, 36, 43, 48, 49</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -688,11 +688,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>08, 17, 24, 43, 47, 58</t>
+          <t>01, 11, 36, 43, 48, 49</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -737,11 +737,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>06, 11, 14, 27, 30, 58</t>
+          <t>06, 11, 17, 27, 30, 58</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>08, 17, 24, 43, 47, 58</t>
+          <t>01, 11, 36, 43, 48, 49</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -786,11 +786,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -800,22 +800,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>05, 10, 33, 37, 42, 53</t>
+          <t>10, 33, 37, 42, 43, 53</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>08, 17, 24, 43, 47, 58</t>
+          <t>01, 11, 36, 43, 48, 49</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -835,11 +835,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -849,22 +849,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>05, 10, 27, 33, 37, 53</t>
+          <t>10, 27, 33, 37, 43, 53</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>08, 17, 24, 43, 47, 58</t>
+          <t>01, 11, 36, 43, 48, 49</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -884,11 +884,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01, 11, 36, 43, 48, 49</t>
+          <t>14, 21, 25, 40, 51, 56</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -933,11 +933,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>01, 11, 36, 43, 48, 49</t>
+          <t>14, 21, 25, 40, 51, 56</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -982,11 +982,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -996,22 +996,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>06, 11, 17, 27, 30, 58</t>
+          <t>06, 11, 27, 30, 43, 58</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>01, 11, 36, 43, 48, 49</t>
+          <t>14, 21, 25, 40, 51, 56</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1031,11 +1031,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10, 25, 27, 38, 43, 53</t>
+          <t>10, 27, 37, 38, 44, 53</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>01, 11, 36, 43, 48, 49</t>
+          <t>14, 21, 25, 40, 51, 56</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1080,11 +1080,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>01, 11, 36, 43, 48, 49</t>
+          <t>14, 21, 25, 40, 51, 56</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1129,11 +1129,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1143,22 +1143,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>06, 11, 17, 27, 30, 58</t>
+          <t>06, 11, 27, 30, 43, 58</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>01, 11, 36, 43, 48, 49</t>
+          <t>14, 21, 25, 40, 51, 56</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1178,11 +1178,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>01, 11, 36, 43, 48, 49</t>
+          <t>14, 21, 25, 40, 51, 56</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1246,17 +1246,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>01, 11, 36, 43, 48, 49</t>
+          <t>14, 21, 25, 40, 51, 56</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1276,11 +1276,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>02, 04, 16, 21, 48, 53</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1325,11 +1325,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>02, 04, 16, 21, 48, 53</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1374,11 +1374,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>02, 04, 16, 21, 48, 53</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1423,11 +1423,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1437,22 +1437,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>10, 27, 37, 38, 44, 53</t>
+          <t>10, 24, 35, 49, 53, 56</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>02, 04, 16, 21, 48, 53</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>6</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1472,11 +1472,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1491,17 +1491,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>02, 04, 16, 21, 48, 53</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1521,11 +1521,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>06, 11, 27, 30, 43, 58</t>
+          <t>11, 14, 27, 30, 43, 58</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>02, 04, 16, 21, 48, 53</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1570,11 +1570,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1589,17 +1589,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>02, 04, 16, 21, 48, 53</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
         <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1619,11 +1619,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1638,17 +1638,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>02, 04, 16, 21, 48, 53</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1668,11 +1668,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>09, 19, 27, 32, 41, 45</t>
+          <t>09, 19, 27, 32, 41, 42</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1717,11 +1717,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1766,11 +1766,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1815,11 +1815,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1829,22 +1829,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10, 24, 35, 49, 53, 56</t>
+          <t>04, 10, 27, 35, 36, 38</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1864,11 +1864,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1913,11 +1913,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
         <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1962,11 +1962,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2011,11 +2011,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2060,11 +2060,11 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2109,11 +2109,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2158,11 +2158,11 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>06, 11, 27, 30, 43, 58</t>
+          <t>06, 11, 14, 27, 30, 58</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2207,11 +2207,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2221,22 +2221,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>04, 10, 27, 35, 36, 38</t>
+          <t>10, 11, 16, 23, 27, 35</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
         <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2256,11 +2256,11 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2305,11 +2305,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2324,17 +2324,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2354,11 +2354,11 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2403,11 +2403,11 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>10, 27, 33, 37, 43, 53</t>
+          <t>10, 11, 27, 33, 37, 43</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2452,11 +2452,11 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2501,11 +2501,11 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2550,11 +2550,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2569,17 +2569,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
         <v>6</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2599,11 +2599,11 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2613,22 +2613,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>10, 11, 16, 23, 27, 35</t>
+          <t>04, 08, 11, 13, 33, 60</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>6</v>
       </c>
       <c r="I45" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2648,11 +2648,11 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2697,11 +2697,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -2746,11 +2746,11 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>10, 33, 37, 42, 43, 53</t>
+          <t>05, 10, 33, 37, 42, 53</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2795,11 +2795,11 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2809,22 +2809,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>10, 11, 27, 33, 37, 43</t>
+          <t>05, 10, 11, 27, 33, 53</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>6</v>
       </c>
       <c r="I49" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2844,11 +2844,11 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>09, 19, 27, 32, 41, 42</t>
+          <t>09, 19, 27, 32, 42, 58</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -2893,11 +2893,11 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2942,11 +2942,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2961,17 +2961,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>6</v>
       </c>
       <c r="I52" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2991,11 +2991,11 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>04, 08, 11, 13, 33, 60</t>
+          <t>04, 06, 08, 11, 27, 49</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3040,11 +3040,11 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3089,11 +3089,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>11, 14, 27, 30, 43, 58</t>
+          <t>06, 11, 14, 27, 30, 58</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3138,11 +3138,11 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3187,11 +3187,11 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3201,22 +3201,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>05, 10, 11, 27, 33, 53</t>
+          <t>06, 10, 11, 27, 33, 37</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
         <v>6</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3236,11 +3236,11 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3255,17 +3255,17 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
         <v>6</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3285,11 +3285,11 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3304,17 +3304,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
         <v>6</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3334,11 +3334,11 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3353,17 +3353,17 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
         <v>6</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3383,11 +3383,11 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3397,22 +3397,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>04, 06, 08, 11, 27, 49</t>
+          <t>11, 13, 25, 33, 53, 56</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
         <v>6</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3432,11 +3432,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -3481,11 +3481,11 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3500,17 +3500,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
         <v>6</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3530,11 +3530,11 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -3579,11 +3579,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>06, 10, 11, 27, 33, 37</t>
+          <t>10, 11, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -3628,11 +3628,11 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>09, 19, 27, 32, 42, 58</t>
+          <t>19, 27, 32, 41, 42, 45</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -3677,11 +3677,11 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>09, 19, 32, 34, 41, 45</t>
+          <t>19, 32, 34, 41, 45, 59</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -3726,11 +3726,11 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3740,22 +3740,22 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>06, 11, 14, 27, 30, 58</t>
+          <t>06, 11, 14, 17, 27, 58</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>6</v>
       </c>
       <c r="I68" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3775,11 +3775,11 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3789,22 +3789,22 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>11, 13, 25, 33, 53, 56</t>
+          <t>05, 15, 25, 33, 36, 56</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H69" t="n">
         <v>6</v>
       </c>
       <c r="I69" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3824,11 +3824,11 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -3873,11 +3873,11 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3887,22 +3887,22 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>06, 11, 14, 27, 30, 58</t>
+          <t>06, 11, 14, 17, 27, 38</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
         <v>6</v>
       </c>
       <c r="I71" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3922,11 +3922,11 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -3971,11 +3971,11 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>10, 11, 27, 33, 37, 53</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -4020,11 +4020,11 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>19, 27, 32, 41, 42, 45</t>
+          <t>19, 27, 32, 42, 45, 46</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -4069,11 +4069,11 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4083,22 +4083,22 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>19, 32, 34, 41, 45, 59</t>
+          <t>19, 32, 34, 45, 46, 59</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
         <v>6</v>
       </c>
       <c r="I75" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -4118,11 +4118,11 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4132,22 +4132,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>06, 11, 14, 17, 27, 58</t>
+          <t>06, 11, 14, 27, 43, 58</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
         <v>6</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -4167,11 +4167,11 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>05, 15, 25, 33, 36, 56</t>
+          <t>23, 24, 41, 43, 53, 56</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
         <v>6</v>
       </c>
       <c r="I77" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -4216,11 +4216,11 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4235,17 +4235,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78" t="n">
         <v>6</v>
       </c>
       <c r="I78" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -4265,11 +4265,11 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>06, 11, 14, 17, 27, 38</t>
+          <t>06, 11, 14, 17, 27, 43</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
         <v>6</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -4314,11 +4314,11 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -4363,11 +4363,11 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>05, 10, 27, 33, 37, 53</t>
+          <t>05, 27, 33, 37, 43, 53</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -4412,11 +4412,11 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4426,22 +4426,22 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>19, 27, 32, 42, 45, 46</t>
+          <t>19, 32, 42, 45, 46, 58</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
         <v>6</v>
       </c>
       <c r="I82" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -4461,11 +4461,11 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -4510,11 +4510,11 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4529,17 +4529,17 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
         <v>6</v>
       </c>
       <c r="I84" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -4559,11 +4559,11 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4573,22 +4573,22 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>23, 24, 41, 43, 53, 56</t>
+          <t>04, 10, 17, 23, 41, 56</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" t="n">
         <v>6</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -4608,11 +4608,11 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -4657,11 +4657,11 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4676,17 +4676,17 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
         <v>6</v>
       </c>
       <c r="I87" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -4706,11 +4706,11 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4725,17 +4725,17 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H88" t="n">
         <v>6</v>
       </c>
       <c r="I88" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -4755,11 +4755,11 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4769,22 +4769,22 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>05, 27, 33, 37, 43, 53</t>
+          <t>10, 17, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H89" t="n">
         <v>6</v>
       </c>
       <c r="I89" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -4804,11 +4804,11 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -4853,11 +4853,11 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -4902,11 +4902,11 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4916,22 +4916,22 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>06, 11, 14, 27, 43, 58</t>
+          <t>06, 11, 27, 30, 43, 58</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
         <v>6</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -4951,11 +4951,11 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4965,22 +4965,22 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>04, 10, 17, 23, 41, 56</t>
+          <t>17, 23, 27, 36, 37, 41</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
         <v>6</v>
       </c>
       <c r="I93" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -5000,11 +5000,11 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>05, 10, 27, 33, 37, 53</t>
+          <t>05, 10, 27, 37, 38, 53</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
         <v>6</v>
       </c>
       <c r="I94" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -5049,11 +5049,11 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>06, 11, 14, 17, 27, 43</t>
+          <t>11, 14, 27, 30, 38, 43</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -5098,11 +5098,11 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5112,22 +5112,22 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>05, 10, 33, 37, 42, 53</t>
+          <t>05, 10, 37, 38, 42, 53</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
         <v>6</v>
       </c>
       <c r="I96" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -5147,11 +5147,11 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5161,22 +5161,22 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>10, 17, 27, 33, 37, 53</t>
+          <t>05, 10, 27, 37, 38, 53</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
         <v>6</v>
       </c>
       <c r="I97" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -5196,11 +5196,11 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -5245,11 +5245,11 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -5294,11 +5294,11 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5308,22 +5308,22 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>06, 11, 27, 30, 43, 58</t>
+          <t>06, 11, 27, 30, 48, 58</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
         <v>6</v>
       </c>
       <c r="I100" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -5343,11 +5343,11 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5357,22 +5357,22 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>17, 23, 27, 36, 37, 41</t>
+          <t>04, 06, 11, 23, 35, 37</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
         <v>6</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -5392,11 +5392,11 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -5441,11 +5441,11 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5455,12 +5455,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>11, 14, 27, 30, 38, 43</t>
+          <t>06, 11, 14, 27, 30, 38</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -5490,11 +5490,11 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -5539,11 +5539,11 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>05, 10, 27, 37, 38, 53</t>
+          <t>06, 11, 27, 37, 38, 53</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -5588,11 +5588,11 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -5637,11 +5637,11 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -5686,11 +5686,11 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>06, 11, 27, 30, 48, 58</t>
+          <t>06, 11, 17, 27, 30, 58</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -5735,11 +5735,11 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5749,22 +5749,22 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>04, 06, 11, 23, 35, 37</t>
+          <t>05, 11, 23, 37, 41, 56</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
         <v>6</v>
       </c>
       <c r="I109" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -5784,11 +5784,11 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5798,22 +5798,22 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>05, 10, 27, 37, 38, 53</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" t="n">
         <v>6</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -5833,11 +5833,11 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>06, 11, 14, 27, 30, 38</t>
+          <t>06, 11, 17, 27, 30, 38</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -5882,11 +5882,11 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5896,22 +5896,22 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>05, 10, 37, 38, 42, 53</t>
+          <t>05, 10, 33, 37, 42, 53</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" t="n">
         <v>6</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -5931,11 +5931,11 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5945,22 +5945,22 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>06, 11, 27, 37, 38, 53</t>
+          <t>05, 10, 11, 27, 33, 37</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113" t="n">
         <v>6</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -5980,11 +5980,11 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5999,17 +5999,17 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114" t="n">
         <v>6</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -6029,11 +6029,11 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6048,17 +6048,17 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" t="n">
         <v>6</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -6078,11 +6078,11 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>06, 11, 17, 27, 30, 58</t>
+          <t>06, 11, 17, 27, 30, 43</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -6127,11 +6127,11 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6141,22 +6141,22 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>05, 11, 23, 37, 41, 56</t>
+          <t>05, 11, 41, 43, 53, 56</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117" t="n">
         <v>6</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -6176,11 +6176,11 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -6225,11 +6225,11 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>06, 11, 17, 27, 30, 38</t>
+          <t>06, 10, 11, 17, 27, 43</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -6274,11 +6274,11 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -6323,11 +6323,11 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>05, 10, 11, 27, 33, 37</t>
+          <t>05, 10, 11, 27, 43, 53</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -6372,11 +6372,11 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>19, 32, 42, 45, 46, 58</t>
+          <t>32, 42, 45, 46, 54, 58</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -6421,11 +6421,11 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6435,22 +6435,22 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>19, 32, 34, 45, 46, 59</t>
+          <t>12, 32, 34, 45, 46, 59</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
         <v>6</v>
       </c>
       <c r="I123" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -6470,11 +6470,11 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6489,17 +6489,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H124" t="n">
         <v>6</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -6519,11 +6519,11 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>05, 11, 41, 43, 53, 56</t>
+          <t>05, 11, 27, 28, 41, 53</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -6568,11 +6568,11 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -6617,11 +6617,11 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H127" t="n">
         <v>6</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -6666,11 +6666,11 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6685,17 +6685,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
         <v>6</v>
       </c>
       <c r="I128" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -6715,11 +6715,11 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6729,12 +6729,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>05, 10, 11, 27, 43, 53</t>
+          <t>05, 10, 11, 27, 37, 53</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -6764,11 +6764,11 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>32, 42, 45, 46, 54, 58</t>
+          <t>11, 32, 42, 45, 46, 58</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -6813,11 +6813,11 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6832,17 +6832,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H131" t="n">
         <v>6</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -6862,11 +6862,11 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6881,17 +6881,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
         <v>6</v>
       </c>
       <c r="I132" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -6911,11 +6911,11 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>05, 11, 27, 28, 41, 53</t>
+          <t>11, 28, 38, 41, 44, 53</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -6960,11 +6960,11 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H134" t="n">
         <v>6</v>
       </c>
       <c r="I134" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -7009,11 +7009,11 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7028,17 +7028,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
         <v>6</v>
       </c>
       <c r="I135" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -7058,11 +7058,11 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>05, 10, 33, 37, 42, 53</t>
+          <t>05, 10, 33, 37, 43, 53</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -7107,11 +7107,11 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7121,22 +7121,22 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>05, 10, 11, 27, 37, 53</t>
+          <t>10, 11, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
         <v>6</v>
       </c>
       <c r="I137" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -7156,11 +7156,11 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7170,22 +7170,22 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>11, 32, 42, 45, 46, 58</t>
+          <t>11, 32, 34, 42, 46, 58</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H138" t="n">
         <v>6</v>
       </c>
       <c r="I138" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -7205,11 +7205,11 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7219,22 +7219,22 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>12, 32, 34, 45, 46, 59</t>
+          <t>03, 32, 34, 42, 46, 59</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
         <v>6</v>
       </c>
       <c r="I139" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -7254,11 +7254,11 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7273,17 +7273,17 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140" t="n">
         <v>6</v>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -7303,11 +7303,11 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7317,22 +7317,22 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>11, 28, 38, 41, 44, 53</t>
+          <t>10, 35, 41, 51, 53, 60</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" t="n">
         <v>6</v>
       </c>
       <c r="I141" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -7352,11 +7352,11 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -7401,11 +7401,11 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7420,17 +7420,17 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H143" t="n">
         <v>6</v>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -7450,11 +7450,11 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -7499,11 +7499,11 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>10, 11, 27, 33, 37, 53</t>
+          <t>05, 10, 27, 33, 43, 53</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -7548,11 +7548,11 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7567,17 +7567,17 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146" t="n">
         <v>6</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -7597,11 +7597,11 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -7646,11 +7646,11 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H148" t="n">
         <v>6</v>
       </c>
       <c r="I148" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -7695,11 +7695,11 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>10, 35, 41, 51, 53, 60</t>
+          <t>05, 06, 10, 35, 44, 54</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -7744,11 +7744,11 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -7793,11 +7793,11 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7812,17 +7812,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H151" t="n">
         <v>6</v>
       </c>
       <c r="I151" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -7842,11 +7842,11 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -7891,11 +7891,11 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>05, 10, 27, 33, 43, 53</t>
+          <t>05, 06, 10, 27, 37, 53</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -7940,11 +7940,11 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7954,22 +7954,22 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>11, 32, 34, 42, 46, 58</t>
+          <t>11, 14, 32, 34, 42, 46</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H154" t="n">
         <v>6</v>
       </c>
       <c r="I154" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -7989,11 +7989,11 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H155" t="n">
         <v>6</v>
       </c>
       <c r="I155" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -8038,11 +8038,11 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>06, 11, 17, 27, 30, 43</t>
+          <t>06, 11, 17, 27, 43, 58</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -8087,11 +8087,11 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>05, 06, 10, 35, 44, 54</t>
+          <t>10, 12, 16, 35, 41, 44</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -8136,11 +8136,11 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -8185,11 +8185,11 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -8234,11 +8234,11 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -8283,11 +8283,11 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8297,12 +8297,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>05, 06, 10, 27, 37, 53</t>
+          <t>05, 10, 27, 33, 37, 43</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G161" t="n">

--- a/excel/historico_acertos_modelos.xlsx
+++ b/excel/historico_acertos_modelos.xlsx
@@ -492,11 +492,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01, 11, 36, 43, 48, 49</t>
+          <t>14, 21, 25, 40, 51, 56</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -541,11 +541,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>01, 11, 36, 43, 48, 49</t>
+          <t>14, 21, 25, 40, 51, 56</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -590,11 +590,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,22 +604,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>06, 11, 17, 27, 30, 58</t>
+          <t>06, 11, 27, 30, 43, 58</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>01, 11, 36, 43, 48, 49</t>
+          <t>14, 21, 25, 40, 51, 56</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -639,11 +639,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -653,22 +653,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10, 25, 27, 38, 43, 53</t>
+          <t>10, 27, 37, 38, 44, 53</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>01, 11, 36, 43, 48, 49</t>
+          <t>14, 21, 25, 40, 51, 56</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -688,11 +688,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01, 11, 36, 43, 48, 49</t>
+          <t>14, 21, 25, 40, 51, 56</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -737,11 +737,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -751,22 +751,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>06, 11, 17, 27, 30, 58</t>
+          <t>06, 11, 27, 30, 43, 58</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01, 11, 36, 43, 48, 49</t>
+          <t>14, 21, 25, 40, 51, 56</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -786,11 +786,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>01, 11, 36, 43, 48, 49</t>
+          <t>14, 21, 25, 40, 51, 56</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -835,11 +835,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -854,17 +854,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>01, 11, 36, 43, 48, 49</t>
+          <t>14, 21, 25, 40, 51, 56</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -884,11 +884,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>02, 04, 16, 21, 48, 53</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -933,11 +933,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>02, 04, 16, 21, 48, 53</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -982,11 +982,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>02, 04, 16, 21, 48, 53</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1031,11 +1031,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10, 27, 37, 38, 44, 53</t>
+          <t>10, 24, 35, 49, 53, 56</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>02, 04, 16, 21, 48, 53</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1080,11 +1080,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>02, 04, 16, 21, 48, 53</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1129,11 +1129,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>06, 11, 27, 30, 43, 58</t>
+          <t>11, 14, 27, 30, 43, 58</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>02, 04, 16, 21, 48, 53</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1178,11 +1178,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>02, 04, 16, 21, 48, 53</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1246,17 +1246,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>02, 04, 16, 21, 48, 53</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1276,11 +1276,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>09, 19, 27, 32, 41, 45</t>
+          <t>09, 19, 27, 32, 41, 42</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1325,11 +1325,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1374,11 +1374,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1423,11 +1423,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1437,22 +1437,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>10, 24, 35, 49, 53, 56</t>
+          <t>04, 10, 27, 35, 36, 38</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>6</v>
       </c>
       <c r="I21" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1472,11 +1472,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1521,11 +1521,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1540,17 +1540,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1570,11 +1570,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1619,11 +1619,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1668,11 +1668,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1717,11 +1717,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1766,11 +1766,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>06, 11, 27, 30, 43, 58</t>
+          <t>06, 11, 14, 27, 30, 58</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1815,11 +1815,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1829,22 +1829,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>04, 10, 27, 35, 36, 38</t>
+          <t>10, 11, 16, 23, 27, 35</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
         <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1864,11 +1864,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1913,11 +1913,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1962,11 +1962,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2011,11 +2011,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10, 27, 33, 37, 43, 53</t>
+          <t>10, 11, 27, 33, 37, 43</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2060,11 +2060,11 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2109,11 +2109,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2158,11 +2158,11 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2177,17 +2177,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2207,11 +2207,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2221,22 +2221,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>10, 11, 16, 23, 27, 35</t>
+          <t>04, 08, 11, 13, 33, 60</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2256,11 +2256,11 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2305,11 +2305,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2354,11 +2354,11 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>10, 33, 37, 42, 43, 53</t>
+          <t>05, 10, 33, 37, 42, 53</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2403,11 +2403,11 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2417,22 +2417,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>10, 11, 27, 33, 37, 43</t>
+          <t>05, 10, 11, 27, 33, 53</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>6</v>
       </c>
       <c r="I41" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2452,11 +2452,11 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>09, 19, 27, 32, 41, 42</t>
+          <t>09, 19, 27, 32, 42, 58</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2501,11 +2501,11 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2550,11 +2550,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2569,17 +2569,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>6</v>
       </c>
       <c r="I44" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2599,11 +2599,11 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>04, 08, 11, 13, 33, 60</t>
+          <t>04, 06, 08, 11, 27, 49</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2648,11 +2648,11 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2697,11 +2697,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>11, 14, 27, 30, 43, 58</t>
+          <t>06, 11, 14, 27, 30, 58</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -2746,11 +2746,11 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2795,11 +2795,11 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2809,22 +2809,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>05, 10, 11, 27, 33, 53</t>
+          <t>06, 10, 11, 27, 33, 37</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
         <v>6</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2844,11 +2844,11 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2863,17 +2863,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
         <v>6</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2893,11 +2893,11 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2912,17 +2912,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" t="n">
         <v>6</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2942,11 +2942,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2961,17 +2961,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" t="n">
         <v>6</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2991,11 +2991,11 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3005,22 +3005,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>04, 06, 08, 11, 27, 49</t>
+          <t>11, 13, 25, 33, 53, 56</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
         <v>6</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3040,11 +3040,11 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3089,11 +3089,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3108,17 +3108,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
         <v>6</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3138,11 +3138,11 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3187,11 +3187,11 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>06, 10, 11, 27, 33, 37</t>
+          <t>10, 11, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3236,11 +3236,11 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>09, 19, 27, 32, 42, 58</t>
+          <t>19, 27, 32, 41, 42, 45</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -3285,11 +3285,11 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>09, 19, 32, 34, 41, 45</t>
+          <t>19, 32, 34, 41, 45, 59</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -3334,11 +3334,11 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3348,22 +3348,22 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>06, 11, 14, 27, 30, 58</t>
+          <t>06, 11, 14, 17, 27, 58</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
         <v>6</v>
       </c>
       <c r="I60" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3383,11 +3383,11 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3397,22 +3397,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>11, 13, 25, 33, 53, 56</t>
+          <t>05, 15, 25, 33, 36, 56</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H61" t="n">
         <v>6</v>
       </c>
       <c r="I61" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3432,11 +3432,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -3481,11 +3481,11 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3495,22 +3495,22 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>06, 11, 14, 27, 30, 58</t>
+          <t>06, 11, 14, 17, 27, 38</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>6</v>
       </c>
       <c r="I63" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3530,11 +3530,11 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -3579,11 +3579,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>10, 11, 27, 33, 37, 53</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -3628,11 +3628,11 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>19, 27, 32, 41, 42, 45</t>
+          <t>19, 27, 32, 42, 45, 46</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -3677,11 +3677,11 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3691,22 +3691,22 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>19, 32, 34, 41, 45, 59</t>
+          <t>19, 32, 34, 45, 46, 59</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>6</v>
       </c>
       <c r="I67" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3726,11 +3726,11 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3740,22 +3740,22 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>06, 11, 14, 17, 27, 58</t>
+          <t>06, 11, 14, 27, 43, 58</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" t="n">
         <v>6</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3775,11 +3775,11 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3789,22 +3789,22 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>05, 15, 25, 33, 36, 56</t>
+          <t>23, 24, 41, 43, 53, 56</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>6</v>
       </c>
       <c r="I69" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3824,11 +3824,11 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3843,17 +3843,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70" t="n">
         <v>6</v>
       </c>
       <c r="I70" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3873,11 +3873,11 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3887,22 +3887,22 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>06, 11, 14, 17, 27, 38</t>
+          <t>06, 11, 14, 17, 27, 43</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="n">
         <v>6</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3922,11 +3922,11 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -3971,11 +3971,11 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>05, 10, 27, 33, 37, 53</t>
+          <t>05, 27, 33, 37, 43, 53</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -4020,11 +4020,11 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4034,22 +4034,22 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>19, 27, 32, 42, 45, 46</t>
+          <t>19, 32, 42, 45, 46, 58</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
         <v>6</v>
       </c>
       <c r="I74" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -4069,11 +4069,11 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -4118,11 +4118,11 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4137,17 +4137,17 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
         <v>6</v>
       </c>
       <c r="I76" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -4167,11 +4167,11 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>23, 24, 41, 43, 53, 56</t>
+          <t>04, 10, 17, 23, 41, 56</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
         <v>6</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -4216,11 +4216,11 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -4265,11 +4265,11 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
         <v>6</v>
       </c>
       <c r="I79" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -4314,11 +4314,11 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4333,17 +4333,17 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H80" t="n">
         <v>6</v>
       </c>
       <c r="I80" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -4363,11 +4363,11 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4377,22 +4377,22 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>05, 27, 33, 37, 43, 53</t>
+          <t>10, 17, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H81" t="n">
         <v>6</v>
       </c>
       <c r="I81" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -4412,11 +4412,11 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -4461,11 +4461,11 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -4510,11 +4510,11 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4524,22 +4524,22 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>06, 11, 14, 27, 43, 58</t>
+          <t>06, 11, 27, 30, 43, 58</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
         <v>6</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -4559,11 +4559,11 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4573,22 +4573,22 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>04, 10, 17, 23, 41, 56</t>
+          <t>17, 23, 27, 36, 37, 41</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
         <v>6</v>
       </c>
       <c r="I85" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -4608,11 +4608,11 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4622,22 +4622,22 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>05, 10, 27, 33, 37, 53</t>
+          <t>05, 10, 27, 37, 38, 53</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
         <v>6</v>
       </c>
       <c r="I86" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -4657,11 +4657,11 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>06, 11, 14, 17, 27, 43</t>
+          <t>11, 14, 27, 30, 38, 43</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -4706,11 +4706,11 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4720,22 +4720,22 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>05, 10, 33, 37, 42, 53</t>
+          <t>05, 10, 37, 38, 42, 53</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
         <v>6</v>
       </c>
       <c r="I88" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -4755,11 +4755,11 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4769,22 +4769,22 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>10, 17, 27, 33, 37, 53</t>
+          <t>05, 10, 27, 37, 38, 53</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
         <v>6</v>
       </c>
       <c r="I89" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -4804,11 +4804,11 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -4853,11 +4853,11 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -4902,11 +4902,11 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4916,22 +4916,22 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>06, 11, 27, 30, 43, 58</t>
+          <t>06, 11, 27, 30, 48, 58</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
         <v>6</v>
       </c>
       <c r="I92" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -4951,11 +4951,11 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4965,22 +4965,22 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>17, 23, 27, 36, 37, 41</t>
+          <t>04, 06, 11, 23, 35, 37</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" t="n">
         <v>6</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -5000,11 +5000,11 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -5049,11 +5049,11 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>11, 14, 27, 30, 38, 43</t>
+          <t>06, 11, 14, 27, 30, 38</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -5098,11 +5098,11 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -5147,11 +5147,11 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>05, 10, 27, 37, 38, 53</t>
+          <t>06, 11, 27, 37, 38, 53</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -5196,11 +5196,11 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -5245,11 +5245,11 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -5294,11 +5294,11 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>06, 11, 27, 30, 48, 58</t>
+          <t>06, 11, 17, 27, 30, 58</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -5343,11 +5343,11 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5357,22 +5357,22 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>04, 06, 11, 23, 35, 37</t>
+          <t>05, 11, 23, 37, 41, 56</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
         <v>6</v>
       </c>
       <c r="I101" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -5392,11 +5392,11 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>05, 10, 27, 37, 38, 53</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102" t="n">
         <v>6</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -5441,11 +5441,11 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5455,12 +5455,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>06, 11, 14, 27, 30, 38</t>
+          <t>06, 11, 17, 27, 30, 38</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -5490,11 +5490,11 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5504,22 +5504,22 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>05, 10, 37, 38, 42, 53</t>
+          <t>05, 10, 33, 37, 42, 53</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104" t="n">
         <v>6</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -5539,11 +5539,11 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5553,22 +5553,22 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>06, 11, 27, 37, 38, 53</t>
+          <t>05, 10, 11, 27, 33, 37</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
         <v>6</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -5588,11 +5588,11 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5607,17 +5607,17 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106" t="n">
         <v>6</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -5637,11 +5637,11 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5656,17 +5656,17 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" t="n">
         <v>6</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -5686,11 +5686,11 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>06, 11, 17, 27, 30, 58</t>
+          <t>06, 11, 17, 27, 30, 43</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -5735,11 +5735,11 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5749,22 +5749,22 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>05, 11, 23, 37, 41, 56</t>
+          <t>05, 11, 41, 43, 53, 56</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" t="n">
         <v>6</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -5784,11 +5784,11 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -5833,11 +5833,11 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>06, 11, 17, 27, 30, 38</t>
+          <t>06, 10, 11, 17, 27, 43</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -5882,11 +5882,11 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -5931,11 +5931,11 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>05, 10, 11, 27, 33, 37</t>
+          <t>05, 10, 11, 27, 43, 53</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -5980,11 +5980,11 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5994,12 +5994,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>19, 32, 42, 45, 46, 58</t>
+          <t>32, 42, 45, 46, 54, 58</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -6029,11 +6029,11 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6043,22 +6043,22 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>19, 32, 34, 45, 46, 59</t>
+          <t>12, 32, 34, 45, 46, 59</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
         <v>6</v>
       </c>
       <c r="I115" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -6078,11 +6078,11 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6097,17 +6097,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H116" t="n">
         <v>6</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -6127,11 +6127,11 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6141,12 +6141,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>05, 11, 41, 43, 53, 56</t>
+          <t>05, 11, 27, 28, 41, 53</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -6176,11 +6176,11 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -6225,11 +6225,11 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6244,17 +6244,17 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H119" t="n">
         <v>6</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -6274,11 +6274,11 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
         <v>6</v>
       </c>
       <c r="I120" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -6323,11 +6323,11 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>05, 10, 11, 27, 43, 53</t>
+          <t>05, 10, 11, 27, 37, 53</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -6372,11 +6372,11 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>32, 42, 45, 46, 54, 58</t>
+          <t>11, 32, 42, 45, 46, 58</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -6421,11 +6421,11 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6440,17 +6440,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H123" t="n">
         <v>6</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -6470,11 +6470,11 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6489,17 +6489,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
         <v>6</v>
       </c>
       <c r="I124" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -6519,11 +6519,11 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>05, 11, 27, 28, 41, 53</t>
+          <t>11, 28, 38, 41, 44, 53</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -6568,11 +6568,11 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6587,17 +6587,17 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
         <v>6</v>
       </c>
       <c r="I126" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -6617,11 +6617,11 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
         <v>6</v>
       </c>
       <c r="I127" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -6666,11 +6666,11 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>05, 10, 33, 37, 42, 53</t>
+          <t>05, 10, 33, 37, 43, 53</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -6715,11 +6715,11 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6729,22 +6729,22 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>05, 10, 11, 27, 37, 53</t>
+          <t>10, 11, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H129" t="n">
         <v>6</v>
       </c>
       <c r="I129" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -6764,11 +6764,11 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6778,22 +6778,22 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>11, 32, 42, 45, 46, 58</t>
+          <t>11, 32, 34, 42, 46, 58</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
         <v>6</v>
       </c>
       <c r="I130" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -6813,11 +6813,11 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6827,22 +6827,22 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>12, 32, 34, 45, 46, 59</t>
+          <t>03, 32, 34, 42, 46, 59</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
         <v>6</v>
       </c>
       <c r="I131" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -6862,11 +6862,11 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6881,17 +6881,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H132" t="n">
         <v>6</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -6911,11 +6911,11 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6925,22 +6925,22 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>11, 28, 38, 41, 44, 53</t>
+          <t>10, 35, 41, 51, 53, 60</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H133" t="n">
         <v>6</v>
       </c>
       <c r="I133" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -6960,11 +6960,11 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -7009,11 +7009,11 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7028,17 +7028,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H135" t="n">
         <v>6</v>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -7058,11 +7058,11 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -7107,11 +7107,11 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>10, 11, 27, 33, 37, 53</t>
+          <t>05, 10, 27, 33, 43, 53</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -7156,11 +7156,11 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7175,17 +7175,17 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H138" t="n">
         <v>6</v>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -7205,11 +7205,11 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -7254,11 +7254,11 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7273,17 +7273,17 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H140" t="n">
         <v>6</v>
       </c>
       <c r="I140" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -7303,11 +7303,11 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7317,12 +7317,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>10, 35, 41, 51, 53, 60</t>
+          <t>05, 06, 10, 35, 44, 54</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -7352,11 +7352,11 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -7401,11 +7401,11 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7420,17 +7420,17 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143" t="n">
         <v>6</v>
       </c>
       <c r="I143" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -7450,11 +7450,11 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -7499,11 +7499,11 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>05, 10, 27, 33, 43, 53</t>
+          <t>05, 06, 10, 27, 37, 53</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -7548,11 +7548,11 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7562,22 +7562,22 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>11, 32, 34, 42, 46, 58</t>
+          <t>11, 14, 32, 34, 42, 46</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H146" t="n">
         <v>6</v>
       </c>
       <c r="I146" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -7597,11 +7597,11 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7616,17 +7616,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H147" t="n">
         <v>6</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -7646,11 +7646,11 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7660,12 +7660,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>06, 11, 17, 27, 30, 43</t>
+          <t>06, 11, 17, 27, 43, 58</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -7695,11 +7695,11 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>05, 06, 10, 35, 44, 54</t>
+          <t>10, 12, 16, 35, 41, 44</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -7744,11 +7744,11 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -7793,11 +7793,11 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -7842,11 +7842,11 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -7891,11 +7891,11 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>05, 06, 10, 27, 37, 53</t>
+          <t>05, 10, 27, 33, 37, 43</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -7940,11 +7940,11 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7954,22 +7954,22 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>11, 14, 32, 34, 42, 46</t>
+          <t>11, 14, 27, 32, 42, 46</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>02, 03, 20, 25, 39, 57</t>
+          <t>07, 10, 14, 27, 36, 55</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H154" t="n">
         <v>6</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -7989,11 +7989,11 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -8003,22 +8003,22 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>03, 32, 34, 42, 46, 59</t>
+          <t>26, 32, 34, 42, 46, 59</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>02, 03, 20, 25, 39, 57</t>
+          <t>07, 10, 14, 27, 36, 55</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H155" t="n">
         <v>6</v>
       </c>
       <c r="I155" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -8038,11 +8038,11 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -8057,17 +8057,17 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>02, 03, 20, 25, 39, 57</t>
+          <t>07, 10, 14, 27, 36, 55</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H156" t="n">
         <v>6</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -8087,11 +8087,11 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -8101,22 +8101,22 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>10, 12, 16, 35, 41, 44</t>
+          <t>05, 10, 41, 44, 45, 53</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>02, 03, 20, 25, 39, 57</t>
+          <t>07, 10, 14, 27, 36, 55</t>
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H157" t="n">
         <v>6</v>
       </c>
       <c r="I157" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -8136,11 +8136,11 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -8155,17 +8155,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>02, 03, 20, 25, 39, 57</t>
+          <t>07, 10, 14, 27, 36, 55</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H158" t="n">
         <v>6</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -8185,11 +8185,11 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -8204,17 +8204,17 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>02, 03, 20, 25, 39, 57</t>
+          <t>07, 10, 14, 27, 36, 55</t>
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H159" t="n">
         <v>6</v>
       </c>
       <c r="I159" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -8234,11 +8234,11 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -8253,17 +8253,17 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>02, 03, 20, 25, 39, 57</t>
+          <t>07, 10, 14, 27, 36, 55</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H160" t="n">
         <v>6</v>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -8283,11 +8283,11 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8297,22 +8297,22 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>05, 10, 27, 33, 37, 43</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>02, 03, 20, 25, 39, 57</t>
+          <t>07, 10, 14, 27, 36, 55</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H161" t="n">
         <v>6</v>
       </c>
       <c r="I161" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>

--- a/excel/historico_acertos_modelos.xlsx
+++ b/excel/historico_acertos_modelos.xlsx
@@ -492,11 +492,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3056</v>
+        <v>3058</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>09, 19, 27, 32, 41, 45</t>
+          <t>09, 19, 27, 32, 41, 42</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -541,11 +541,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3056</v>
+        <v>3058</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -590,11 +590,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3056</v>
+        <v>3058</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -639,11 +639,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3056</v>
+        <v>3058</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -653,12 +653,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10, 27, 37, 38, 44, 53</t>
+          <t>04, 10, 27, 35, 36, 38</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -688,11 +688,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3056</v>
+        <v>3058</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -737,11 +737,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3056</v>
+        <v>3058</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -751,22 +751,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>06, 11, 27, 30, 43, 58</t>
+          <t>11, 14, 27, 30, 43, 58</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -786,11 +786,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3056</v>
+        <v>3058</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -835,11 +835,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3056</v>
+        <v>3058</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -854,17 +854,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14, 21, 25, 40, 51, 56</t>
+          <t>14, 23, 53, 56, 57, 60</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -884,11 +884,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3057</v>
+        <v>3059</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>09, 19, 27, 32, 41, 45</t>
+          <t>09, 19, 27, 32, 41, 42</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -933,11 +933,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3057</v>
+        <v>3059</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -982,11 +982,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3057</v>
+        <v>3059</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>06, 11, 27, 30, 43, 58</t>
+          <t>06, 11, 14, 27, 30, 58</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1031,11 +1031,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3057</v>
+        <v>3059</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1045,12 +1045,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10, 24, 35, 49, 53, 56</t>
+          <t>10, 11, 16, 23, 27, 35</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1080,11 +1080,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3057</v>
+        <v>3059</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1129,11 +1129,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3057</v>
+        <v>3059</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1178,11 +1178,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3057</v>
+        <v>3059</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1227,11 +1227,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3057</v>
+        <v>3059</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10, 27, 33, 37, 43, 53</t>
+          <t>10, 11, 27, 33, 37, 43</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>02, 04, 16, 21, 48, 53</t>
+          <t>01, 02, 07, 18, 33, 35</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1276,11 +1276,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3058</v>
+        <v>3060</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1325,11 +1325,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3058</v>
+        <v>3060</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1374,11 +1374,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3058</v>
+        <v>3060</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>06, 11, 27, 30, 43, 58</t>
+          <t>06, 11, 14, 27, 30, 58</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
         <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1423,11 +1423,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3058</v>
+        <v>3060</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>04, 10, 27, 35, 36, 38</t>
+          <t>04, 08, 11, 13, 33, 60</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1472,11 +1472,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3058</v>
+        <v>3060</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1521,11 +1521,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3058</v>
+        <v>3060</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1540,17 +1540,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1570,11 +1570,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3058</v>
+        <v>3060</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10, 33, 37, 42, 43, 53</t>
+          <t>05, 10, 33, 37, 42, 53</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1619,11 +1619,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3058</v>
+        <v>3060</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1633,22 +1633,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10, 27, 33, 37, 43, 53</t>
+          <t>05, 10, 11, 27, 33, 53</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14, 23, 53, 56, 57, 60</t>
+          <t>06, 15, 23, 36, 37, 38</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1668,11 +1668,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3059</v>
+        <v>3061</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>09, 19, 27, 32, 41, 42</t>
+          <t>09, 19, 27, 32, 42, 58</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1717,11 +1717,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3059</v>
+        <v>3061</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1766,11 +1766,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3059</v>
+        <v>3061</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1815,11 +1815,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3059</v>
+        <v>3061</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1829,22 +1829,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10, 11, 16, 23, 27, 35</t>
+          <t>04, 06, 08, 11, 27, 49</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1864,11 +1864,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3059</v>
+        <v>3061</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1913,11 +1913,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3059</v>
+        <v>3061</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11, 14, 27, 30, 43, 58</t>
+          <t>06, 11, 14, 27, 30, 58</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -1962,11 +1962,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3059</v>
+        <v>3061</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>10, 33, 37, 42, 43, 53</t>
+          <t>05, 10, 33, 37, 42, 53</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2011,11 +2011,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3059</v>
+        <v>3061</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10, 11, 27, 33, 37, 43</t>
+          <t>06, 10, 11, 27, 33, 37</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>01, 02, 07, 18, 33, 35</t>
+          <t>24, 25, 28, 37, 47, 55</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2060,11 +2060,11 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3060</v>
+        <v>3062</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2074,22 +2074,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>09, 19, 27, 32, 41, 42</t>
+          <t>09, 19, 27, 32, 42, 58</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
         <v>6</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2109,11 +2109,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3060</v>
+        <v>3062</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2128,17 +2128,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
         <v>6</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2158,11 +2158,11 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3060</v>
+        <v>3062</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2207,11 +2207,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3060</v>
+        <v>3062</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2221,22 +2221,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>04, 08, 11, 13, 33, 60</t>
+          <t>11, 13, 25, 33, 53, 56</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
         <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2256,11 +2256,11 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3060</v>
+        <v>3062</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2305,11 +2305,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3060</v>
+        <v>3062</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2319,22 +2319,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>11, 14, 27, 30, 43, 58</t>
+          <t>06, 11, 14, 27, 30, 58</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
         <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2354,11 +2354,11 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3060</v>
+        <v>3062</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2403,11 +2403,11 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3060</v>
+        <v>3062</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2417,22 +2417,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>05, 10, 11, 27, 33, 53</t>
+          <t>10, 11, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>06, 15, 23, 36, 37, 38</t>
+          <t>05, 09, 11, 17, 18, 38</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
         <v>6</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2452,11 +2452,11 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3061</v>
+        <v>3063</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2466,22 +2466,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>09, 19, 27, 32, 42, 58</t>
+          <t>19, 27, 32, 41, 42, 45</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
         <v>6</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2501,11 +2501,11 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3061</v>
+        <v>3063</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>09, 19, 32, 34, 41, 45</t>
+          <t>19, 32, 34, 41, 45, 59</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
         <v>6</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2550,11 +2550,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3061</v>
+        <v>3063</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>06, 11, 14, 27, 30, 58</t>
+          <t>06, 11, 14, 17, 27, 58</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2599,11 +2599,11 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3061</v>
+        <v>3063</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2613,22 +2613,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>04, 06, 08, 11, 27, 49</t>
+          <t>05, 15, 25, 33, 36, 56</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
         <v>6</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2648,11 +2648,11 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3061</v>
+        <v>3063</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2697,11 +2697,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3061</v>
+        <v>3063</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>06, 11, 14, 27, 30, 58</t>
+          <t>06, 11, 14, 17, 27, 38</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -2746,11 +2746,11 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3061</v>
+        <v>3063</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2795,11 +2795,11 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3061</v>
+        <v>3063</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>06, 10, 11, 27, 33, 37</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>24, 25, 28, 37, 47, 55</t>
+          <t>05, 35, 36, 41, 43, 48</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2844,11 +2844,11 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3062</v>
+        <v>3064</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>09, 19, 27, 32, 42, 58</t>
+          <t>19, 27, 32, 42, 45, 46</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -2893,11 +2893,11 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3062</v>
+        <v>3064</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2907,22 +2907,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>09, 19, 32, 34, 41, 45</t>
+          <t>19, 32, 34, 45, 46, 59</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>6</v>
       </c>
       <c r="I51" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2942,11 +2942,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3062</v>
+        <v>3064</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>06, 11, 14, 27, 30, 58</t>
+          <t>06, 11, 14, 27, 43, 58</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -2991,11 +2991,11 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3062</v>
+        <v>3064</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3005,22 +3005,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>11, 13, 25, 33, 53, 56</t>
+          <t>23, 24, 41, 43, 53, 56</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>6</v>
       </c>
       <c r="I53" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3040,11 +3040,11 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3062</v>
+        <v>3064</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3059,17 +3059,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
         <v>6</v>
       </c>
       <c r="I54" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3089,11 +3089,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3062</v>
+        <v>3064</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>06, 11, 14, 27, 30, 58</t>
+          <t>06, 11, 14, 17, 27, 43</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3138,11 +3138,11 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3062</v>
+        <v>3064</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3187,11 +3187,11 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3062</v>
+        <v>3064</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>10, 11, 27, 33, 37, 53</t>
+          <t>05, 27, 33, 37, 43, 53</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>05, 09, 11, 17, 18, 38</t>
+          <t>04, 10, 20, 25, 27, 48</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3236,11 +3236,11 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3063</v>
+        <v>3065</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3250,22 +3250,22 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>19, 27, 32, 41, 42, 45</t>
+          <t>19, 32, 42, 45, 46, 58</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
         <v>6</v>
       </c>
       <c r="I58" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3285,11 +3285,11 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3063</v>
+        <v>3065</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3299,22 +3299,22 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>19, 32, 34, 41, 45, 59</t>
+          <t>19, 32, 34, 45, 46, 59</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
         <v>6</v>
       </c>
       <c r="I59" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3334,11 +3334,11 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3063</v>
+        <v>3065</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>06, 11, 14, 17, 27, 58</t>
+          <t>06, 11, 14, 27, 43, 58</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3383,11 +3383,11 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3063</v>
+        <v>3065</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3397,22 +3397,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>05, 15, 25, 33, 36, 56</t>
+          <t>04, 10, 17, 23, 41, 56</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
         <v>6</v>
       </c>
       <c r="I61" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3432,11 +3432,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3063</v>
+        <v>3065</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3451,17 +3451,17 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62" t="n">
         <v>6</v>
       </c>
       <c r="I62" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3481,11 +3481,11 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3063</v>
+        <v>3065</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>06, 11, 14, 17, 27, 38</t>
+          <t>06, 11, 14, 17, 27, 43</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -3530,11 +3530,11 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3063</v>
+        <v>3065</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64" t="n">
         <v>6</v>
       </c>
       <c r="I64" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3579,11 +3579,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3063</v>
+        <v>3065</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>27/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3593,22 +3593,22 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>05, 10, 27, 33, 37, 53</t>
+          <t>10, 17, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>05, 35, 36, 41, 43, 48</t>
+          <t>08, 10, 30, 38, 50, 53</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65" t="n">
         <v>6</v>
       </c>
       <c r="I65" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3628,11 +3628,11 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3064</v>
+        <v>3066</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3642,22 +3642,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>19, 27, 32, 42, 45, 46</t>
+          <t>19, 32, 42, 45, 46, 58</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
         <v>6</v>
       </c>
       <c r="I66" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3677,11 +3677,11 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3064</v>
+        <v>3066</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -3726,11 +3726,11 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>3064</v>
+        <v>3066</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>06, 11, 14, 27, 43, 58</t>
+          <t>06, 11, 27, 30, 43, 58</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -3775,11 +3775,11 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3064</v>
+        <v>3066</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>23, 24, 41, 43, 53, 56</t>
+          <t>17, 23, 27, 36, 37, 41</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -3824,11 +3824,11 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3064</v>
+        <v>3066</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3838,22 +3838,22 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>05, 10, 27, 33, 37, 53</t>
+          <t>05, 10, 27, 37, 38, 53</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
         <v>6</v>
       </c>
       <c r="I70" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3873,11 +3873,11 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3064</v>
+        <v>3066</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3887,22 +3887,22 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>06, 11, 14, 17, 27, 43</t>
+          <t>11, 14, 27, 30, 38, 43</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
         <v>6</v>
       </c>
       <c r="I71" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3922,11 +3922,11 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3064</v>
+        <v>3066</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3936,22 +3936,22 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>05, 10, 33, 37, 42, 53</t>
+          <t>05, 10, 37, 38, 42, 53</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
         <v>6</v>
       </c>
       <c r="I72" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3971,11 +3971,11 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3064</v>
+        <v>3066</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3985,22 +3985,22 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>05, 27, 33, 37, 43, 53</t>
+          <t>05, 10, 27, 37, 38, 53</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>04, 10, 20, 25, 27, 48</t>
+          <t>04, 06, 09, 13, 28, 48</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
         <v>6</v>
       </c>
       <c r="I73" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -4020,11 +4020,11 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3065</v>
+        <v>3067</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -4069,11 +4069,11 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3065</v>
+        <v>3067</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -4118,11 +4118,11 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3065</v>
+        <v>3067</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4132,12 +4132,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>06, 11, 14, 27, 43, 58</t>
+          <t>06, 11, 27, 30, 48, 58</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -4167,11 +4167,11 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3065</v>
+        <v>3067</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>04, 10, 17, 23, 41, 56</t>
+          <t>04, 06, 11, 23, 35, 37</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -4216,11 +4216,11 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3065</v>
+        <v>3067</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4230,22 +4230,22 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>05, 10, 27, 33, 37, 53</t>
+          <t>05, 10, 27, 37, 38, 53</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
         <v>6</v>
       </c>
       <c r="I78" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -4265,11 +4265,11 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3065</v>
+        <v>3067</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>06, 11, 14, 17, 27, 43</t>
+          <t>06, 11, 14, 27, 30, 38</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -4314,11 +4314,11 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3065</v>
+        <v>3067</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4328,22 +4328,22 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>05, 10, 33, 37, 42, 53</t>
+          <t>05, 10, 37, 38, 42, 53</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
         <v>6</v>
       </c>
       <c r="I80" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -4363,11 +4363,11 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3065</v>
+        <v>3067</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4377,22 +4377,22 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>10, 17, 27, 33, 37, 53</t>
+          <t>06, 11, 27, 37, 38, 53</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>08, 10, 30, 38, 50, 53</t>
+          <t>01, 04, 17, 33, 41, 52</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
         <v>6</v>
       </c>
       <c r="I81" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -4412,11 +4412,11 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3066</v>
+        <v>3068</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -4461,11 +4461,11 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3066</v>
+        <v>3068</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -4510,11 +4510,11 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3066</v>
+        <v>3068</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4524,22 +4524,22 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>06, 11, 27, 30, 43, 58</t>
+          <t>06, 11, 17, 27, 30, 58</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
         <v>6</v>
       </c>
       <c r="I84" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -4559,11 +4559,11 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3066</v>
+        <v>3068</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>17, 23, 27, 36, 37, 41</t>
+          <t>05, 11, 23, 37, 41, 56</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -4608,11 +4608,11 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3066</v>
+        <v>3068</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4622,22 +4622,22 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>05, 10, 27, 37, 38, 53</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
         <v>6</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -4657,11 +4657,11 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3066</v>
+        <v>3068</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>11, 14, 27, 30, 38, 43</t>
+          <t>06, 11, 17, 27, 30, 38</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -4706,11 +4706,11 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3066</v>
+        <v>3068</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4720,22 +4720,22 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>05, 10, 37, 38, 42, 53</t>
+          <t>05, 10, 33, 37, 42, 53</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
         <v>6</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -4755,11 +4755,11 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3066</v>
+        <v>3068</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4769,22 +4769,22 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>05, 10, 27, 37, 38, 53</t>
+          <t>05, 10, 11, 27, 33, 37</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>04, 06, 09, 13, 28, 48</t>
+          <t>07, 10, 39, 40, 43, 57</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
         <v>6</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -4804,11 +4804,11 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3067</v>
+        <v>3069</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4823,17 +4823,17 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
         <v>6</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -4853,11 +4853,11 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3067</v>
+        <v>3069</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4872,17 +4872,17 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
         <v>6</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -4902,11 +4902,11 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3067</v>
+        <v>3069</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4916,12 +4916,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>06, 11, 27, 30, 48, 58</t>
+          <t>06, 11, 17, 27, 30, 43</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -4951,11 +4951,11 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3067</v>
+        <v>3069</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>04, 06, 11, 23, 35, 37</t>
+          <t>05, 11, 41, 43, 53, 56</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -5000,11 +5000,11 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3067</v>
+        <v>3069</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>05, 10, 27, 37, 38, 53</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" t="n">
         <v>6</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -5049,11 +5049,11 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3067</v>
+        <v>3069</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>06, 11, 14, 27, 30, 38</t>
+          <t>06, 10, 11, 17, 27, 43</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -5098,11 +5098,11 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>3067</v>
+        <v>3069</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5112,22 +5112,22 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>05, 10, 37, 38, 42, 53</t>
+          <t>05, 10, 33, 37, 42, 53</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
         <v>6</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -5147,11 +5147,11 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>3067</v>
+        <v>3069</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5161,22 +5161,22 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>06, 11, 27, 37, 38, 53</t>
+          <t>05, 10, 11, 27, 43, 53</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>01, 04, 17, 33, 41, 52</t>
+          <t>05, 19, 22, 44, 47, 57</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97" t="n">
         <v>6</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -5196,11 +5196,11 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>3068</v>
+        <v>3070</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5210,22 +5210,22 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>19, 32, 42, 45, 46, 58</t>
+          <t>32, 42, 45, 46, 54, 58</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
         <v>6</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -5245,11 +5245,11 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>3068</v>
+        <v>3070</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>19, 32, 34, 45, 46, 59</t>
+          <t>12, 32, 34, 45, 46, 59</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -5294,11 +5294,11 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>3068</v>
+        <v>3070</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5308,22 +5308,22 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>06, 11, 17, 27, 30, 58</t>
+          <t>06, 11, 17, 27, 30, 43</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H100" t="n">
         <v>6</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -5343,11 +5343,11 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>3068</v>
+        <v>3070</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5357,22 +5357,22 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>05, 11, 23, 37, 41, 56</t>
+          <t>05, 11, 27, 28, 41, 53</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
         <v>6</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -5392,11 +5392,11 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>3068</v>
+        <v>3070</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -5441,11 +5441,11 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3068</v>
+        <v>3070</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5455,22 +5455,22 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>06, 11, 17, 27, 30, 38</t>
+          <t>06, 10, 11, 17, 27, 43</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H103" t="n">
         <v>6</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -5490,11 +5490,11 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>3068</v>
+        <v>3070</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5509,17 +5509,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H104" t="n">
         <v>6</v>
       </c>
       <c r="I104" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -5539,11 +5539,11 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>3068</v>
+        <v>3070</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>05, 10, 11, 27, 33, 37</t>
+          <t>05, 10, 11, 27, 37, 53</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>07, 10, 39, 40, 43, 57</t>
+          <t>19, 27, 29, 43, 54, 60</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -5588,11 +5588,11 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3069</v>
+        <v>3071</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>19, 32, 42, 45, 46, 58</t>
+          <t>11, 32, 42, 45, 46, 58</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -5637,11 +5637,11 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>3069</v>
+        <v>3071</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5651,22 +5651,22 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>19, 32, 34, 45, 46, 59</t>
+          <t>12, 32, 34, 45, 46, 59</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H107" t="n">
         <v>6</v>
       </c>
       <c r="I107" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -5686,11 +5686,11 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3069</v>
+        <v>3071</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -5735,11 +5735,11 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3069</v>
+        <v>3071</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>05, 11, 41, 43, 53, 56</t>
+          <t>11, 28, 38, 41, 44, 53</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -5784,11 +5784,11 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>3069</v>
+        <v>3071</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5803,17 +5803,17 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
         <v>6</v>
       </c>
       <c r="I110" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -5833,11 +5833,11 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>3069</v>
+        <v>3071</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -5882,11 +5882,11 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>3069</v>
+        <v>3071</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5896,22 +5896,22 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>05, 10, 33, 37, 42, 53</t>
+          <t>05, 10, 33, 37, 43, 53</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
         <v>6</v>
       </c>
       <c r="I112" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -5931,11 +5931,11 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>3069</v>
+        <v>3071</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5945,22 +5945,22 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>05, 10, 11, 27, 43, 53</t>
+          <t>10, 11, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>05, 19, 22, 44, 47, 57</t>
+          <t>12, 22, 41, 45, 51, 52</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
         <v>6</v>
       </c>
       <c r="I113" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -5980,11 +5980,11 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>3070</v>
+        <v>3072</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5994,22 +5994,22 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>32, 42, 45, 46, 54, 58</t>
+          <t>11, 32, 34, 42, 46, 58</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
         <v>6</v>
       </c>
       <c r="I114" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -6029,11 +6029,11 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>3070</v>
+        <v>3072</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>12, 32, 34, 45, 46, 59</t>
+          <t>03, 32, 34, 42, 46, 59</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -6078,11 +6078,11 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>3070</v>
+        <v>3072</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6097,17 +6097,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H116" t="n">
         <v>6</v>
       </c>
       <c r="I116" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -6127,11 +6127,11 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>3070</v>
+        <v>3072</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6141,22 +6141,22 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>05, 11, 27, 28, 41, 53</t>
+          <t>10, 35, 41, 51, 53, 60</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
         <v>6</v>
       </c>
       <c r="I117" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -6176,11 +6176,11 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>3070</v>
+        <v>3072</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6195,17 +6195,17 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
         <v>6</v>
       </c>
       <c r="I118" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -6225,11 +6225,11 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>3070</v>
+        <v>3072</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6244,17 +6244,17 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H119" t="n">
         <v>6</v>
       </c>
       <c r="I119" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -6274,11 +6274,11 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>3070</v>
+        <v>3072</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>05, 10, 33, 37, 42, 53</t>
+          <t>05, 10, 33, 37, 43, 53</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -6323,11 +6323,11 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>3070</v>
+        <v>3072</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6337,22 +6337,22 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>05, 10, 11, 27, 37, 53</t>
+          <t>05, 10, 27, 33, 43, 53</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>19, 27, 29, 43, 54, 60</t>
+          <t>02, 06, 09, 16, 31, 40</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
         <v>6</v>
       </c>
       <c r="I121" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -6372,11 +6372,11 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>3071</v>
+        <v>3073</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>11, 32, 42, 45, 46, 58</t>
+          <t>11, 32, 34, 42, 46, 58</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -6421,11 +6421,11 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>3071</v>
+        <v>3073</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6435,22 +6435,22 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>12, 32, 34, 45, 46, 59</t>
+          <t>03, 32, 34, 42, 46, 59</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
         <v>6</v>
       </c>
       <c r="I123" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -6470,11 +6470,11 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>3071</v>
+        <v>3073</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -6519,11 +6519,11 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3071</v>
+        <v>3073</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6533,22 +6533,22 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>11, 28, 38, 41, 44, 53</t>
+          <t>05, 06, 10, 35, 44, 54</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H125" t="n">
         <v>6</v>
       </c>
       <c r="I125" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -6568,11 +6568,11 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>3071</v>
+        <v>3073</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -6617,11 +6617,11 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>3071</v>
+        <v>3073</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -6666,11 +6666,11 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>3071</v>
+        <v>3073</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -6715,11 +6715,11 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>3071</v>
+        <v>3073</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6729,12 +6729,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>10, 11, 27, 33, 37, 53</t>
+          <t>05, 06, 10, 27, 37, 53</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>12, 22, 41, 45, 51, 52</t>
+          <t>04, 13, 23, 28, 41, 58</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -6764,11 +6764,11 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>3072</v>
+        <v>3074</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>11, 32, 34, 42, 46, 58</t>
+          <t>11, 14, 32, 34, 42, 46</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -6813,11 +6813,11 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>3072</v>
+        <v>3074</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6832,17 +6832,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H131" t="n">
         <v>6</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -6862,11 +6862,11 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>3072</v>
+        <v>3074</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6876,22 +6876,22 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>06, 11, 17, 27, 30, 43</t>
+          <t>06, 11, 17, 27, 43, 58</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
         <v>6</v>
       </c>
       <c r="I132" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -6911,11 +6911,11 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>3072</v>
+        <v>3074</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>10, 35, 41, 51, 53, 60</t>
+          <t>10, 12, 16, 35, 41, 44</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -6960,11 +6960,11 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>3072</v>
+        <v>3074</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -7009,11 +7009,11 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>3072</v>
+        <v>3074</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7028,17 +7028,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
         <v>6</v>
       </c>
       <c r="I135" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -7058,11 +7058,11 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>3072</v>
+        <v>3074</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -7107,11 +7107,11 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>3072</v>
+        <v>3074</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>05, 10, 27, 33, 43, 53</t>
+          <t>05, 10, 27, 33, 37, 43</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>02, 06, 09, 16, 31, 40</t>
+          <t>02, 03, 20, 25, 39, 57</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -7156,11 +7156,11 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>3073</v>
+        <v>3075</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7170,22 +7170,22 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>11, 32, 34, 42, 46, 58</t>
+          <t>11, 14, 27, 32, 42, 46</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>07, 10, 14, 27, 36, 55</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H138" t="n">
         <v>6</v>
       </c>
       <c r="I138" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -7205,11 +7205,11 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>3073</v>
+        <v>3075</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>03, 32, 34, 42, 46, 59</t>
+          <t>26, 32, 34, 42, 46, 59</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>07, 10, 14, 27, 36, 55</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -7254,11 +7254,11 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3073</v>
+        <v>3075</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7268,22 +7268,22 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>06, 11, 17, 27, 30, 43</t>
+          <t>06, 11, 17, 27, 43, 58</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>07, 10, 14, 27, 36, 55</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140" t="n">
         <v>6</v>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -7303,11 +7303,11 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>3073</v>
+        <v>3075</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7317,22 +7317,22 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>05, 06, 10, 35, 44, 54</t>
+          <t>05, 10, 41, 44, 45, 53</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>07, 10, 14, 27, 36, 55</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141" t="n">
         <v>6</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -7352,11 +7352,11 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>3073</v>
+        <v>3075</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7371,17 +7371,17 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>07, 10, 14, 27, 36, 55</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H142" t="n">
         <v>6</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -7401,11 +7401,11 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>3073</v>
+        <v>3075</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7420,17 +7420,17 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>07, 10, 14, 27, 36, 55</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H143" t="n">
         <v>6</v>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -7450,11 +7450,11 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>3073</v>
+        <v>3075</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7469,17 +7469,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>07, 10, 14, 27, 36, 55</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144" t="n">
         <v>6</v>
       </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -7499,11 +7499,11 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>3073</v>
+        <v>3075</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>26/10/2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7513,22 +7513,22 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>05, 06, 10, 27, 37, 53</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>04, 13, 23, 28, 41, 58</t>
+          <t>07, 10, 14, 27, 36, 55</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H145" t="n">
         <v>6</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -7548,11 +7548,11 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>3074</v>
+        <v>3076</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7562,22 +7562,22 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>11, 14, 32, 34, 42, 46</t>
+          <t>11, 27, 32, 34, 42, 46</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>02, 03, 20, 25, 39, 57</t>
+          <t>06, 30, 32, 38, 49, 57</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146" t="n">
         <v>6</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -7597,11 +7597,11 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>3074</v>
+        <v>3076</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>03, 32, 34, 42, 46, 59</t>
+          <t>26, 32, 34, 42, 46, 59</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>02, 03, 20, 25, 39, 57</t>
+          <t>06, 30, 32, 38, 49, 57</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -7646,11 +7646,11 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>3074</v>
+        <v>3076</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7660,22 +7660,22 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>06, 11, 17, 27, 43, 58</t>
+          <t>06, 10, 14, 27, 43, 58</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>02, 03, 20, 25, 39, 57</t>
+          <t>06, 30, 32, 38, 49, 57</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H148" t="n">
         <v>6</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -7695,11 +7695,11 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>3074</v>
+        <v>3076</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>10, 12, 16, 35, 41, 44</t>
+          <t>05, 10, 25, 41, 45, 53</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>02, 03, 20, 25, 39, 57</t>
+          <t>06, 30, 32, 38, 49, 57</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -7744,11 +7744,11 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>3074</v>
+        <v>3076</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>02, 03, 20, 25, 39, 57</t>
+          <t>06, 30, 32, 38, 49, 57</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -7793,11 +7793,11 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>3074</v>
+        <v>3076</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7807,22 +7807,22 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>06, 10, 11, 17, 27, 43</t>
+          <t>06, 10, 11, 14, 27, 43</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>02, 03, 20, 25, 39, 57</t>
+          <t>06, 30, 32, 38, 49, 57</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H151" t="n">
         <v>6</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -7842,11 +7842,11 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>3074</v>
+        <v>3076</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>02, 03, 20, 25, 39, 57</t>
+          <t>06, 30, 32, 38, 49, 57</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -7891,11 +7891,11 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>3074</v>
+        <v>3076</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>05, 10, 27, 33, 37, 43</t>
+          <t>05, 10, 27, 33, 37, 53</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>02, 03, 20, 25, 39, 57</t>
+          <t>06, 30, 32, 38, 49, 57</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -7940,11 +7940,11 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>3075</v>
+        <v>3077</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7954,22 +7954,22 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>11, 14, 27, 32, 42, 46</t>
+          <t>11, 27, 34, 42, 43, 46</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>07, 10, 14, 27, 36, 55</t>
+          <t>02, 14, 18, 31, 35, 40</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H154" t="n">
         <v>6</v>
       </c>
       <c r="I154" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -7989,11 +7989,11 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>3075</v>
+        <v>3077</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>26, 32, 34, 42, 46, 59</t>
+          <t>26, 34, 42, 46, 56, 59</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>07, 10, 14, 27, 36, 55</t>
+          <t>02, 14, 18, 31, 35, 40</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -8038,11 +8038,11 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>3075</v>
+        <v>3077</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>06, 11, 17, 27, 43, 58</t>
+          <t>06, 14, 27, 30, 43, 58</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>07, 10, 14, 27, 36, 55</t>
+          <t>02, 14, 18, 31, 35, 40</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -8087,11 +8087,11 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>3075</v>
+        <v>3077</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>05, 10, 41, 44, 45, 53</t>
+          <t>05, 23, 35, 45, 53, 54</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>07, 10, 14, 27, 36, 55</t>
+          <t>02, 14, 18, 31, 35, 40</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -8136,11 +8136,11 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>3075</v>
+        <v>3077</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -8150,22 +8150,22 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>05, 10, 27, 33, 37, 53</t>
+          <t>05, 10, 27, 37, 38, 53</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>07, 10, 14, 27, 36, 55</t>
+          <t>02, 14, 18, 31, 35, 40</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H158" t="n">
         <v>6</v>
       </c>
       <c r="I158" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -8185,11 +8185,11 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>3075</v>
+        <v>3077</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -8199,22 +8199,22 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>06, 10, 11, 17, 27, 43</t>
+          <t>06, 10, 11, 27, 38, 43</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>07, 10, 14, 27, 36, 55</t>
+          <t>02, 14, 18, 31, 35, 40</t>
         </is>
       </c>
       <c r="G159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H159" t="n">
         <v>6</v>
       </c>
       <c r="I159" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -8234,11 +8234,11 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>3075</v>
+        <v>3077</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>05, 10, 33, 37, 43, 53</t>
+          <t>05, 10, 37, 38, 43, 53</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>07, 10, 14, 27, 36, 55</t>
+          <t>02, 14, 18, 31, 35, 40</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H160" t="n">
         <v>6</v>
       </c>
       <c r="I160" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -8283,11 +8283,11 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>3075</v>
+        <v>3077</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8297,22 +8297,22 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>05, 10, 27, 33, 37, 53</t>
+          <t>05, 10, 27, 38, 43, 53</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>07, 10, 14, 27, 36, 55</t>
+          <t>02, 14, 18, 31, 35, 40</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H161" t="n">
         <v>6</v>
       </c>
       <c r="I161" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
